--- a/research/traditional_assets/database/data/norway/norway_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_paper_forest_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ob_nskog" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.05967058823529411</v>
+        <v>0.05379419944378228</v>
       </c>
       <c r="H2">
-        <v>0.05967058823529411</v>
+        <v>0.05379419944378228</v>
       </c>
       <c r="I2">
-        <v>-0.02117647058823529</v>
+        <v>0.1422328168454509</v>
       </c>
       <c r="J2">
-        <v>-0.02117647058823529</v>
+        <v>0.1255710539872357</v>
       </c>
       <c r="K2">
-        <v>-243.6</v>
+        <v>175.6</v>
       </c>
       <c r="L2">
-        <v>-0.2292705882352941</v>
+        <v>0.1395311879221295</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,79 +623,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>133.3</v>
+        <v>188.5</v>
       </c>
       <c r="V2">
-        <v>0.3244098320759309</v>
+        <v>0.2929292929292929</v>
       </c>
       <c r="W2">
-        <v>-0.4838133068520357</v>
+        <v>0.553768527278461</v>
       </c>
       <c r="X2">
-        <v>0.06814872568389657</v>
+        <v>0.0986285450789802</v>
       </c>
       <c r="Y2">
-        <v>-0.5519620325359322</v>
+        <v>0.4551399821994808</v>
       </c>
       <c r="Z2">
-        <v>1.861748729630279</v>
+        <v>2.875257025359836</v>
       </c>
       <c r="AA2">
-        <v>-0.03942526721570002</v>
+        <v>0.3610490551586387</v>
       </c>
       <c r="AB2">
-        <v>0.04907614656142101</v>
+        <v>0.08182469202032319</v>
       </c>
       <c r="AC2">
-        <v>-0.08850141377712104</v>
+        <v>0.2792243631383154</v>
       </c>
       <c r="AD2">
-        <v>253.9</v>
+        <v>277.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>253.9</v>
+        <v>277.8</v>
       </c>
       <c r="AG2">
-        <v>120.6</v>
+        <v>89.30000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.3819193742478941</v>
+        <v>0.3015304461087594</v>
       </c>
       <c r="AI2">
-        <v>0.4446584938704028</v>
+        <v>0.3830667402095974</v>
       </c>
       <c r="AJ2">
-        <v>0.2269049858889934</v>
+        <v>0.1218613537117904</v>
       </c>
       <c r="AK2">
-        <v>0.27553118574366</v>
+        <v>0.1663871809204397</v>
       </c>
       <c r="AL2">
-        <v>14.1</v>
+        <v>9.67</v>
       </c>
       <c r="AM2">
-        <v>13.412</v>
+        <v>9.302</v>
       </c>
       <c r="AN2">
-        <v>13.15544041450777</v>
+        <v>1.285515964831097</v>
       </c>
       <c r="AO2">
-        <v>-1.595744680851064</v>
+        <v>18.51085832471562</v>
       </c>
       <c r="AP2">
-        <v>6.248704663212434</v>
+        <v>0.4132346136048127</v>
       </c>
       <c r="AQ2">
-        <v>-1.677602147330749</v>
+        <v>19.24317351107289</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +715,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.05967058823529411</v>
+        <v>0.05379419944378228</v>
       </c>
       <c r="H3">
-        <v>0.05967058823529411</v>
+        <v>0.05379419944378228</v>
       </c>
       <c r="I3">
-        <v>-0.02117647058823529</v>
+        <v>0.1422328168454509</v>
       </c>
       <c r="J3">
-        <v>-0.02117647058823529</v>
+        <v>0.1255710539872357</v>
       </c>
       <c r="K3">
-        <v>-243.6</v>
+        <v>175.6</v>
       </c>
       <c r="L3">
-        <v>-0.2292705882352941</v>
+        <v>0.1395311879221295</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +739,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +748,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>133.3</v>
+        <v>188.5</v>
       </c>
       <c r="V3">
-        <v>0.3244098320759309</v>
+        <v>0.2929292929292929</v>
       </c>
       <c r="W3">
-        <v>-0.4838133068520357</v>
+        <v>0.553768527278461</v>
       </c>
       <c r="X3">
-        <v>0.06814872568389657</v>
+        <v>0.0986285450789802</v>
       </c>
       <c r="Y3">
-        <v>-0.5519620325359322</v>
+        <v>0.4551399821994808</v>
       </c>
       <c r="Z3">
-        <v>1.861748729630279</v>
+        <v>2.875257025359836</v>
       </c>
       <c r="AA3">
-        <v>-0.03942526721570002</v>
+        <v>0.3610490551586387</v>
       </c>
       <c r="AB3">
-        <v>0.04907614656142101</v>
+        <v>0.08182469202032319</v>
       </c>
       <c r="AC3">
-        <v>-0.08850141377712104</v>
+        <v>0.2792243631383154</v>
       </c>
       <c r="AD3">
-        <v>253.9</v>
+        <v>277.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>253.9</v>
+        <v>277.8</v>
       </c>
       <c r="AG3">
-        <v>120.6</v>
+        <v>89.30000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.3819193742478941</v>
+        <v>0.3015304461087594</v>
       </c>
       <c r="AI3">
-        <v>0.4446584938704028</v>
+        <v>0.3830667402095974</v>
       </c>
       <c r="AJ3">
-        <v>0.2269049858889934</v>
+        <v>0.1218613537117904</v>
       </c>
       <c r="AK3">
-        <v>0.27553118574366</v>
+        <v>0.1663871809204397</v>
       </c>
       <c r="AL3">
-        <v>14.1</v>
+        <v>9.67</v>
       </c>
       <c r="AM3">
-        <v>13.412</v>
+        <v>9.302</v>
       </c>
       <c r="AN3">
-        <v>13.15544041450777</v>
+        <v>1.285515964831097</v>
       </c>
       <c r="AO3">
-        <v>-1.595744680851064</v>
+        <v>18.51085832471562</v>
       </c>
       <c r="AP3">
-        <v>6.248704663212434</v>
+        <v>0.4132346136048127</v>
       </c>
       <c r="AQ3">
-        <v>-1.677602147330749</v>
+        <v>19.24317351107289</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Norske Skog ASA (OB:NSKOG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OB:NSKOG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Paper/Forest Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.301530446108759</v>
+      </c>
+      <c r="F2">
+        <v>0.38</v>
+      </c>
+      <c r="G2">
+        <v>643.5</v>
+      </c>
+      <c r="H2">
+        <v>620.916297376027</v>
+      </c>
+      <c r="I2">
+        <v>732.8</v>
+      </c>
+      <c r="J2">
+        <v>782.510297376027</v>
+      </c>
+      <c r="K2">
+        <v>277.8</v>
+      </c>
+      <c r="L2">
+        <v>350.094</v>
+      </c>
+      <c r="M2">
+        <v>0.08182469202032321</v>
+      </c>
+      <c r="N2">
+        <v>0.07909147529203971</v>
+      </c>
+      <c r="O2">
+        <v>0.0429</v>
+      </c>
+      <c r="P2">
+        <v>0.036894</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.0986285450789802</v>
+      </c>
+      <c r="T2">
+        <v>0.104954444019419</v>
+      </c>
+      <c r="U2">
+        <v>1.01160152333445</v>
+      </c>
+      <c r="V2">
+        <v>1.11856198837936</v>
+      </c>
+      <c r="W2">
+        <v>10.42909273137407</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>643.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.055</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>216.1</v>
+      </c>
+      <c r="AH2">
+        <v>43.4</v>
+      </c>
+      <c r="AI2">
+        <v>154</v>
+      </c>
+      <c r="AJ2">
+        <v>277.8</v>
+      </c>
+      <c r="AK2">
+        <v>277.8</v>
+      </c>
+      <c r="AL2">
+        <v>9.67</v>
+      </c>
+      <c r="AM2">
+        <v>277.8</v>
+      </c>
+      <c r="AN2">
+        <v>188.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08355748067660379</v>
+      </c>
+      <c r="C2">
+        <v>892.9296022893401</v>
+      </c>
+      <c r="D2">
+        <v>704.4296022893401</v>
+      </c>
+      <c r="E2">
+        <v>-277.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>188.5</v>
+      </c>
+      <c r="H2">
+        <v>643.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>216.1</v>
+      </c>
+      <c r="K2">
+        <v>43.4</v>
+      </c>
+      <c r="L2">
+        <v>172.7</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>172.7</v>
+      </c>
+      <c r="O2">
+        <v>37.99399999999999</v>
+      </c>
+      <c r="P2">
+        <v>134.706</v>
+      </c>
+      <c r="Q2">
+        <v>178.106</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08355748067660379</v>
+      </c>
+      <c r="T2">
+        <v>0.7567748066294203</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.035646</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08342747421911526</v>
+      </c>
+      <c r="C3">
+        <v>885.7687102955887</v>
+      </c>
+      <c r="D3">
+        <v>706.4817102955886</v>
+      </c>
+      <c r="E3">
+        <v>-268.587</v>
+      </c>
+      <c r="F3">
+        <v>9.212999999999999</v>
+      </c>
+      <c r="G3">
+        <v>188.5</v>
+      </c>
+      <c r="H3">
+        <v>643.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>216.1</v>
+      </c>
+      <c r="K3">
+        <v>43.4</v>
+      </c>
+      <c r="L3">
+        <v>172.7</v>
+      </c>
+      <c r="M3">
+        <v>0.4210341</v>
+      </c>
+      <c r="N3">
+        <v>172.2789659</v>
+      </c>
+      <c r="O3">
+        <v>37.90137249799999</v>
+      </c>
+      <c r="P3">
+        <v>134.377593402</v>
+      </c>
+      <c r="Q3">
+        <v>177.777593402</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08391011537284369</v>
+      </c>
+      <c r="T3">
+        <v>0.7627372748028642</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.035646</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>410.180553071592</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08329746776162673</v>
+      </c>
+      <c r="C4">
+        <v>878.6198094242848</v>
+      </c>
+      <c r="D4">
+        <v>708.5458094242848</v>
+      </c>
+      <c r="E4">
+        <v>-259.374</v>
+      </c>
+      <c r="F4">
+        <v>18.426</v>
+      </c>
+      <c r="G4">
+        <v>188.5</v>
+      </c>
+      <c r="H4">
+        <v>643.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>216.1</v>
+      </c>
+      <c r="K4">
+        <v>43.4</v>
+      </c>
+      <c r="L4">
+        <v>172.7</v>
+      </c>
+      <c r="M4">
+        <v>0.8420682</v>
+      </c>
+      <c r="N4">
+        <v>171.8579318</v>
+      </c>
+      <c r="O4">
+        <v>37.80874499599999</v>
+      </c>
+      <c r="P4">
+        <v>134.049186804</v>
+      </c>
+      <c r="Q4">
+        <v>177.449186804</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08426994669553747</v>
+      </c>
+      <c r="T4">
+        <v>0.7688214260002559</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.035646</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>205.090276535796</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.0831674613041382</v>
+      </c>
+      <c r="C5">
+        <v>871.483005085338</v>
+      </c>
+      <c r="D5">
+        <v>710.6220050853381</v>
+      </c>
+      <c r="E5">
+        <v>-250.161</v>
+      </c>
+      <c r="F5">
+        <v>27.639</v>
+      </c>
+      <c r="G5">
+        <v>188.5</v>
+      </c>
+      <c r="H5">
+        <v>643.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>216.1</v>
+      </c>
+      <c r="K5">
+        <v>43.4</v>
+      </c>
+      <c r="L5">
+        <v>172.7</v>
+      </c>
+      <c r="M5">
+        <v>1.2631023</v>
+      </c>
+      <c r="N5">
+        <v>171.4368977</v>
+      </c>
+      <c r="O5">
+        <v>37.71611749399999</v>
+      </c>
+      <c r="P5">
+        <v>133.720780206</v>
+      </c>
+      <c r="Q5">
+        <v>177.120780206</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08463719722076103</v>
+      </c>
+      <c r="T5">
+        <v>0.7750310236140888</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.035646</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>136.726851023864</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08303745484664966</v>
+      </c>
+      <c r="C6">
+        <v>864.358403927785</v>
+      </c>
+      <c r="D6">
+        <v>712.710403927785</v>
+      </c>
+      <c r="E6">
+        <v>-240.948</v>
+      </c>
+      <c r="F6">
+        <v>36.852</v>
+      </c>
+      <c r="G6">
+        <v>188.5</v>
+      </c>
+      <c r="H6">
+        <v>643.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>216.1</v>
+      </c>
+      <c r="K6">
+        <v>43.4</v>
+      </c>
+      <c r="L6">
+        <v>172.7</v>
+      </c>
+      <c r="M6">
+        <v>1.6841364</v>
+      </c>
+      <c r="N6">
+        <v>171.0158636</v>
+      </c>
+      <c r="O6">
+        <v>37.623489992</v>
+      </c>
+      <c r="P6">
+        <v>133.392373608</v>
+      </c>
+      <c r="Q6">
+        <v>176.792373608</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08501209879859341</v>
+      </c>
+      <c r="T6">
+        <v>0.7813699878448764</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.035646</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>102.545138267898</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08290744838916114</v>
+      </c>
+      <c r="C7">
+        <v>857.2461138580525</v>
+      </c>
+      <c r="D7">
+        <v>714.8111138580524</v>
+      </c>
+      <c r="E7">
+        <v>-231.735</v>
+      </c>
+      <c r="F7">
+        <v>46.065</v>
+      </c>
+      <c r="G7">
+        <v>188.5</v>
+      </c>
+      <c r="H7">
+        <v>643.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>216.1</v>
+      </c>
+      <c r="K7">
+        <v>43.4</v>
+      </c>
+      <c r="L7">
+        <v>172.7</v>
+      </c>
+      <c r="M7">
+        <v>2.1051705</v>
+      </c>
+      <c r="N7">
+        <v>170.5948295</v>
+      </c>
+      <c r="O7">
+        <v>37.53086248999999</v>
+      </c>
+      <c r="P7">
+        <v>133.06396701</v>
+      </c>
+      <c r="Q7">
+        <v>176.46396701</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08539489304122226</v>
+      </c>
+      <c r="T7">
+        <v>0.7878424039542071</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.035646</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>82.03611061431839</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08277744193167261</v>
+      </c>
+      <c r="C8">
+        <v>850.1462440585425</v>
+      </c>
+      <c r="D8">
+        <v>716.9242440585425</v>
+      </c>
+      <c r="E8">
+        <v>-222.522</v>
+      </c>
+      <c r="F8">
+        <v>55.278</v>
+      </c>
+      <c r="G8">
+        <v>188.5</v>
+      </c>
+      <c r="H8">
+        <v>643.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>216.1</v>
+      </c>
+      <c r="K8">
+        <v>43.4</v>
+      </c>
+      <c r="L8">
+        <v>172.7</v>
+      </c>
+      <c r="M8">
+        <v>2.5262046</v>
+      </c>
+      <c r="N8">
+        <v>170.1737954</v>
+      </c>
+      <c r="O8">
+        <v>37.43823498799999</v>
+      </c>
+      <c r="P8">
+        <v>132.735560412</v>
+      </c>
+      <c r="Q8">
+        <v>176.135560412</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08578583184220491</v>
+      </c>
+      <c r="T8">
+        <v>0.7944525310445871</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.035646</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>68.36342551193199</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.0826474354741841</v>
+      </c>
+      <c r="C9">
+        <v>843.0589050065483</v>
+      </c>
+      <c r="D9">
+        <v>719.0499050065483</v>
+      </c>
+      <c r="E9">
+        <v>-213.309</v>
+      </c>
+      <c r="F9">
+        <v>64.491</v>
+      </c>
+      <c r="G9">
+        <v>188.5</v>
+      </c>
+      <c r="H9">
+        <v>643.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>216.1</v>
+      </c>
+      <c r="K9">
+        <v>43.4</v>
+      </c>
+      <c r="L9">
+        <v>172.7</v>
+      </c>
+      <c r="M9">
+        <v>2.9472387</v>
+      </c>
+      <c r="N9">
+        <v>169.7527613</v>
+      </c>
+      <c r="O9">
+        <v>37.34560748599999</v>
+      </c>
+      <c r="P9">
+        <v>132.407153814</v>
+      </c>
+      <c r="Q9">
+        <v>175.807153814</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08618517792923021</v>
+      </c>
+      <c r="T9">
+        <v>0.8012048114057283</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.035646</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>58.59722186737028</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08251742901669555</v>
+      </c>
+      <c r="C10">
+        <v>835.9842084935095</v>
+      </c>
+      <c r="D10">
+        <v>721.1882084935095</v>
+      </c>
+      <c r="E10">
+        <v>-204.096</v>
+      </c>
+      <c r="F10">
+        <v>73.70399999999999</v>
+      </c>
+      <c r="G10">
+        <v>188.5</v>
+      </c>
+      <c r="H10">
+        <v>643.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>216.1</v>
+      </c>
+      <c r="K10">
+        <v>43.4</v>
+      </c>
+      <c r="L10">
+        <v>172.7</v>
+      </c>
+      <c r="M10">
+        <v>3.3682728</v>
+      </c>
+      <c r="N10">
+        <v>169.3317272</v>
+      </c>
+      <c r="O10">
+        <v>37.25297998399999</v>
+      </c>
+      <c r="P10">
+        <v>132.078747216</v>
+      </c>
+      <c r="Q10">
+        <v>175.478747216</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08659320545292995</v>
+      </c>
+      <c r="T10">
+        <v>0.8081038804703723</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.035646</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>51.27256913394901</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08238742255920704</v>
+      </c>
+      <c r="C11">
+        <v>828.9222676446067</v>
+      </c>
+      <c r="D11">
+        <v>723.3392676446067</v>
+      </c>
+      <c r="E11">
+        <v>-194.883</v>
+      </c>
+      <c r="F11">
+        <v>82.91699999999999</v>
+      </c>
+      <c r="G11">
+        <v>188.5</v>
+      </c>
+      <c r="H11">
+        <v>643.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>216.1</v>
+      </c>
+      <c r="K11">
+        <v>43.4</v>
+      </c>
+      <c r="L11">
+        <v>172.7</v>
+      </c>
+      <c r="M11">
+        <v>3.7893069</v>
+      </c>
+      <c r="N11">
+        <v>168.9106931</v>
+      </c>
+      <c r="O11">
+        <v>37.16035248199999</v>
+      </c>
+      <c r="P11">
+        <v>131.750340618</v>
+      </c>
+      <c r="Q11">
+        <v>175.150340618</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08701020061451323</v>
+      </c>
+      <c r="T11">
+        <v>0.8151545774265471</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.035646</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>45.57561700795468</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08225741610171849</v>
+      </c>
+      <c r="C12">
+        <v>821.8731969387168</v>
+      </c>
+      <c r="D12">
+        <v>725.5031969387168</v>
+      </c>
+      <c r="E12">
+        <v>-185.67</v>
+      </c>
+      <c r="F12">
+        <v>92.13</v>
+      </c>
+      <c r="G12">
+        <v>188.5</v>
+      </c>
+      <c r="H12">
+        <v>643.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>216.1</v>
+      </c>
+      <c r="K12">
+        <v>43.4</v>
+      </c>
+      <c r="L12">
+        <v>172.7</v>
+      </c>
+      <c r="M12">
+        <v>4.210341000000001</v>
+      </c>
+      <c r="N12">
+        <v>168.489659</v>
+      </c>
+      <c r="O12">
+        <v>37.06772497999999</v>
+      </c>
+      <c r="P12">
+        <v>131.42193402</v>
+      </c>
+      <c r="Q12">
+        <v>174.82193402</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08743646233524277</v>
+      </c>
+      <c r="T12">
+        <v>0.8223619565373034</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.035646</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>41.0180553071592</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08212740964422999</v>
+      </c>
+      <c r="C13">
+        <v>814.8371122287161</v>
+      </c>
+      <c r="D13">
+        <v>727.6801122287161</v>
+      </c>
+      <c r="E13">
+        <v>-176.457</v>
+      </c>
+      <c r="F13">
+        <v>101.343</v>
+      </c>
+      <c r="G13">
+        <v>188.5</v>
+      </c>
+      <c r="H13">
+        <v>643.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>216.1</v>
+      </c>
+      <c r="K13">
+        <v>43.4</v>
+      </c>
+      <c r="L13">
+        <v>172.7</v>
+      </c>
+      <c r="M13">
+        <v>4.6313751</v>
+      </c>
+      <c r="N13">
+        <v>168.0686249</v>
+      </c>
+      <c r="O13">
+        <v>36.97509747799999</v>
+      </c>
+      <c r="P13">
+        <v>131.093527422</v>
+      </c>
+      <c r="Q13">
+        <v>174.493527422</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08787230297104492</v>
+      </c>
+      <c r="T13">
+        <v>0.8297312992235825</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.035646</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>37.28914118832655</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08199740318674145</v>
+      </c>
+      <c r="C14">
+        <v>807.8141307621623</v>
+      </c>
+      <c r="D14">
+        <v>729.8701307621624</v>
+      </c>
+      <c r="E14">
+        <v>-167.244</v>
+      </c>
+      <c r="F14">
+        <v>110.556</v>
+      </c>
+      <c r="G14">
+        <v>188.5</v>
+      </c>
+      <c r="H14">
+        <v>643.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>216.1</v>
+      </c>
+      <c r="K14">
+        <v>43.4</v>
+      </c>
+      <c r="L14">
+        <v>172.7</v>
+      </c>
+      <c r="M14">
+        <v>5.0524092</v>
+      </c>
+      <c r="N14">
+        <v>167.6475908</v>
+      </c>
+      <c r="O14">
+        <v>36.882469976</v>
+      </c>
+      <c r="P14">
+        <v>130.765120824</v>
+      </c>
+      <c r="Q14">
+        <v>174.165120824</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08831804907584256</v>
+      </c>
+      <c r="T14">
+        <v>0.8372681269709132</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.035646</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>34.181712755966</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08186739672925292</v>
+      </c>
+      <c r="C15">
+        <v>800.8043712023405</v>
+      </c>
+      <c r="D15">
+        <v>732.0733712023405</v>
+      </c>
+      <c r="E15">
+        <v>-158.031</v>
+      </c>
+      <c r="F15">
+        <v>119.769</v>
+      </c>
+      <c r="G15">
+        <v>188.5</v>
+      </c>
+      <c r="H15">
+        <v>643.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>216.1</v>
+      </c>
+      <c r="K15">
+        <v>43.4</v>
+      </c>
+      <c r="L15">
+        <v>172.7</v>
+      </c>
+      <c r="M15">
+        <v>5.4734433</v>
+      </c>
+      <c r="N15">
+        <v>167.2265567</v>
+      </c>
+      <c r="O15">
+        <v>36.78984247399999</v>
+      </c>
+      <c r="P15">
+        <v>130.436714226</v>
+      </c>
+      <c r="Q15">
+        <v>173.836714226</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.0887740422175321</v>
+      </c>
+      <c r="T15">
+        <v>0.8449782151262286</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.035646</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>31.5523502362763</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.0817373902717644</v>
+      </c>
+      <c r="C16">
+        <v>793.8079536496972</v>
+      </c>
+      <c r="D16">
+        <v>734.2899536496972</v>
+      </c>
+      <c r="E16">
+        <v>-148.818</v>
+      </c>
+      <c r="F16">
+        <v>128.982</v>
+      </c>
+      <c r="G16">
+        <v>188.5</v>
+      </c>
+      <c r="H16">
+        <v>643.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>216.1</v>
+      </c>
+      <c r="K16">
+        <v>43.4</v>
+      </c>
+      <c r="L16">
+        <v>172.7</v>
+      </c>
+      <c r="M16">
+        <v>5.8944774</v>
+      </c>
+      <c r="N16">
+        <v>166.8055226</v>
+      </c>
+      <c r="O16">
+        <v>36.69721497199999</v>
+      </c>
+      <c r="P16">
+        <v>130.108307628</v>
+      </c>
+      <c r="Q16">
+        <v>173.508307628</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08924063985088883</v>
+      </c>
+      <c r="T16">
+        <v>0.852867607657249</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.035646</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>29.29861093368514</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08160738381427586</v>
+      </c>
+      <c r="C17">
+        <v>786.824999663665</v>
+      </c>
+      <c r="D17">
+        <v>736.519999663665</v>
+      </c>
+      <c r="E17">
+        <v>-139.605</v>
+      </c>
+      <c r="F17">
+        <v>138.195</v>
+      </c>
+      <c r="G17">
+        <v>188.5</v>
+      </c>
+      <c r="H17">
+        <v>643.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>216.1</v>
+      </c>
+      <c r="K17">
+        <v>43.4</v>
+      </c>
+      <c r="L17">
+        <v>172.7</v>
+      </c>
+      <c r="M17">
+        <v>6.3155115</v>
+      </c>
+      <c r="N17">
+        <v>166.3844885</v>
+      </c>
+      <c r="O17">
+        <v>36.60458746999999</v>
+      </c>
+      <c r="P17">
+        <v>129.77990103</v>
+      </c>
+      <c r="Q17">
+        <v>173.17990103</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08971821625208926</v>
+      </c>
+      <c r="T17">
+        <v>0.8609426329537052</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.035646</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>27.3453702047728</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08147737735678734</v>
+      </c>
+      <c r="C18">
+        <v>779.855632284883</v>
+      </c>
+      <c r="D18">
+        <v>738.763632284883</v>
+      </c>
+      <c r="E18">
+        <v>-130.392</v>
+      </c>
+      <c r="F18">
+        <v>147.408</v>
+      </c>
+      <c r="G18">
+        <v>188.5</v>
+      </c>
+      <c r="H18">
+        <v>643.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>216.1</v>
+      </c>
+      <c r="K18">
+        <v>43.4</v>
+      </c>
+      <c r="L18">
+        <v>172.7</v>
+      </c>
+      <c r="M18">
+        <v>6.7365456</v>
+      </c>
+      <c r="N18">
+        <v>165.9634544</v>
+      </c>
+      <c r="O18">
+        <v>36.51195996799999</v>
+      </c>
+      <c r="P18">
+        <v>129.451494432</v>
+      </c>
+      <c r="Q18">
+        <v>172.851494432</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09020716351998492</v>
+      </c>
+      <c r="T18">
+        <v>0.8692099207572199</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.035646</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>25.6362845669745</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.0813473708992988</v>
+      </c>
+      <c r="C19">
+        <v>772.8999760578282</v>
+      </c>
+      <c r="D19">
+        <v>741.0209760578282</v>
+      </c>
+      <c r="E19">
+        <v>-121.179</v>
+      </c>
+      <c r="F19">
+        <v>156.621</v>
+      </c>
+      <c r="G19">
+        <v>188.5</v>
+      </c>
+      <c r="H19">
+        <v>643.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>216.1</v>
+      </c>
+      <c r="K19">
+        <v>43.4</v>
+      </c>
+      <c r="L19">
+        <v>172.7</v>
+      </c>
+      <c r="M19">
+        <v>7.157579700000001</v>
+      </c>
+      <c r="N19">
+        <v>165.5424203</v>
+      </c>
+      <c r="O19">
+        <v>36.41933246599999</v>
+      </c>
+      <c r="P19">
+        <v>129.123087834</v>
+      </c>
+      <c r="Q19">
+        <v>172.523087834</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09070789264975759</v>
+      </c>
+      <c r="T19">
+        <v>0.8776764203150362</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.035646</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>24.1282678277407</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08121736444181027</v>
+      </c>
+      <c r="C20">
+        <v>765.9581570538596</v>
+      </c>
+      <c r="D20">
+        <v>743.2921570538596</v>
+      </c>
+      <c r="E20">
+        <v>-111.966</v>
+      </c>
+      <c r="F20">
+        <v>165.834</v>
+      </c>
+      <c r="G20">
+        <v>188.5</v>
+      </c>
+      <c r="H20">
+        <v>643.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>216.1</v>
+      </c>
+      <c r="K20">
+        <v>43.4</v>
+      </c>
+      <c r="L20">
+        <v>172.7</v>
+      </c>
+      <c r="M20">
+        <v>7.578613799999999</v>
+      </c>
+      <c r="N20">
+        <v>165.1213862</v>
+      </c>
+      <c r="O20">
+        <v>36.32670496399999</v>
+      </c>
+      <c r="P20">
+        <v>128.794681236</v>
+      </c>
+      <c r="Q20">
+        <v>172.194681236</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09122083468513448</v>
+      </c>
+      <c r="T20">
+        <v>0.8863494198620674</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.035646</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>22.78780850397734</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08108735798432175</v>
+      </c>
+      <c r="C21">
+        <v>759.0303028946898</v>
+      </c>
+      <c r="D21">
+        <v>745.5773028946899</v>
+      </c>
+      <c r="E21">
+        <v>-102.753</v>
+      </c>
+      <c r="F21">
+        <v>175.047</v>
+      </c>
+      <c r="G21">
+        <v>188.5</v>
+      </c>
+      <c r="H21">
+        <v>643.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>216.1</v>
+      </c>
+      <c r="K21">
+        <v>43.4</v>
+      </c>
+      <c r="L21">
+        <v>172.7</v>
+      </c>
+      <c r="M21">
+        <v>7.9996479</v>
+      </c>
+      <c r="N21">
+        <v>164.7003521</v>
+      </c>
+      <c r="O21">
+        <v>36.23407746199999</v>
+      </c>
+      <c r="P21">
+        <v>128.466274638</v>
+      </c>
+      <c r="Q21">
+        <v>171.866274638</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09174644195595277</v>
+      </c>
+      <c r="T21">
+        <v>0.8952365675460624</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.035646</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>21.58845016166273</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08095735152683323</v>
+      </c>
+      <c r="C22">
+        <v>752.1165427762911</v>
+      </c>
+      <c r="D22">
+        <v>747.8765427762911</v>
+      </c>
+      <c r="E22">
+        <v>-93.54000000000002</v>
+      </c>
+      <c r="F22">
+        <v>184.26</v>
+      </c>
+      <c r="G22">
+        <v>188.5</v>
+      </c>
+      <c r="H22">
+        <v>643.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>216.1</v>
+      </c>
+      <c r="K22">
+        <v>43.4</v>
+      </c>
+      <c r="L22">
+        <v>172.7</v>
+      </c>
+      <c r="M22">
+        <v>8.420682000000001</v>
+      </c>
+      <c r="N22">
+        <v>164.279318</v>
+      </c>
+      <c r="O22">
+        <v>36.14144996</v>
+      </c>
+      <c r="P22">
+        <v>128.13786804</v>
+      </c>
+      <c r="Q22">
+        <v>171.53786804</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09228518940854152</v>
+      </c>
+      <c r="T22">
+        <v>0.9043458939221574</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.035646</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>20.5090276535796</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08082734506934471</v>
+      </c>
+      <c r="C23">
+        <v>745.2170074932434</v>
+      </c>
+      <c r="D23">
+        <v>750.1900074932433</v>
+      </c>
+      <c r="E23">
+        <v>-84.32700000000003</v>
+      </c>
+      <c r="F23">
+        <v>193.473</v>
+      </c>
+      <c r="G23">
+        <v>188.5</v>
+      </c>
+      <c r="H23">
+        <v>643.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>216.1</v>
+      </c>
+      <c r="K23">
+        <v>43.4</v>
+      </c>
+      <c r="L23">
+        <v>172.7</v>
+      </c>
+      <c r="M23">
+        <v>8.841716099999999</v>
+      </c>
+      <c r="N23">
+        <v>163.8582839</v>
+      </c>
+      <c r="O23">
+        <v>36.048822458</v>
+      </c>
+      <c r="P23">
+        <v>127.809461442</v>
+      </c>
+      <c r="Q23">
+        <v>171.209461442</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09283757603714518</v>
+      </c>
+      <c r="T23">
+        <v>0.9136858361558747</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.035646</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>19.53240728912343</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08069733861185616</v>
+      </c>
+      <c r="C24">
+        <v>738.3318294635369</v>
+      </c>
+      <c r="D24">
+        <v>752.5178294635369</v>
+      </c>
+      <c r="E24">
+        <v>-75.11400000000003</v>
+      </c>
+      <c r="F24">
+        <v>202.686</v>
+      </c>
+      <c r="G24">
+        <v>188.5</v>
+      </c>
+      <c r="H24">
+        <v>643.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>216.1</v>
+      </c>
+      <c r="K24">
+        <v>43.4</v>
+      </c>
+      <c r="L24">
+        <v>172.7</v>
+      </c>
+      <c r="M24">
+        <v>9.262750199999999</v>
+      </c>
+      <c r="N24">
+        <v>163.4372498</v>
+      </c>
+      <c r="O24">
+        <v>35.95619495599999</v>
+      </c>
+      <c r="P24">
+        <v>127.481054844</v>
+      </c>
+      <c r="Q24">
+        <v>170.881054844</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09340412642545662</v>
+      </c>
+      <c r="T24">
+        <v>0.9232652640878928</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.035646</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>18.64457059416328</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08056733215436765</v>
+      </c>
+      <c r="C25">
+        <v>731.4611427538357</v>
+      </c>
+      <c r="D25">
+        <v>754.8601427538357</v>
+      </c>
+      <c r="E25">
+        <v>-65.90100000000001</v>
+      </c>
+      <c r="F25">
+        <v>211.899</v>
+      </c>
+      <c r="G25">
+        <v>188.5</v>
+      </c>
+      <c r="H25">
+        <v>643.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>216.1</v>
+      </c>
+      <c r="K25">
+        <v>43.4</v>
+      </c>
+      <c r="L25">
+        <v>172.7</v>
+      </c>
+      <c r="M25">
+        <v>9.683784300000001</v>
+      </c>
+      <c r="N25">
+        <v>163.0162157</v>
+      </c>
+      <c r="O25">
+        <v>35.86356745399999</v>
+      </c>
+      <c r="P25">
+        <v>127.152648246</v>
+      </c>
+      <c r="Q25">
+        <v>170.552648246</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09398539240826967</v>
+      </c>
+      <c r="T25">
+        <v>0.9330935083298334</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.035646</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>17.83393709006922</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08043732569687911</v>
+      </c>
+      <c r="C26">
+        <v>724.6050831052202</v>
+      </c>
+      <c r="D26">
+        <v>757.2170831052201</v>
+      </c>
+      <c r="E26">
+        <v>-56.68800000000002</v>
+      </c>
+      <c r="F26">
+        <v>221.112</v>
+      </c>
+      <c r="G26">
+        <v>188.5</v>
+      </c>
+      <c r="H26">
+        <v>643.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>216.1</v>
+      </c>
+      <c r="K26">
+        <v>43.4</v>
+      </c>
+      <c r="L26">
+        <v>172.7</v>
+      </c>
+      <c r="M26">
+        <v>10.1048184</v>
+      </c>
+      <c r="N26">
+        <v>162.5951816</v>
+      </c>
+      <c r="O26">
+        <v>35.77093995199999</v>
+      </c>
+      <c r="P26">
+        <v>126.824241648</v>
+      </c>
+      <c r="Q26">
+        <v>170.224241648</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09458195486431462</v>
+      </c>
+      <c r="T26">
+        <v>0.9431803905781407</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.035646</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>17.090856377983</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08030731923939058</v>
+      </c>
+      <c r="C27">
+        <v>717.7637879594063</v>
+      </c>
+      <c r="D27">
+        <v>759.5887879594063</v>
+      </c>
+      <c r="E27">
+        <v>-47.47500000000002</v>
+      </c>
+      <c r="F27">
+        <v>230.325</v>
+      </c>
+      <c r="G27">
+        <v>188.5</v>
+      </c>
+      <c r="H27">
+        <v>643.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>216.1</v>
+      </c>
+      <c r="K27">
+        <v>43.4</v>
+      </c>
+      <c r="L27">
+        <v>172.7</v>
+      </c>
+      <c r="M27">
+        <v>10.5258525</v>
+      </c>
+      <c r="N27">
+        <v>162.1741475</v>
+      </c>
+      <c r="O27">
+        <v>35.67831244999999</v>
+      </c>
+      <c r="P27">
+        <v>126.49583505</v>
+      </c>
+      <c r="Q27">
+        <v>169.89583505</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09519442565252077</v>
+      </c>
+      <c r="T27">
+        <v>0.9535362563530696</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.035646</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>16.40722212286368</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08017731278190206</v>
+      </c>
+      <c r="C28">
+        <v>710.9373964854628</v>
+      </c>
+      <c r="D28">
+        <v>761.9753964854629</v>
+      </c>
+      <c r="E28">
+        <v>-38.26200000000003</v>
+      </c>
+      <c r="F28">
+        <v>239.538</v>
+      </c>
+      <c r="G28">
+        <v>188.5</v>
+      </c>
+      <c r="H28">
+        <v>643.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>216.1</v>
+      </c>
+      <c r="K28">
+        <v>43.4</v>
+      </c>
+      <c r="L28">
+        <v>172.7</v>
+      </c>
+      <c r="M28">
+        <v>10.9468866</v>
+      </c>
+      <c r="N28">
+        <v>161.7531134</v>
+      </c>
+      <c r="O28">
+        <v>35.58568494799999</v>
+      </c>
+      <c r="P28">
+        <v>126.167428452</v>
+      </c>
+      <c r="Q28">
+        <v>169.567428452</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09582344970527304</v>
+      </c>
+      <c r="T28">
+        <v>0.9641720103921858</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.035646</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>15.77617511813815</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08004730632441351</v>
+      </c>
+      <c r="C29">
+        <v>704.1260496070361</v>
+      </c>
+      <c r="D29">
+        <v>764.377049607036</v>
+      </c>
+      <c r="E29">
+        <v>-29.04900000000001</v>
+      </c>
+      <c r="F29">
+        <v>248.751</v>
+      </c>
+      <c r="G29">
+        <v>188.5</v>
+      </c>
+      <c r="H29">
+        <v>643.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>216.1</v>
+      </c>
+      <c r="K29">
+        <v>43.4</v>
+      </c>
+      <c r="L29">
+        <v>172.7</v>
+      </c>
+      <c r="M29">
+        <v>11.3679207</v>
+      </c>
+      <c r="N29">
+        <v>161.3320793</v>
+      </c>
+      <c r="O29">
+        <v>35.49305744599999</v>
+      </c>
+      <c r="P29">
+        <v>125.839021854</v>
+      </c>
+      <c r="Q29">
+        <v>169.239021854</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09646970729371715</v>
+      </c>
+      <c r="T29">
+        <v>0.9750991549529215</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.035646</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>15.19187233598489</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.07991729986692499</v>
+      </c>
+      <c r="C30">
+        <v>697.3298900300833</v>
+      </c>
+      <c r="D30">
+        <v>766.7938900300833</v>
+      </c>
+      <c r="E30">
+        <v>-19.83600000000001</v>
+      </c>
+      <c r="F30">
+        <v>257.964</v>
+      </c>
+      <c r="G30">
+        <v>188.5</v>
+      </c>
+      <c r="H30">
+        <v>643.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>216.1</v>
+      </c>
+      <c r="K30">
+        <v>43.4</v>
+      </c>
+      <c r="L30">
+        <v>172.7</v>
+      </c>
+      <c r="M30">
+        <v>11.7889548</v>
+      </c>
+      <c r="N30">
+        <v>160.9110452</v>
+      </c>
+      <c r="O30">
+        <v>35.400429944</v>
+      </c>
+      <c r="P30">
+        <v>125.510615256</v>
+      </c>
+      <c r="Q30">
+        <v>168.910615256</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09713391648184028</v>
+      </c>
+      <c r="T30">
+        <v>0.9863298313070112</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.035646</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>14.64930546684257</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.07978729340943645</v>
+      </c>
+      <c r="C31">
+        <v>690.5490622711445</v>
+      </c>
+      <c r="D31">
+        <v>769.2260622711444</v>
+      </c>
+      <c r="E31">
+        <v>-10.62300000000005</v>
+      </c>
+      <c r="F31">
+        <v>267.177</v>
+      </c>
+      <c r="G31">
+        <v>188.5</v>
+      </c>
+      <c r="H31">
+        <v>643.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>216.1</v>
+      </c>
+      <c r="K31">
+        <v>43.4</v>
+      </c>
+      <c r="L31">
+        <v>172.7</v>
+      </c>
+      <c r="M31">
+        <v>12.2099889</v>
+      </c>
+      <c r="N31">
+        <v>160.4900111</v>
+      </c>
+      <c r="O31">
+        <v>35.307802442</v>
+      </c>
+      <c r="P31">
+        <v>125.182208658</v>
+      </c>
+      <c r="Q31">
+        <v>168.582208658</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09781683578793868</v>
+      </c>
+      <c r="T31">
+        <v>0.9978768647414976</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.035646</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>14.14415700246869</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.07965728695194794</v>
+      </c>
+      <c r="C32">
+        <v>683.7837126861443</v>
+      </c>
+      <c r="D32">
+        <v>771.6737126861443</v>
+      </c>
+      <c r="E32">
+        <v>-1.410000000000025</v>
+      </c>
+      <c r="F32">
+        <v>276.39</v>
+      </c>
+      <c r="G32">
+        <v>188.5</v>
+      </c>
+      <c r="H32">
+        <v>643.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>216.1</v>
+      </c>
+      <c r="K32">
+        <v>43.4</v>
+      </c>
+      <c r="L32">
+        <v>172.7</v>
+      </c>
+      <c r="M32">
+        <v>12.631023</v>
+      </c>
+      <c r="N32">
+        <v>160.068977</v>
+      </c>
+      <c r="O32">
+        <v>35.21517493999999</v>
+      </c>
+      <c r="P32">
+        <v>124.85380206</v>
+      </c>
+      <c r="Q32">
+        <v>168.25380206</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09851926707421135</v>
+      </c>
+      <c r="T32">
+        <v>1.009753813416969</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.035646</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>13.6726851023864</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.07952728049445942</v>
+      </c>
+      <c r="C33">
+        <v>677.033989499753</v>
+      </c>
+      <c r="D33">
+        <v>774.136989499753</v>
+      </c>
+      <c r="E33">
+        <v>7.802999999999997</v>
+      </c>
+      <c r="F33">
+        <v>285.603</v>
+      </c>
+      <c r="G33">
+        <v>188.5</v>
+      </c>
+      <c r="H33">
+        <v>643.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>216.1</v>
+      </c>
+      <c r="K33">
+        <v>43.4</v>
+      </c>
+      <c r="L33">
+        <v>172.7</v>
+      </c>
+      <c r="M33">
+        <v>13.0520571</v>
+      </c>
+      <c r="N33">
+        <v>159.6479429</v>
+      </c>
+      <c r="O33">
+        <v>35.12254743799999</v>
+      </c>
+      <c r="P33">
+        <v>124.525395462</v>
+      </c>
+      <c r="Q33">
+        <v>167.925395462</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09924205868762234</v>
+      </c>
+      <c r="T33">
+        <v>1.021975021474339</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.035646</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>13.2316307442449</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.07979663403697088</v>
+      </c>
+      <c r="C34">
+        <v>662.7348026600514</v>
+      </c>
+      <c r="D34">
+        <v>769.0508026600513</v>
+      </c>
+      <c r="E34">
+        <v>17.01599999999996</v>
+      </c>
+      <c r="F34">
+        <v>294.816</v>
+      </c>
+      <c r="G34">
+        <v>188.5</v>
+      </c>
+      <c r="H34">
+        <v>643.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>216.1</v>
+      </c>
+      <c r="K34">
+        <v>43.4</v>
+      </c>
+      <c r="L34">
+        <v>172.7</v>
+      </c>
+      <c r="M34">
+        <v>13.9447968</v>
+      </c>
+      <c r="N34">
+        <v>158.7552032</v>
+      </c>
+      <c r="O34">
+        <v>34.926144704</v>
+      </c>
+      <c r="P34">
+        <v>123.829058496</v>
+      </c>
+      <c r="Q34">
+        <v>167.229058496</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09998610887789836</v>
+      </c>
+      <c r="T34">
+        <v>1.034555676827513</v>
+      </c>
+      <c r="U34">
+        <v>0.0473</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.036894</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>12.38454761850671</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.07967910757948235</v>
+      </c>
+      <c r="C35">
+        <v>655.7328053413014</v>
+      </c>
+      <c r="D35">
+        <v>771.2618053413014</v>
+      </c>
+      <c r="E35">
+        <v>26.22899999999998</v>
+      </c>
+      <c r="F35">
+        <v>304.029</v>
+      </c>
+      <c r="G35">
+        <v>188.5</v>
+      </c>
+      <c r="H35">
+        <v>643.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>216.1</v>
+      </c>
+      <c r="K35">
+        <v>43.4</v>
+      </c>
+      <c r="L35">
+        <v>172.7</v>
+      </c>
+      <c r="M35">
+        <v>14.3805717</v>
+      </c>
+      <c r="N35">
+        <v>158.3194283</v>
+      </c>
+      <c r="O35">
+        <v>34.83027422599999</v>
+      </c>
+      <c r="P35">
+        <v>123.489154074</v>
+      </c>
+      <c r="Q35">
+        <v>166.889154074</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1007523695216155</v>
+      </c>
+      <c r="T35">
+        <v>1.047511874131529</v>
+      </c>
+      <c r="U35">
+        <v>0.0473</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.036894</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>12.00925829673378</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.07956158112199382</v>
+      </c>
+      <c r="C36">
+        <v>648.743557837719</v>
+      </c>
+      <c r="D36">
+        <v>773.4855578377191</v>
+      </c>
+      <c r="E36">
+        <v>35.44200000000001</v>
+      </c>
+      <c r="F36">
+        <v>313.242</v>
+      </c>
+      <c r="G36">
+        <v>188.5</v>
+      </c>
+      <c r="H36">
+        <v>643.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>216.1</v>
+      </c>
+      <c r="K36">
+        <v>43.4</v>
+      </c>
+      <c r="L36">
+        <v>172.7</v>
+      </c>
+      <c r="M36">
+        <v>14.8163466</v>
+      </c>
+      <c r="N36">
+        <v>157.8836534</v>
+      </c>
+      <c r="O36">
+        <v>34.73440374799999</v>
+      </c>
+      <c r="P36">
+        <v>123.149249652</v>
+      </c>
+      <c r="Q36">
+        <v>166.549249652</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1015418501848391</v>
+      </c>
+      <c r="T36">
+        <v>1.06086068347506</v>
+      </c>
+      <c r="U36">
+        <v>0.0473</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.036894</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>11.65604481741808</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.07944405466450528</v>
+      </c>
+      <c r="C37">
+        <v>641.767170751504</v>
+      </c>
+      <c r="D37">
+        <v>775.722170751504</v>
+      </c>
+      <c r="E37">
+        <v>44.65500000000003</v>
+      </c>
+      <c r="F37">
+        <v>322.455</v>
+      </c>
+      <c r="G37">
+        <v>188.5</v>
+      </c>
+      <c r="H37">
+        <v>643.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>216.1</v>
+      </c>
+      <c r="K37">
+        <v>43.4</v>
+      </c>
+      <c r="L37">
+        <v>172.7</v>
+      </c>
+      <c r="M37">
+        <v>15.2521215</v>
+      </c>
+      <c r="N37">
+        <v>157.4478785</v>
+      </c>
+      <c r="O37">
+        <v>34.63853326999999</v>
+      </c>
+      <c r="P37">
+        <v>122.80934523</v>
+      </c>
+      <c r="Q37">
+        <v>166.20934523</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1023556225607774</v>
+      </c>
+      <c r="T37">
+        <v>1.074620225413777</v>
+      </c>
+      <c r="U37">
+        <v>0.0473</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.036894</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>11.32301496549185</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.07932652820701677</v>
+      </c>
+      <c r="C38">
+        <v>634.8037559678351</v>
+      </c>
+      <c r="D38">
+        <v>777.971755967835</v>
+      </c>
+      <c r="E38">
+        <v>53.86799999999994</v>
+      </c>
+      <c r="F38">
+        <v>331.6679999999999</v>
+      </c>
+      <c r="G38">
+        <v>188.5</v>
+      </c>
+      <c r="H38">
+        <v>643.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>216.1</v>
+      </c>
+      <c r="K38">
+        <v>43.4</v>
+      </c>
+      <c r="L38">
+        <v>172.7</v>
+      </c>
+      <c r="M38">
+        <v>15.6878964</v>
+      </c>
+      <c r="N38">
+        <v>157.0121036</v>
+      </c>
+      <c r="O38">
+        <v>34.54266279199999</v>
+      </c>
+      <c r="P38">
+        <v>122.469440808</v>
+      </c>
+      <c r="Q38">
+        <v>165.869440808</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1031948253234637</v>
+      </c>
+      <c r="T38">
+        <v>1.088809753038078</v>
+      </c>
+      <c r="U38">
+        <v>0.0473</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.036894</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>11.00848677200597</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.07920900174952825</v>
+      </c>
+      <c r="C39">
+        <v>627.8534266735297</v>
+      </c>
+      <c r="D39">
+        <v>780.2344266735297</v>
+      </c>
+      <c r="E39">
+        <v>63.08099999999996</v>
+      </c>
+      <c r="F39">
+        <v>340.881</v>
+      </c>
+      <c r="G39">
+        <v>188.5</v>
+      </c>
+      <c r="H39">
+        <v>643.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>216.1</v>
+      </c>
+      <c r="K39">
+        <v>43.4</v>
+      </c>
+      <c r="L39">
+        <v>172.7</v>
+      </c>
+      <c r="M39">
+        <v>16.1236713</v>
+      </c>
+      <c r="N39">
+        <v>156.5763287</v>
+      </c>
+      <c r="O39">
+        <v>34.44679231399999</v>
+      </c>
+      <c r="P39">
+        <v>122.129536386</v>
+      </c>
+      <c r="Q39">
+        <v>165.529536386</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1040606694436956</v>
+      </c>
+      <c r="T39">
+        <v>1.103449741856802</v>
+      </c>
+      <c r="U39">
+        <v>0.0473</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.036894</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>10.71096010249229</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.07909147529203971</v>
+      </c>
+      <c r="C40">
+        <v>620.9162973760269</v>
+      </c>
+      <c r="D40">
+        <v>782.510297376027</v>
+      </c>
+      <c r="E40">
+        <v>72.29399999999998</v>
+      </c>
+      <c r="F40">
+        <v>350.094</v>
+      </c>
+      <c r="G40">
+        <v>188.5</v>
+      </c>
+      <c r="H40">
+        <v>643.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>216.1</v>
+      </c>
+      <c r="K40">
+        <v>43.4</v>
+      </c>
+      <c r="L40">
+        <v>172.7</v>
+      </c>
+      <c r="M40">
+        <v>16.5594462</v>
+      </c>
+      <c r="N40">
+        <v>156.1405538</v>
+      </c>
+      <c r="O40">
+        <v>34.35092183599999</v>
+      </c>
+      <c r="P40">
+        <v>121.789631964</v>
+      </c>
+      <c r="Q40">
+        <v>165.189631964</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1049544440194189</v>
+      </c>
+      <c r="T40">
+        <v>1.118561988379356</v>
+      </c>
+      <c r="U40">
+        <v>0.0473</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.036894</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>10.42909273137407</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08012990883455118</v>
+      </c>
+      <c r="C41">
+        <v>592.0423553834189</v>
+      </c>
+      <c r="D41">
+        <v>762.8493553834189</v>
+      </c>
+      <c r="E41">
+        <v>81.50700000000001</v>
+      </c>
+      <c r="F41">
+        <v>359.307</v>
+      </c>
+      <c r="G41">
+        <v>188.5</v>
+      </c>
+      <c r="H41">
+        <v>643.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>216.1</v>
+      </c>
+      <c r="K41">
+        <v>43.4</v>
+      </c>
+      <c r="L41">
+        <v>172.7</v>
+      </c>
+      <c r="M41">
+        <v>18.3605877</v>
+      </c>
+      <c r="N41">
+        <v>154.3394123</v>
+      </c>
+      <c r="O41">
+        <v>33.95467070599999</v>
+      </c>
+      <c r="P41">
+        <v>120.384741594</v>
+      </c>
+      <c r="Q41">
+        <v>163.784741594</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1058775226795921</v>
+      </c>
+      <c r="T41">
+        <v>1.134169718394453</v>
+      </c>
+      <c r="U41">
+        <v>0.0511</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.039858</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>9.40601699802888</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08004202237706266</v>
+      </c>
+      <c r="C42">
+        <v>584.4549819550035</v>
+      </c>
+      <c r="D42">
+        <v>764.4749819550035</v>
+      </c>
+      <c r="E42">
+        <v>90.71999999999997</v>
+      </c>
+      <c r="F42">
+        <v>368.52</v>
+      </c>
+      <c r="G42">
+        <v>188.5</v>
+      </c>
+      <c r="H42">
+        <v>643.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>216.1</v>
+      </c>
+      <c r="K42">
+        <v>43.4</v>
+      </c>
+      <c r="L42">
+        <v>172.7</v>
+      </c>
+      <c r="M42">
+        <v>18.831372</v>
+      </c>
+      <c r="N42">
+        <v>153.868628</v>
+      </c>
+      <c r="O42">
+        <v>33.85109816</v>
+      </c>
+      <c r="P42">
+        <v>120.01752984</v>
+      </c>
+      <c r="Q42">
+        <v>163.41752984</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1068313706284378</v>
+      </c>
+      <c r="T42">
+        <v>1.150297706076719</v>
+      </c>
+      <c r="U42">
+        <v>0.0511</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.039858</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>9.170866573078159</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.07995413591957412</v>
+      </c>
+      <c r="C43">
+        <v>576.8745517198979</v>
+      </c>
+      <c r="D43">
+        <v>766.1075517198979</v>
+      </c>
+      <c r="E43">
+        <v>99.93299999999999</v>
+      </c>
+      <c r="F43">
+        <v>377.733</v>
+      </c>
+      <c r="G43">
+        <v>188.5</v>
+      </c>
+      <c r="H43">
+        <v>643.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>216.1</v>
+      </c>
+      <c r="K43">
+        <v>43.4</v>
+      </c>
+      <c r="L43">
+        <v>172.7</v>
+      </c>
+      <c r="M43">
+        <v>19.3021563</v>
+      </c>
+      <c r="N43">
+        <v>153.3978437</v>
+      </c>
+      <c r="O43">
+        <v>33.74752561399999</v>
+      </c>
+      <c r="P43">
+        <v>119.650318086</v>
+      </c>
+      <c r="Q43">
+        <v>163.050318086</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1078175524060578</v>
+      </c>
+      <c r="T43">
+        <v>1.166972405205842</v>
+      </c>
+      <c r="U43">
+        <v>0.0511</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.039858</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>8.947186900564056</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.07986624946208561</v>
+      </c>
+      <c r="C44">
+        <v>569.301109255777</v>
+      </c>
+      <c r="D44">
+        <v>767.747109255777</v>
+      </c>
+      <c r="E44">
+        <v>109.146</v>
+      </c>
+      <c r="F44">
+        <v>386.946</v>
+      </c>
+      <c r="G44">
+        <v>188.5</v>
+      </c>
+      <c r="H44">
+        <v>643.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>216.1</v>
+      </c>
+      <c r="K44">
+        <v>43.4</v>
+      </c>
+      <c r="L44">
+        <v>172.7</v>
+      </c>
+      <c r="M44">
+        <v>19.7729406</v>
+      </c>
+      <c r="N44">
+        <v>152.9270594</v>
+      </c>
+      <c r="O44">
+        <v>33.64395306799999</v>
+      </c>
+      <c r="P44">
+        <v>119.283106332</v>
+      </c>
+      <c r="Q44">
+        <v>162.683106332</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1088377404518717</v>
+      </c>
+      <c r="T44">
+        <v>1.184222093960107</v>
+      </c>
+      <c r="U44">
+        <v>0.0511</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.039858</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>8.734158641026818</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.07977836300459706</v>
+      </c>
+      <c r="C45">
+        <v>561.7346995227427</v>
+      </c>
+      <c r="D45">
+        <v>769.3936995227427</v>
+      </c>
+      <c r="E45">
+        <v>118.359</v>
+      </c>
+      <c r="F45">
+        <v>396.159</v>
+      </c>
+      <c r="G45">
+        <v>188.5</v>
+      </c>
+      <c r="H45">
+        <v>643.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>216.1</v>
+      </c>
+      <c r="K45">
+        <v>43.4</v>
+      </c>
+      <c r="L45">
+        <v>172.7</v>
+      </c>
+      <c r="M45">
+        <v>20.2437249</v>
+      </c>
+      <c r="N45">
+        <v>152.4562751</v>
+      </c>
+      <c r="O45">
+        <v>33.54038052199999</v>
+      </c>
+      <c r="P45">
+        <v>118.915894578</v>
+      </c>
+      <c r="Q45">
+        <v>162.315894578</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1098937245694685</v>
+      </c>
+      <c r="T45">
+        <v>1.202077034951363</v>
+      </c>
+      <c r="U45">
+        <v>0.0511</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.039858</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>8.531038672630846</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.07969047654710855</v>
+      </c>
+      <c r="C46">
+        <v>554.1753678674278</v>
+      </c>
+      <c r="D46">
+        <v>771.0473678674277</v>
+      </c>
+      <c r="E46">
+        <v>127.5719999999999</v>
+      </c>
+      <c r="F46">
+        <v>405.372</v>
+      </c>
+      <c r="G46">
+        <v>188.5</v>
+      </c>
+      <c r="H46">
+        <v>643.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>216.1</v>
+      </c>
+      <c r="K46">
+        <v>43.4</v>
+      </c>
+      <c r="L46">
+        <v>172.7</v>
+      </c>
+      <c r="M46">
+        <v>20.7145092</v>
+      </c>
+      <c r="N46">
+        <v>151.9854908</v>
+      </c>
+      <c r="O46">
+        <v>33.43680797599999</v>
+      </c>
+      <c r="P46">
+        <v>118.548682824</v>
+      </c>
+      <c r="Q46">
+        <v>161.948682824</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.110987422405551</v>
+      </c>
+      <c r="T46">
+        <v>1.220569652406594</v>
+      </c>
+      <c r="U46">
+        <v>0.0511</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.039858</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.337151430071053</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.07960259008962002</v>
+      </c>
+      <c r="C47">
+        <v>546.6231600271628</v>
+      </c>
+      <c r="D47">
+        <v>772.7081600271628</v>
+      </c>
+      <c r="E47">
+        <v>136.785</v>
+      </c>
+      <c r="F47">
+        <v>414.585</v>
+      </c>
+      <c r="G47">
+        <v>188.5</v>
+      </c>
+      <c r="H47">
+        <v>643.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>216.1</v>
+      </c>
+      <c r="K47">
+        <v>43.4</v>
+      </c>
+      <c r="L47">
+        <v>172.7</v>
+      </c>
+      <c r="M47">
+        <v>21.1852935</v>
+      </c>
+      <c r="N47">
+        <v>151.5147065</v>
+      </c>
+      <c r="O47">
+        <v>33.33323542999999</v>
+      </c>
+      <c r="P47">
+        <v>118.18147107</v>
+      </c>
+      <c r="Q47">
+        <v>161.58147107</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1121208910720364</v>
+      </c>
+      <c r="T47">
+        <v>1.239734728678378</v>
+      </c>
+      <c r="U47">
+        <v>0.0511</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.039858</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>8.151881398291696</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.07951470363213148</v>
+      </c>
+      <c r="C48">
+        <v>539.0781221341909</v>
+      </c>
+      <c r="D48">
+        <v>774.376122134191</v>
+      </c>
+      <c r="E48">
+        <v>145.998</v>
+      </c>
+      <c r="F48">
+        <v>423.798</v>
+      </c>
+      <c r="G48">
+        <v>188.5</v>
+      </c>
+      <c r="H48">
+        <v>643.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>216.1</v>
+      </c>
+      <c r="K48">
+        <v>43.4</v>
+      </c>
+      <c r="L48">
+        <v>172.7</v>
+      </c>
+      <c r="M48">
+        <v>21.6560778</v>
+      </c>
+      <c r="N48">
+        <v>151.0439222</v>
+      </c>
+      <c r="O48">
+        <v>33.22966288399999</v>
+      </c>
+      <c r="P48">
+        <v>117.814259316</v>
+      </c>
+      <c r="Q48">
+        <v>161.214259316</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1132963400595027</v>
+      </c>
+      <c r="T48">
+        <v>1.259609622589857</v>
+      </c>
+      <c r="U48">
+        <v>0.0511</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.039858</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>7.974666585285356</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.07942681717464296</v>
+      </c>
+      <c r="C49">
+        <v>531.5403007199391</v>
+      </c>
+      <c r="D49">
+        <v>776.0513007199391</v>
+      </c>
+      <c r="E49">
+        <v>155.211</v>
+      </c>
+      <c r="F49">
+        <v>433.011</v>
+      </c>
+      <c r="G49">
+        <v>188.5</v>
+      </c>
+      <c r="H49">
+        <v>643.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>216.1</v>
+      </c>
+      <c r="K49">
+        <v>43.4</v>
+      </c>
+      <c r="L49">
+        <v>172.7</v>
+      </c>
+      <c r="M49">
+        <v>22.1268621</v>
+      </c>
+      <c r="N49">
+        <v>150.5731379</v>
+      </c>
+      <c r="O49">
+        <v>33.12609033799999</v>
+      </c>
+      <c r="P49">
+        <v>117.447047562</v>
+      </c>
+      <c r="Q49">
+        <v>160.847047562</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1145161456125339</v>
+      </c>
+      <c r="T49">
+        <v>1.280234512497997</v>
+      </c>
+      <c r="U49">
+        <v>0.0511</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.039858</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>7.804992828151624</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08005029071715443</v>
+      </c>
+      <c r="C50">
+        <v>510.5977481466459</v>
+      </c>
+      <c r="D50">
+        <v>764.3217481466459</v>
+      </c>
+      <c r="E50">
+        <v>164.424</v>
+      </c>
+      <c r="F50">
+        <v>442.224</v>
+      </c>
+      <c r="G50">
+        <v>188.5</v>
+      </c>
+      <c r="H50">
+        <v>643.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>216.1</v>
+      </c>
+      <c r="K50">
+        <v>43.4</v>
+      </c>
+      <c r="L50">
+        <v>172.7</v>
+      </c>
+      <c r="M50">
+        <v>23.437872</v>
+      </c>
+      <c r="N50">
+        <v>149.262128</v>
+      </c>
+      <c r="O50">
+        <v>32.83766815999999</v>
+      </c>
+      <c r="P50">
+        <v>116.42445984</v>
+      </c>
+      <c r="Q50">
+        <v>159.82445984</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1157828667637585</v>
+      </c>
+      <c r="T50">
+        <v>1.301652667402603</v>
+      </c>
+      <c r="U50">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>7.36841638182852</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.07997722425966591</v>
+      </c>
+      <c r="C51">
+        <v>502.7409901839026</v>
+      </c>
+      <c r="D51">
+        <v>765.6779901839026</v>
+      </c>
+      <c r="E51">
+        <v>173.6369999999999</v>
+      </c>
+      <c r="F51">
+        <v>451.437</v>
+      </c>
+      <c r="G51">
+        <v>188.5</v>
+      </c>
+      <c r="H51">
+        <v>643.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>216.1</v>
+      </c>
+      <c r="K51">
+        <v>43.4</v>
+      </c>
+      <c r="L51">
+        <v>172.7</v>
+      </c>
+      <c r="M51">
+        <v>23.926161</v>
+      </c>
+      <c r="N51">
+        <v>148.773839</v>
+      </c>
+      <c r="O51">
+        <v>32.73024457999999</v>
+      </c>
+      <c r="P51">
+        <v>116.04359442</v>
+      </c>
+      <c r="Q51">
+        <v>159.44359442</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1170992632542469</v>
+      </c>
+      <c r="T51">
+        <v>1.323910749950527</v>
+      </c>
+      <c r="U51">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>7.218040537301407</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.07990415780217737</v>
+      </c>
+      <c r="C52">
+        <v>494.8890539134877</v>
+      </c>
+      <c r="D52">
+        <v>767.0390539134877</v>
+      </c>
+      <c r="E52">
+        <v>182.85</v>
+      </c>
+      <c r="F52">
+        <v>460.65</v>
+      </c>
+      <c r="G52">
+        <v>188.5</v>
+      </c>
+      <c r="H52">
+        <v>643.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>216.1</v>
+      </c>
+      <c r="K52">
+        <v>43.4</v>
+      </c>
+      <c r="L52">
+        <v>172.7</v>
+      </c>
+      <c r="M52">
+        <v>24.41445</v>
+      </c>
+      <c r="N52">
+        <v>148.28555</v>
+      </c>
+      <c r="O52">
+        <v>32.62282099999999</v>
+      </c>
+      <c r="P52">
+        <v>115.662729</v>
+      </c>
+      <c r="Q52">
+        <v>159.062729</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1184683156043547</v>
+      </c>
+      <c r="T52">
+        <v>1.347059155800368</v>
+      </c>
+      <c r="U52">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>7.07367972655538</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.07983109134468885</v>
+      </c>
+      <c r="C53">
+        <v>487.0419650942064</v>
+      </c>
+      <c r="D53">
+        <v>768.4049650942064</v>
+      </c>
+      <c r="E53">
+        <v>192.063</v>
+      </c>
+      <c r="F53">
+        <v>469.863</v>
+      </c>
+      <c r="G53">
+        <v>188.5</v>
+      </c>
+      <c r="H53">
+        <v>643.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>216.1</v>
+      </c>
+      <c r="K53">
+        <v>43.4</v>
+      </c>
+      <c r="L53">
+        <v>172.7</v>
+      </c>
+      <c r="M53">
+        <v>24.902739</v>
+      </c>
+      <c r="N53">
+        <v>147.797261</v>
+      </c>
+      <c r="O53">
+        <v>32.51539741999999</v>
+      </c>
+      <c r="P53">
+        <v>115.28186358</v>
+      </c>
+      <c r="Q53">
+        <v>158.68186358</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1198932476422221</v>
+      </c>
+      <c r="T53">
+        <v>1.37115239454204</v>
+      </c>
+      <c r="U53">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>6.934980124073901</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.07975802488720032</v>
+      </c>
+      <c r="C54">
+        <v>479.199749668674</v>
+      </c>
+      <c r="D54">
+        <v>769.7757496686739</v>
+      </c>
+      <c r="E54">
+        <v>201.276</v>
+      </c>
+      <c r="F54">
+        <v>479.076</v>
+      </c>
+      <c r="G54">
+        <v>188.5</v>
+      </c>
+      <c r="H54">
+        <v>643.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>216.1</v>
+      </c>
+      <c r="K54">
+        <v>43.4</v>
+      </c>
+      <c r="L54">
+        <v>172.7</v>
+      </c>
+      <c r="M54">
+        <v>25.391028</v>
+      </c>
+      <c r="N54">
+        <v>147.308972</v>
+      </c>
+      <c r="O54">
+        <v>32.40797383999999</v>
+      </c>
+      <c r="P54">
+        <v>114.90099816</v>
+      </c>
+      <c r="Q54">
+        <v>158.30099816</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.121377551848334</v>
+      </c>
+      <c r="T54">
+        <v>1.396249518231281</v>
+      </c>
+      <c r="U54">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.22</v>
+      </c>
+      <c r="W54">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>6.801615121687864</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.07968495842971179</v>
+      </c>
+      <c r="C55">
+        <v>471.362433764955</v>
+      </c>
+      <c r="D55">
+        <v>771.151433764955</v>
+      </c>
+      <c r="E55">
+        <v>210.489</v>
+      </c>
+      <c r="F55">
+        <v>488.289</v>
+      </c>
+      <c r="G55">
+        <v>188.5</v>
+      </c>
+      <c r="H55">
+        <v>643.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>216.1</v>
+      </c>
+      <c r="K55">
+        <v>43.4</v>
+      </c>
+      <c r="L55">
+        <v>172.7</v>
+      </c>
+      <c r="M55">
+        <v>25.879317</v>
+      </c>
+      <c r="N55">
+        <v>146.820683</v>
+      </c>
+      <c r="O55">
+        <v>32.30055025999999</v>
+      </c>
+      <c r="P55">
+        <v>114.52013274</v>
+      </c>
+      <c r="Q55">
+        <v>157.92013274</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.122925017935557</v>
+      </c>
+      <c r="T55">
+        <v>1.422414604630702</v>
+      </c>
+      <c r="U55">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.22</v>
+      </c>
+      <c r="W55">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>6.673282760901301</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.07961189197222326</v>
+      </c>
+      <c r="C56">
+        <v>463.5300436982253</v>
+      </c>
+      <c r="D56">
+        <v>772.5320436982253</v>
+      </c>
+      <c r="E56">
+        <v>219.702</v>
+      </c>
+      <c r="F56">
+        <v>497.502</v>
+      </c>
+      <c r="G56">
+        <v>188.5</v>
+      </c>
+      <c r="H56">
+        <v>643.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>216.1</v>
+      </c>
+      <c r="K56">
+        <v>43.4</v>
+      </c>
+      <c r="L56">
+        <v>172.7</v>
+      </c>
+      <c r="M56">
+        <v>26.367606</v>
+      </c>
+      <c r="N56">
+        <v>146.332394</v>
+      </c>
+      <c r="O56">
+        <v>32.19312667999999</v>
+      </c>
+      <c r="P56">
+        <v>114.13926732</v>
+      </c>
+      <c r="Q56">
+        <v>157.53926732</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1245397651570071</v>
+      </c>
+      <c r="T56">
+        <v>1.449717303482272</v>
+      </c>
+      <c r="U56">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.22</v>
+      </c>
+      <c r="W56">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>6.54970345051424</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.07953882551473473</v>
+      </c>
+      <c r="C57">
+        <v>455.702605972449</v>
+      </c>
+      <c r="D57">
+        <v>773.917605972449</v>
+      </c>
+      <c r="E57">
+        <v>228.915</v>
+      </c>
+      <c r="F57">
+        <v>506.715</v>
+      </c>
+      <c r="G57">
+        <v>188.5</v>
+      </c>
+      <c r="H57">
+        <v>643.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>216.1</v>
+      </c>
+      <c r="K57">
+        <v>43.4</v>
+      </c>
+      <c r="L57">
+        <v>172.7</v>
+      </c>
+      <c r="M57">
+        <v>26.855895</v>
+      </c>
+      <c r="N57">
+        <v>145.844105</v>
+      </c>
+      <c r="O57">
+        <v>32.08570309999999</v>
+      </c>
+      <c r="P57">
+        <v>113.7584019</v>
+      </c>
+      <c r="Q57">
+        <v>157.1584019</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1262262789216327</v>
+      </c>
+      <c r="T57">
+        <v>1.478233455616135</v>
+      </c>
+      <c r="U57">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.22</v>
+      </c>
+      <c r="W57">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>6.430617933232162</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.0794657590572462</v>
+      </c>
+      <c r="C58">
+        <v>447.8801472820754</v>
+      </c>
+      <c r="D58">
+        <v>775.3081472820754</v>
+      </c>
+      <c r="E58">
+        <v>238.128</v>
+      </c>
+      <c r="F58">
+        <v>515.928</v>
+      </c>
+      <c r="G58">
+        <v>188.5</v>
+      </c>
+      <c r="H58">
+        <v>643.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>216.1</v>
+      </c>
+      <c r="K58">
+        <v>43.4</v>
+      </c>
+      <c r="L58">
+        <v>172.7</v>
+      </c>
+      <c r="M58">
+        <v>27.344184</v>
+      </c>
+      <c r="N58">
+        <v>145.355816</v>
+      </c>
+      <c r="O58">
+        <v>31.97827951999999</v>
+      </c>
+      <c r="P58">
+        <v>113.37753648</v>
+      </c>
+      <c r="Q58">
+        <v>156.77753648</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1279894524028323</v>
+      </c>
+      <c r="T58">
+        <v>1.508045796483354</v>
+      </c>
+      <c r="U58">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.22</v>
+      </c>
+      <c r="W58">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>6.315785470138731</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08028189259975767</v>
+      </c>
+      <c r="C59">
+        <v>423.4133836487589</v>
+      </c>
+      <c r="D59">
+        <v>760.054383648759</v>
+      </c>
+      <c r="E59">
+        <v>247.3410000000001</v>
+      </c>
+      <c r="F59">
+        <v>525.1410000000001</v>
+      </c>
+      <c r="G59">
+        <v>188.5</v>
+      </c>
+      <c r="H59">
+        <v>643.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>216.1</v>
+      </c>
+      <c r="K59">
+        <v>43.4</v>
+      </c>
+      <c r="L59">
+        <v>172.7</v>
+      </c>
+      <c r="M59">
+        <v>28.882755</v>
+      </c>
+      <c r="N59">
+        <v>143.817245</v>
+      </c>
+      <c r="O59">
+        <v>31.63979389999999</v>
+      </c>
+      <c r="P59">
+        <v>112.1774511</v>
+      </c>
+      <c r="Q59">
+        <v>155.5774511</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1298346339529248</v>
+      </c>
+      <c r="T59">
+        <v>1.539244757856026</v>
+      </c>
+      <c r="U59">
+        <v>0.055</v>
+      </c>
+      <c r="V59">
+        <v>0.22</v>
+      </c>
+      <c r="W59">
+        <v>0.0429</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>5.979346499321133</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.08022442614226914</v>
+      </c>
+      <c r="C60">
+        <v>415.254776841242</v>
+      </c>
+      <c r="D60">
+        <v>761.1087768412419</v>
+      </c>
+      <c r="E60">
+        <v>256.5539999999999</v>
+      </c>
+      <c r="F60">
+        <v>534.3539999999999</v>
+      </c>
+      <c r="G60">
+        <v>188.5</v>
+      </c>
+      <c r="H60">
+        <v>643.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>216.1</v>
+      </c>
+      <c r="K60">
+        <v>43.4</v>
+      </c>
+      <c r="L60">
+        <v>172.7</v>
+      </c>
+      <c r="M60">
+        <v>29.38947</v>
+      </c>
+      <c r="N60">
+        <v>143.31053</v>
+      </c>
+      <c r="O60">
+        <v>31.5283166</v>
+      </c>
+      <c r="P60">
+        <v>111.7822134</v>
+      </c>
+      <c r="Q60">
+        <v>155.1822134</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.131767681291117</v>
+      </c>
+      <c r="T60">
+        <v>1.571929384055967</v>
+      </c>
+      <c r="U60">
+        <v>0.055</v>
+      </c>
+      <c r="V60">
+        <v>0.22</v>
+      </c>
+      <c r="W60">
+        <v>0.0429</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>5.876254318298357</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.08016695968478062</v>
+      </c>
+      <c r="C61">
+        <v>407.0990995331146</v>
+      </c>
+      <c r="D61">
+        <v>762.1660995331144</v>
+      </c>
+      <c r="E61">
+        <v>265.7669999999999</v>
+      </c>
+      <c r="F61">
+        <v>543.5669999999999</v>
+      </c>
+      <c r="G61">
+        <v>188.5</v>
+      </c>
+      <c r="H61">
+        <v>643.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>216.1</v>
+      </c>
+      <c r="K61">
+        <v>43.4</v>
+      </c>
+      <c r="L61">
+        <v>172.7</v>
+      </c>
+      <c r="M61">
+        <v>29.896185</v>
+      </c>
+      <c r="N61">
+        <v>142.803815</v>
+      </c>
+      <c r="O61">
+        <v>31.41683929999999</v>
+      </c>
+      <c r="P61">
+        <v>111.3869757</v>
+      </c>
+      <c r="Q61">
+        <v>154.7869757</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1337950236214161</v>
+      </c>
+      <c r="T61">
+        <v>1.606208382265662</v>
+      </c>
+      <c r="U61">
+        <v>0.055</v>
+      </c>
+      <c r="V61">
+        <v>0.22</v>
+      </c>
+      <c r="W61">
+        <v>0.0429</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>5.776656787479741</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08010949322729209</v>
+      </c>
+      <c r="C62">
+        <v>398.946363950231</v>
+      </c>
+      <c r="D62">
+        <v>763.226363950231</v>
+      </c>
+      <c r="E62">
+        <v>274.98</v>
+      </c>
+      <c r="F62">
+        <v>552.78</v>
+      </c>
+      <c r="G62">
+        <v>188.5</v>
+      </c>
+      <c r="H62">
+        <v>643.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>216.1</v>
+      </c>
+      <c r="K62">
+        <v>43.4</v>
+      </c>
+      <c r="L62">
+        <v>172.7</v>
+      </c>
+      <c r="M62">
+        <v>30.4029</v>
+      </c>
+      <c r="N62">
+        <v>142.2971</v>
+      </c>
+      <c r="O62">
+        <v>31.305362</v>
+      </c>
+      <c r="P62">
+        <v>110.991738</v>
+      </c>
+      <c r="Q62">
+        <v>154.391738</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1359237330682302</v>
+      </c>
+      <c r="T62">
+        <v>1.642201330385842</v>
+      </c>
+      <c r="U62">
+        <v>0.055</v>
+      </c>
+      <c r="V62">
+        <v>0.22</v>
+      </c>
+      <c r="W62">
+        <v>0.0429</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.680379174355078</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.08005202676980355</v>
+      </c>
+      <c r="C63">
+        <v>390.7965823865718</v>
+      </c>
+      <c r="D63">
+        <v>764.2895823865717</v>
+      </c>
+      <c r="E63">
+        <v>284.1929999999999</v>
+      </c>
+      <c r="F63">
+        <v>561.9929999999999</v>
+      </c>
+      <c r="G63">
+        <v>188.5</v>
+      </c>
+      <c r="H63">
+        <v>643.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>216.1</v>
+      </c>
+      <c r="K63">
+        <v>43.4</v>
+      </c>
+      <c r="L63">
+        <v>172.7</v>
+      </c>
+      <c r="M63">
+        <v>30.909615</v>
+      </c>
+      <c r="N63">
+        <v>141.790385</v>
+      </c>
+      <c r="O63">
+        <v>31.19388469999999</v>
+      </c>
+      <c r="P63">
+        <v>110.5965003</v>
+      </c>
+      <c r="Q63">
+        <v>153.9965003</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1381616071020604</v>
+      </c>
+      <c r="T63">
+        <v>1.680040070717313</v>
+      </c>
+      <c r="U63">
+        <v>0.055</v>
+      </c>
+      <c r="V63">
+        <v>0.22</v>
+      </c>
+      <c r="W63">
+        <v>0.0429</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.587258204283684</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.07999456031231503</v>
+      </c>
+      <c r="C64">
+        <v>382.6497672047166</v>
+      </c>
+      <c r="D64">
+        <v>765.3557672047166</v>
+      </c>
+      <c r="E64">
+        <v>293.406</v>
+      </c>
+      <c r="F64">
+        <v>571.206</v>
+      </c>
+      <c r="G64">
+        <v>188.5</v>
+      </c>
+      <c r="H64">
+        <v>643.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>216.1</v>
+      </c>
+      <c r="K64">
+        <v>43.4</v>
+      </c>
+      <c r="L64">
+        <v>172.7</v>
+      </c>
+      <c r="M64">
+        <v>31.41633</v>
+      </c>
+      <c r="N64">
+        <v>141.28367</v>
+      </c>
+      <c r="O64">
+        <v>31.08240739999999</v>
+      </c>
+      <c r="P64">
+        <v>110.2012626</v>
+      </c>
+      <c r="Q64">
+        <v>153.6012626</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1405172639797764</v>
+      </c>
+      <c r="T64">
+        <v>1.719870323697809</v>
+      </c>
+      <c r="U64">
+        <v>0.055</v>
+      </c>
+      <c r="V64">
+        <v>0.22</v>
+      </c>
+      <c r="W64">
+        <v>0.0429</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.497141136472655</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.0799370938548265</v>
+      </c>
+      <c r="C65">
+        <v>374.5059308363255</v>
+      </c>
+      <c r="D65">
+        <v>766.4249308363255</v>
+      </c>
+      <c r="E65">
+        <v>302.619</v>
+      </c>
+      <c r="F65">
+        <v>580.419</v>
+      </c>
+      <c r="G65">
+        <v>188.5</v>
+      </c>
+      <c r="H65">
+        <v>643.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>216.1</v>
+      </c>
+      <c r="K65">
+        <v>43.4</v>
+      </c>
+      <c r="L65">
+        <v>172.7</v>
+      </c>
+      <c r="M65">
+        <v>31.923045</v>
+      </c>
+      <c r="N65">
+        <v>140.776955</v>
+      </c>
+      <c r="O65">
+        <v>30.97093009999999</v>
+      </c>
+      <c r="P65">
+        <v>109.8060249</v>
+      </c>
+      <c r="Q65">
+        <v>153.2060249</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1430002536616932</v>
+      </c>
+      <c r="T65">
+        <v>1.761853563325899</v>
+      </c>
+      <c r="U65">
+        <v>0.055</v>
+      </c>
+      <c r="V65">
+        <v>0.22</v>
+      </c>
+      <c r="W65">
+        <v>0.0429</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.409884927957217</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.07987962739733798</v>
+      </c>
+      <c r="C66">
+        <v>366.3650857826216</v>
+      </c>
+      <c r="D66">
+        <v>767.4970857826215</v>
+      </c>
+      <c r="E66">
+        <v>311.8319999999999</v>
+      </c>
+      <c r="F66">
+        <v>589.6319999999999</v>
+      </c>
+      <c r="G66">
+        <v>188.5</v>
+      </c>
+      <c r="H66">
+        <v>643.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>216.1</v>
+      </c>
+      <c r="K66">
+        <v>43.4</v>
+      </c>
+      <c r="L66">
+        <v>172.7</v>
+      </c>
+      <c r="M66">
+        <v>32.42975999999999</v>
+      </c>
+      <c r="N66">
+        <v>140.27024</v>
+      </c>
+      <c r="O66">
+        <v>30.8594528</v>
+      </c>
+      <c r="P66">
+        <v>109.4107872</v>
+      </c>
+      <c r="Q66">
+        <v>152.8107872</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1456211872148277</v>
+      </c>
+      <c r="T66">
+        <v>1.80616920515555</v>
+      </c>
+      <c r="U66">
+        <v>0.055</v>
+      </c>
+      <c r="V66">
+        <v>0.22</v>
+      </c>
+      <c r="W66">
+        <v>0.0429</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.325355475957886</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.07982216093984945</v>
+      </c>
+      <c r="C67">
+        <v>358.2272446148772</v>
+      </c>
+      <c r="D67">
+        <v>768.5722446148773</v>
+      </c>
+      <c r="E67">
+        <v>321.045</v>
+      </c>
+      <c r="F67">
+        <v>598.845</v>
+      </c>
+      <c r="G67">
+        <v>188.5</v>
+      </c>
+      <c r="H67">
+        <v>643.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>216.1</v>
+      </c>
+      <c r="K67">
+        <v>43.4</v>
+      </c>
+      <c r="L67">
+        <v>172.7</v>
+      </c>
+      <c r="M67">
+        <v>32.936475</v>
+      </c>
+      <c r="N67">
+        <v>139.763525</v>
+      </c>
+      <c r="O67">
+        <v>30.74797549999999</v>
+      </c>
+      <c r="P67">
+        <v>109.0155495</v>
+      </c>
+      <c r="Q67">
+        <v>152.4155495</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1483918883995698</v>
+      </c>
+      <c r="T67">
+        <v>1.853017169375466</v>
+      </c>
+      <c r="U67">
+        <v>0.055</v>
+      </c>
+      <c r="V67">
+        <v>0.22</v>
+      </c>
+      <c r="W67">
+        <v>0.0429</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.243426930173918</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.07976469448236093</v>
+      </c>
+      <c r="C68">
+        <v>350.0924199749069</v>
+      </c>
+      <c r="D68">
+        <v>769.6504199749069</v>
+      </c>
+      <c r="E68">
+        <v>330.258</v>
+      </c>
+      <c r="F68">
+        <v>608.058</v>
+      </c>
+      <c r="G68">
+        <v>188.5</v>
+      </c>
+      <c r="H68">
+        <v>643.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>216.1</v>
+      </c>
+      <c r="K68">
+        <v>43.4</v>
+      </c>
+      <c r="L68">
+        <v>172.7</v>
+      </c>
+      <c r="M68">
+        <v>33.44319</v>
+      </c>
+      <c r="N68">
+        <v>139.25681</v>
+      </c>
+      <c r="O68">
+        <v>30.63649819999999</v>
+      </c>
+      <c r="P68">
+        <v>108.6203118</v>
+      </c>
+      <c r="Q68">
+        <v>152.0203118</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1513255720069439</v>
+      </c>
+      <c r="T68">
+        <v>1.902620896196555</v>
+      </c>
+      <c r="U68">
+        <v>0.055</v>
+      </c>
+      <c r="V68">
+        <v>0.22</v>
+      </c>
+      <c r="W68">
+        <v>0.0429</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>5.163981067595524</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.07970722802487239</v>
+      </c>
+      <c r="C69">
+        <v>341.9606245755615</v>
+      </c>
+      <c r="D69">
+        <v>770.7316245755615</v>
+      </c>
+      <c r="E69">
+        <v>339.4709999999999</v>
+      </c>
+      <c r="F69">
+        <v>617.271</v>
+      </c>
+      <c r="G69">
+        <v>188.5</v>
+      </c>
+      <c r="H69">
+        <v>643.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>216.1</v>
+      </c>
+      <c r="K69">
+        <v>43.4</v>
+      </c>
+      <c r="L69">
+        <v>172.7</v>
+      </c>
+      <c r="M69">
+        <v>33.949905</v>
+      </c>
+      <c r="N69">
+        <v>138.750095</v>
+      </c>
+      <c r="O69">
+        <v>30.52502089999999</v>
+      </c>
+      <c r="P69">
+        <v>108.2250741</v>
+      </c>
+      <c r="Q69">
+        <v>151.6250741</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1544370546208254</v>
+      </c>
+      <c r="T69">
+        <v>1.955230909491648</v>
+      </c>
+      <c r="U69">
+        <v>0.055</v>
+      </c>
+      <c r="V69">
+        <v>0.22</v>
+      </c>
+      <c r="W69">
+        <v>0.0429</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.086906723303055</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.07964976156738386</v>
+      </c>
+      <c r="C70">
+        <v>333.8318712012284</v>
+      </c>
+      <c r="D70">
+        <v>771.8158712012284</v>
+      </c>
+      <c r="E70">
+        <v>348.684</v>
+      </c>
+      <c r="F70">
+        <v>626.484</v>
+      </c>
+      <c r="G70">
+        <v>188.5</v>
+      </c>
+      <c r="H70">
+        <v>643.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>216.1</v>
+      </c>
+      <c r="K70">
+        <v>43.4</v>
+      </c>
+      <c r="L70">
+        <v>172.7</v>
+      </c>
+      <c r="M70">
+        <v>34.45662</v>
+      </c>
+      <c r="N70">
+        <v>138.24338</v>
+      </c>
+      <c r="O70">
+        <v>30.4135436</v>
+      </c>
+      <c r="P70">
+        <v>107.8298364</v>
+      </c>
+      <c r="Q70">
+        <v>151.2298364</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1577430048980746</v>
+      </c>
+      <c r="T70">
+        <v>2.011129048617685</v>
+      </c>
+      <c r="U70">
+        <v>0.055</v>
+      </c>
+      <c r="V70">
+        <v>0.22</v>
+      </c>
+      <c r="W70">
+        <v>0.0429</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.012099271489775</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.07959229510989534</v>
+      </c>
+      <c r="C71">
+        <v>325.7061727083357</v>
+      </c>
+      <c r="D71">
+        <v>772.9031727083357</v>
+      </c>
+      <c r="E71">
+        <v>357.897</v>
+      </c>
+      <c r="F71">
+        <v>635.697</v>
+      </c>
+      <c r="G71">
+        <v>188.5</v>
+      </c>
+      <c r="H71">
+        <v>643.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>216.1</v>
+      </c>
+      <c r="K71">
+        <v>43.4</v>
+      </c>
+      <c r="L71">
+        <v>172.7</v>
+      </c>
+      <c r="M71">
+        <v>34.963335</v>
+      </c>
+      <c r="N71">
+        <v>137.736665</v>
+      </c>
+      <c r="O71">
+        <v>30.30206629999999</v>
+      </c>
+      <c r="P71">
+        <v>107.4345987</v>
+      </c>
+      <c r="Q71">
+        <v>150.8345987</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.161262242289985</v>
+      </c>
+      <c r="T71">
+        <v>2.07063351930024</v>
+      </c>
+      <c r="U71">
+        <v>0.055</v>
+      </c>
+      <c r="V71">
+        <v>0.22</v>
+      </c>
+      <c r="W71">
+        <v>0.0429</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>4.939460151613111</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.0795348286524068</v>
+      </c>
+      <c r="C72">
+        <v>317.58354202586</v>
+      </c>
+      <c r="D72">
+        <v>773.9935420258601</v>
+      </c>
+      <c r="E72">
+        <v>367.1100000000001</v>
+      </c>
+      <c r="F72">
+        <v>644.9100000000001</v>
+      </c>
+      <c r="G72">
+        <v>188.5</v>
+      </c>
+      <c r="H72">
+        <v>643.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>216.1</v>
+      </c>
+      <c r="K72">
+        <v>43.4</v>
+      </c>
+      <c r="L72">
+        <v>172.7</v>
+      </c>
+      <c r="M72">
+        <v>35.47005000000001</v>
+      </c>
+      <c r="N72">
+        <v>137.22995</v>
+      </c>
+      <c r="O72">
+        <v>30.19058899999999</v>
+      </c>
+      <c r="P72">
+        <v>107.039361</v>
+      </c>
+      <c r="Q72">
+        <v>150.439361</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1650160955080227</v>
+      </c>
+      <c r="T72">
+        <v>2.134104954694966</v>
+      </c>
+      <c r="U72">
+        <v>0.055</v>
+      </c>
+      <c r="V72">
+        <v>0.22</v>
+      </c>
+      <c r="W72">
+        <v>0.0429</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>4.868896435161494</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.07947736219491829</v>
+      </c>
+      <c r="C73">
+        <v>309.4639921558387</v>
+      </c>
+      <c r="D73">
+        <v>775.0869921558386</v>
+      </c>
+      <c r="E73">
+        <v>376.3229999999999</v>
+      </c>
+      <c r="F73">
+        <v>654.1229999999999</v>
+      </c>
+      <c r="G73">
+        <v>188.5</v>
+      </c>
+      <c r="H73">
+        <v>643.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>216.1</v>
+      </c>
+      <c r="K73">
+        <v>43.4</v>
+      </c>
+      <c r="L73">
+        <v>172.7</v>
+      </c>
+      <c r="M73">
+        <v>35.97676499999999</v>
+      </c>
+      <c r="N73">
+        <v>136.723235</v>
+      </c>
+      <c r="O73">
+        <v>30.0791117</v>
+      </c>
+      <c r="P73">
+        <v>106.6441233</v>
+      </c>
+      <c r="Q73">
+        <v>150.0441233</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1690288351548906</v>
+      </c>
+      <c r="T73">
+        <v>2.201953730461741</v>
+      </c>
+      <c r="U73">
+        <v>0.055</v>
+      </c>
+      <c r="V73">
+        <v>0.22</v>
+      </c>
+      <c r="W73">
+        <v>0.0429</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>4.80032042903246</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.07941989573742975</v>
+      </c>
+      <c r="C74">
+        <v>301.3475361738874</v>
+      </c>
+      <c r="D74">
+        <v>776.1835361738873</v>
+      </c>
+      <c r="E74">
+        <v>385.5359999999999</v>
+      </c>
+      <c r="F74">
+        <v>663.3359999999999</v>
+      </c>
+      <c r="G74">
+        <v>188.5</v>
+      </c>
+      <c r="H74">
+        <v>643.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>216.1</v>
+      </c>
+      <c r="K74">
+        <v>43.4</v>
+      </c>
+      <c r="L74">
+        <v>172.7</v>
+      </c>
+      <c r="M74">
+        <v>36.48347999999999</v>
+      </c>
+      <c r="N74">
+        <v>136.21652</v>
+      </c>
+      <c r="O74">
+        <v>29.9676344</v>
+      </c>
+      <c r="P74">
+        <v>106.2488856</v>
+      </c>
+      <c r="Q74">
+        <v>149.6488856</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1733281990622491</v>
+      </c>
+      <c r="T74">
+        <v>2.274648847354715</v>
+      </c>
+      <c r="U74">
+        <v>0.055</v>
+      </c>
+      <c r="V74">
+        <v>0.22</v>
+      </c>
+      <c r="W74">
+        <v>0.0429</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.733649311962566</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.07936242927994122</v>
+      </c>
+      <c r="C75">
+        <v>293.2341872297202</v>
+      </c>
+      <c r="D75">
+        <v>777.2831872297202</v>
+      </c>
+      <c r="E75">
+        <v>394.749</v>
+      </c>
+      <c r="F75">
+        <v>672.549</v>
+      </c>
+      <c r="G75">
+        <v>188.5</v>
+      </c>
+      <c r="H75">
+        <v>643.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>216.1</v>
+      </c>
+      <c r="K75">
+        <v>43.4</v>
+      </c>
+      <c r="L75">
+        <v>172.7</v>
+      </c>
+      <c r="M75">
+        <v>36.990195</v>
+      </c>
+      <c r="N75">
+        <v>135.709805</v>
+      </c>
+      <c r="O75">
+        <v>29.85615709999999</v>
+      </c>
+      <c r="P75">
+        <v>105.8536479</v>
+      </c>
+      <c r="Q75">
+        <v>149.2536479</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1779460343701526</v>
+      </c>
+      <c r="T75">
+        <v>2.352728787721242</v>
+      </c>
+      <c r="U75">
+        <v>0.055</v>
+      </c>
+      <c r="V75">
+        <v>0.22</v>
+      </c>
+      <c r="W75">
+        <v>0.0429</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.66880480083979</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.0793049628224527</v>
+      </c>
+      <c r="C76">
+        <v>285.1239585476764</v>
+      </c>
+      <c r="D76">
+        <v>778.3859585476763</v>
+      </c>
+      <c r="E76">
+        <v>403.9619999999999</v>
+      </c>
+      <c r="F76">
+        <v>681.7619999999999</v>
+      </c>
+      <c r="G76">
+        <v>188.5</v>
+      </c>
+      <c r="H76">
+        <v>643.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>216.1</v>
+      </c>
+      <c r="K76">
+        <v>43.4</v>
+      </c>
+      <c r="L76">
+        <v>172.7</v>
+      </c>
+      <c r="M76">
+        <v>37.49691</v>
+      </c>
+      <c r="N76">
+        <v>135.20309</v>
+      </c>
+      <c r="O76">
+        <v>29.74467979999999</v>
+      </c>
+      <c r="P76">
+        <v>105.4584102</v>
+      </c>
+      <c r="Q76">
+        <v>148.8584102</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1829190877786642</v>
+      </c>
+      <c r="T76">
+        <v>2.436814877346733</v>
+      </c>
+      <c r="U76">
+        <v>0.055</v>
+      </c>
+      <c r="V76">
+        <v>0.22</v>
+      </c>
+      <c r="W76">
+        <v>0.0429</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.605712844071684</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.07924749636496417</v>
+      </c>
+      <c r="C77">
+        <v>277.0168634272499</v>
+      </c>
+      <c r="D77">
+        <v>779.4918634272498</v>
+      </c>
+      <c r="E77">
+        <v>413.1749999999999</v>
+      </c>
+      <c r="F77">
+        <v>690.9749999999999</v>
+      </c>
+      <c r="G77">
+        <v>188.5</v>
+      </c>
+      <c r="H77">
+        <v>643.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>216.1</v>
+      </c>
+      <c r="K77">
+        <v>43.4</v>
+      </c>
+      <c r="L77">
+        <v>172.7</v>
+      </c>
+      <c r="M77">
+        <v>38.00362499999999</v>
+      </c>
+      <c r="N77">
+        <v>134.696375</v>
+      </c>
+      <c r="O77">
+        <v>29.63320249999999</v>
+      </c>
+      <c r="P77">
+        <v>105.0631725</v>
+      </c>
+      <c r="Q77">
+        <v>148.4631725</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1882899854598566</v>
+      </c>
+      <c r="T77">
+        <v>2.527627854142264</v>
+      </c>
+      <c r="U77">
+        <v>0.055</v>
+      </c>
+      <c r="V77">
+        <v>0.22</v>
+      </c>
+      <c r="W77">
+        <v>0.0429</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.544303339484063</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.08144266990747565</v>
+      </c>
+      <c r="C78">
+        <v>227.6769220581662</v>
+      </c>
+      <c r="D78">
+        <v>739.3649220581661</v>
+      </c>
+      <c r="E78">
+        <v>422.388</v>
+      </c>
+      <c r="F78">
+        <v>700.188</v>
+      </c>
+      <c r="G78">
+        <v>188.5</v>
+      </c>
+      <c r="H78">
+        <v>643.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>216.1</v>
+      </c>
+      <c r="K78">
+        <v>43.4</v>
+      </c>
+      <c r="L78">
+        <v>172.7</v>
+      </c>
+      <c r="M78">
+        <v>41.1710544</v>
+      </c>
+      <c r="N78">
+        <v>131.5289456</v>
+      </c>
+      <c r="O78">
+        <v>28.93636803199999</v>
+      </c>
+      <c r="P78">
+        <v>102.592577568</v>
+      </c>
+      <c r="Q78">
+        <v>145.992577568</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1941084579478152</v>
+      </c>
+      <c r="T78">
+        <v>2.626008579004089</v>
+      </c>
+      <c r="U78">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V78">
+        <v>0.22</v>
+      </c>
+      <c r="W78">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.194694610493142</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.08141484344998712</v>
+      </c>
+      <c r="C79">
+        <v>218.9467093901507</v>
+      </c>
+      <c r="D79">
+        <v>739.8477093901506</v>
+      </c>
+      <c r="E79">
+        <v>431.6009999999999</v>
+      </c>
+      <c r="F79">
+        <v>709.401</v>
+      </c>
+      <c r="G79">
+        <v>188.5</v>
+      </c>
+      <c r="H79">
+        <v>643.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>216.1</v>
+      </c>
+      <c r="K79">
+        <v>43.4</v>
+      </c>
+      <c r="L79">
+        <v>172.7</v>
+      </c>
+      <c r="M79">
+        <v>41.7127788</v>
+      </c>
+      <c r="N79">
+        <v>130.9872212</v>
+      </c>
+      <c r="O79">
+        <v>28.817188664</v>
+      </c>
+      <c r="P79">
+        <v>102.170032536</v>
+      </c>
+      <c r="Q79">
+        <v>145.570032536</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2004328845651613</v>
+      </c>
+      <c r="T79">
+        <v>2.732944149506072</v>
+      </c>
+      <c r="U79">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V79">
+        <v>0.22</v>
+      </c>
+      <c r="W79">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.140218057110115</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.08138701699249859</v>
+      </c>
+      <c r="C80">
+        <v>210.2171276309012</v>
+      </c>
+      <c r="D80">
+        <v>740.3311276309013</v>
+      </c>
+      <c r="E80">
+        <v>440.814</v>
+      </c>
+      <c r="F80">
+        <v>718.614</v>
+      </c>
+      <c r="G80">
+        <v>188.5</v>
+      </c>
+      <c r="H80">
+        <v>643.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>216.1</v>
+      </c>
+      <c r="K80">
+        <v>43.4</v>
+      </c>
+      <c r="L80">
+        <v>172.7</v>
+      </c>
+      <c r="M80">
+        <v>42.2545032</v>
+      </c>
+      <c r="N80">
+        <v>130.4454968</v>
+      </c>
+      <c r="O80">
+        <v>28.698009296</v>
+      </c>
+      <c r="P80">
+        <v>101.747487504</v>
+      </c>
+      <c r="Q80">
+        <v>145.147487504</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2073322590568117</v>
+      </c>
+      <c r="T80">
+        <v>2.849601135508236</v>
+      </c>
+      <c r="U80">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V80">
+        <v>0.22</v>
+      </c>
+      <c r="W80">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>4.087138338429217</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.08135919053501006</v>
+      </c>
+      <c r="C81">
+        <v>201.4881780179383</v>
+      </c>
+      <c r="D81">
+        <v>740.8151780179383</v>
+      </c>
+      <c r="E81">
+        <v>450.027</v>
+      </c>
+      <c r="F81">
+        <v>727.827</v>
+      </c>
+      <c r="G81">
+        <v>188.5</v>
+      </c>
+      <c r="H81">
+        <v>643.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>216.1</v>
+      </c>
+      <c r="K81">
+        <v>43.4</v>
+      </c>
+      <c r="L81">
+        <v>172.7</v>
+      </c>
+      <c r="M81">
+        <v>42.7962276</v>
+      </c>
+      <c r="N81">
+        <v>129.9037724</v>
+      </c>
+      <c r="O81">
+        <v>28.57882992799999</v>
+      </c>
+      <c r="P81">
+        <v>101.324942472</v>
+      </c>
+      <c r="Q81">
+        <v>144.724942472</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2148887168333812</v>
+      </c>
+      <c r="T81">
+        <v>2.977368310653463</v>
+      </c>
+      <c r="U81">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V81">
+        <v>0.22</v>
+      </c>
+      <c r="W81">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>4.035402410094669</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.08395216407752153</v>
+      </c>
+      <c r="C82">
+        <v>149.7320531038495</v>
+      </c>
+      <c r="D82">
+        <v>698.2720531038494</v>
+      </c>
+      <c r="E82">
+        <v>459.24</v>
+      </c>
+      <c r="F82">
+        <v>737.04</v>
+      </c>
+      <c r="G82">
+        <v>188.5</v>
+      </c>
+      <c r="H82">
+        <v>643.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>216.1</v>
+      </c>
+      <c r="K82">
+        <v>43.4</v>
+      </c>
+      <c r="L82">
+        <v>172.7</v>
+      </c>
+      <c r="M82">
+        <v>46.43352</v>
+      </c>
+      <c r="N82">
+        <v>126.26648</v>
+      </c>
+      <c r="O82">
+        <v>27.77862559999999</v>
+      </c>
+      <c r="P82">
+        <v>98.48785439999999</v>
+      </c>
+      <c r="Q82">
+        <v>141.8878544</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2232008203876077</v>
+      </c>
+      <c r="T82">
+        <v>3.117912203313213</v>
+      </c>
+      <c r="U82">
+        <v>0.063</v>
+      </c>
+      <c r="V82">
+        <v>0.22</v>
+      </c>
+      <c r="W82">
+        <v>0.04914</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>3.719295887970586</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.08395709762003299</v>
+      </c>
+      <c r="C83">
+        <v>140.4427648780749</v>
+      </c>
+      <c r="D83">
+        <v>698.1957648780749</v>
+      </c>
+      <c r="E83">
+        <v>468.453</v>
+      </c>
+      <c r="F83">
+        <v>746.253</v>
+      </c>
+      <c r="G83">
+        <v>188.5</v>
+      </c>
+      <c r="H83">
+        <v>643.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>216.1</v>
+      </c>
+      <c r="K83">
+        <v>43.4</v>
+      </c>
+      <c r="L83">
+        <v>172.7</v>
+      </c>
+      <c r="M83">
+        <v>47.013939</v>
+      </c>
+      <c r="N83">
+        <v>125.686061</v>
+      </c>
+      <c r="O83">
+        <v>27.65093341999999</v>
+      </c>
+      <c r="P83">
+        <v>98.03512757999999</v>
+      </c>
+      <c r="Q83">
+        <v>141.43512758</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2323878822107</v>
+      </c>
+      <c r="T83">
+        <v>3.273250189937146</v>
+      </c>
+      <c r="U83">
+        <v>0.063</v>
+      </c>
+      <c r="V83">
+        <v>0.22</v>
+      </c>
+      <c r="W83">
+        <v>0.04914</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>3.673378654785765</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.08396203116254447</v>
+      </c>
+      <c r="C84">
+        <v>131.1534933198946</v>
+      </c>
+      <c r="D84">
+        <v>698.1194933198946</v>
+      </c>
+      <c r="E84">
+        <v>477.666</v>
+      </c>
+      <c r="F84">
+        <v>755.466</v>
+      </c>
+      <c r="G84">
+        <v>188.5</v>
+      </c>
+      <c r="H84">
+        <v>643.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>216.1</v>
+      </c>
+      <c r="K84">
+        <v>43.4</v>
+      </c>
+      <c r="L84">
+        <v>172.7</v>
+      </c>
+      <c r="M84">
+        <v>47.594358</v>
+      </c>
+      <c r="N84">
+        <v>125.105642</v>
+      </c>
+      <c r="O84">
+        <v>27.52324123999999</v>
+      </c>
+      <c r="P84">
+        <v>97.58240076</v>
+      </c>
+      <c r="Q84">
+        <v>140.98240076</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2425957286808026</v>
+      </c>
+      <c r="T84">
+        <v>3.445847952852628</v>
+      </c>
+      <c r="U84">
+        <v>0.063</v>
+      </c>
+      <c r="V84">
+        <v>0.22</v>
+      </c>
+      <c r="W84">
+        <v>0.04914</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>3.628581354117645</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.08396696470505594</v>
+      </c>
+      <c r="C85">
+        <v>121.8642384238468</v>
+      </c>
+      <c r="D85">
+        <v>698.0432384238468</v>
+      </c>
+      <c r="E85">
+        <v>486.879</v>
+      </c>
+      <c r="F85">
+        <v>764.679</v>
+      </c>
+      <c r="G85">
+        <v>188.5</v>
+      </c>
+      <c r="H85">
+        <v>643.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>216.1</v>
+      </c>
+      <c r="K85">
+        <v>43.4</v>
+      </c>
+      <c r="L85">
+        <v>172.7</v>
+      </c>
+      <c r="M85">
+        <v>48.174777</v>
+      </c>
+      <c r="N85">
+        <v>124.525223</v>
+      </c>
+      <c r="O85">
+        <v>27.39554905999999</v>
+      </c>
+      <c r="P85">
+        <v>97.12967393999999</v>
+      </c>
+      <c r="Q85">
+        <v>140.52967394</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.254004498265035</v>
+      </c>
+      <c r="T85">
+        <v>3.638751334934638</v>
+      </c>
+      <c r="U85">
+        <v>0.063</v>
+      </c>
+      <c r="V85">
+        <v>0.22</v>
+      </c>
+      <c r="W85">
+        <v>0.04914</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>3.584863506477673</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.08397189824756741</v>
+      </c>
+      <c r="C86">
+        <v>112.5750001844719</v>
+      </c>
+      <c r="D86">
+        <v>697.9670001844719</v>
+      </c>
+      <c r="E86">
+        <v>496.0919999999999</v>
+      </c>
+      <c r="F86">
+        <v>773.8919999999999</v>
+      </c>
+      <c r="G86">
+        <v>188.5</v>
+      </c>
+      <c r="H86">
+        <v>643.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>216.1</v>
+      </c>
+      <c r="K86">
+        <v>43.4</v>
+      </c>
+      <c r="L86">
+        <v>172.7</v>
+      </c>
+      <c r="M86">
+        <v>48.755196</v>
+      </c>
+      <c r="N86">
+        <v>123.944804</v>
+      </c>
+      <c r="O86">
+        <v>27.26785687999999</v>
+      </c>
+      <c r="P86">
+        <v>96.67694711999999</v>
+      </c>
+      <c r="Q86">
+        <v>140.07694712</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2668393640472963</v>
+      </c>
+      <c r="T86">
+        <v>3.855767639776897</v>
+      </c>
+      <c r="U86">
+        <v>0.063</v>
+      </c>
+      <c r="V86">
+        <v>0.22</v>
+      </c>
+      <c r="W86">
+        <v>0.04914</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>3.542186559971988</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.08397683179007889</v>
+      </c>
+      <c r="C87">
+        <v>103.2857785963133</v>
+      </c>
+      <c r="D87">
+        <v>697.8907785963132</v>
+      </c>
+      <c r="E87">
+        <v>505.3049999999999</v>
+      </c>
+      <c r="F87">
+        <v>783.1049999999999</v>
+      </c>
+      <c r="G87">
+        <v>188.5</v>
+      </c>
+      <c r="H87">
+        <v>643.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>216.1</v>
+      </c>
+      <c r="K87">
+        <v>43.4</v>
+      </c>
+      <c r="L87">
+        <v>172.7</v>
+      </c>
+      <c r="M87">
+        <v>49.335615</v>
+      </c>
+      <c r="N87">
+        <v>123.364385</v>
+      </c>
+      <c r="O87">
+        <v>27.1401647</v>
+      </c>
+      <c r="P87">
+        <v>96.2242203</v>
+      </c>
+      <c r="Q87">
+        <v>139.6242203</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2813855452671925</v>
+      </c>
+      <c r="T87">
+        <v>4.101719451931458</v>
+      </c>
+      <c r="U87">
+        <v>0.063</v>
+      </c>
+      <c r="V87">
+        <v>0.22</v>
+      </c>
+      <c r="W87">
+        <v>0.04914</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>3.500513776913494</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.08874444533259035</v>
+      </c>
+      <c r="C88">
+        <v>27.45328757839025</v>
+      </c>
+      <c r="D88">
+        <v>631.2712875783902</v>
+      </c>
+      <c r="E88">
+        <v>514.518</v>
+      </c>
+      <c r="F88">
+        <v>792.318</v>
+      </c>
+      <c r="G88">
+        <v>188.5</v>
+      </c>
+      <c r="H88">
+        <v>643.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>216.1</v>
+      </c>
+      <c r="K88">
+        <v>43.4</v>
+      </c>
+      <c r="L88">
+        <v>172.7</v>
+      </c>
+      <c r="M88">
+        <v>55.5414918</v>
+      </c>
+      <c r="N88">
+        <v>117.1585082</v>
+      </c>
+      <c r="O88">
+        <v>25.774871804</v>
+      </c>
+      <c r="P88">
+        <v>91.383636396</v>
+      </c>
+      <c r="Q88">
+        <v>134.783636396</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2980097523756453</v>
+      </c>
+      <c r="T88">
+        <v>4.382807237250956</v>
+      </c>
+      <c r="U88">
+        <v>0.0701</v>
+      </c>
+      <c r="V88">
+        <v>0.22</v>
+      </c>
+      <c r="W88">
+        <v>0.054678</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>3.109387133890416</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.08880475887510184</v>
+      </c>
+      <c r="C89">
+        <v>17.47887589485958</v>
+      </c>
+      <c r="D89">
+        <v>630.5098758948595</v>
+      </c>
+      <c r="E89">
+        <v>523.731</v>
+      </c>
+      <c r="F89">
+        <v>801.5309999999999</v>
+      </c>
+      <c r="G89">
+        <v>188.5</v>
+      </c>
+      <c r="H89">
+        <v>643.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>216.1</v>
+      </c>
+      <c r="K89">
+        <v>43.4</v>
+      </c>
+      <c r="L89">
+        <v>172.7</v>
+      </c>
+      <c r="M89">
+        <v>56.18732309999999</v>
+      </c>
+      <c r="N89">
+        <v>116.5126769</v>
+      </c>
+      <c r="O89">
+        <v>25.632788918</v>
+      </c>
+      <c r="P89">
+        <v>90.87988798200001</v>
+      </c>
+      <c r="Q89">
+        <v>134.279887982</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3171915298084756</v>
+      </c>
+      <c r="T89">
+        <v>4.707139297234995</v>
+      </c>
+      <c r="U89">
+        <v>0.0701</v>
+      </c>
+      <c r="V89">
+        <v>0.22</v>
+      </c>
+      <c r="W89">
+        <v>0.054678</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>3.073647051891675</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.08886507241761329</v>
+      </c>
+      <c r="C90">
+        <v>7.506298761195012</v>
+      </c>
+      <c r="D90">
+        <v>629.7502987611949</v>
+      </c>
+      <c r="E90">
+        <v>532.944</v>
+      </c>
+      <c r="F90">
+        <v>810.7439999999999</v>
+      </c>
+      <c r="G90">
+        <v>188.5</v>
+      </c>
+      <c r="H90">
+        <v>643.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>216.1</v>
+      </c>
+      <c r="K90">
+        <v>43.4</v>
+      </c>
+      <c r="L90">
+        <v>172.7</v>
+      </c>
+      <c r="M90">
+        <v>56.83315439999999</v>
+      </c>
+      <c r="N90">
+        <v>115.8668456</v>
+      </c>
+      <c r="O90">
+        <v>25.490706032</v>
+      </c>
+      <c r="P90">
+        <v>90.37613956800001</v>
+      </c>
+      <c r="Q90">
+        <v>133.776139568</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3395702701467775</v>
+      </c>
+      <c r="T90">
+        <v>5.085526700549705</v>
+      </c>
+      <c r="U90">
+        <v>0.0701</v>
+      </c>
+      <c r="V90">
+        <v>0.22</v>
+      </c>
+      <c r="W90">
+        <v>0.054678</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.038719244483815</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.08892538596012475</v>
+      </c>
+      <c r="C91">
+        <v>-2.464450444889053</v>
+      </c>
+      <c r="D91">
+        <v>628.9925495551109</v>
+      </c>
+      <c r="E91">
+        <v>542.1569999999999</v>
+      </c>
+      <c r="F91">
+        <v>819.957</v>
+      </c>
+      <c r="G91">
+        <v>188.5</v>
+      </c>
+      <c r="H91">
+        <v>643.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>216.1</v>
+      </c>
+      <c r="K91">
+        <v>43.4</v>
+      </c>
+      <c r="L91">
+        <v>172.7</v>
+      </c>
+      <c r="M91">
+        <v>57.4789857</v>
+      </c>
+      <c r="N91">
+        <v>115.2210143</v>
+      </c>
+      <c r="O91">
+        <v>25.34862314599999</v>
+      </c>
+      <c r="P91">
+        <v>89.872391154</v>
+      </c>
+      <c r="Q91">
+        <v>133.272391154</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3660178723647706</v>
+      </c>
+      <c r="T91">
+        <v>5.532711813557999</v>
+      </c>
+      <c r="U91">
+        <v>0.0701</v>
+      </c>
+      <c r="V91">
+        <v>0.22</v>
+      </c>
+      <c r="W91">
+        <v>0.054678</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>3.004576331624446</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1039382995026362</v>
+      </c>
+      <c r="C92">
+        <v>-156.6460915892986</v>
+      </c>
+      <c r="D92">
+        <v>484.0239084107013</v>
+      </c>
+      <c r="E92">
+        <v>551.3699999999999</v>
+      </c>
+      <c r="F92">
+        <v>829.17</v>
+      </c>
+      <c r="G92">
+        <v>188.5</v>
+      </c>
+      <c r="H92">
+        <v>643.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>216.1</v>
+      </c>
+      <c r="K92">
+        <v>43.4</v>
+      </c>
+      <c r="L92">
+        <v>172.7</v>
+      </c>
+      <c r="M92">
+        <v>75.78613800000001</v>
+      </c>
+      <c r="N92">
+        <v>96.91386199999998</v>
+      </c>
+      <c r="O92">
+        <v>21.32104963999999</v>
+      </c>
+      <c r="P92">
+        <v>75.59281235999998</v>
+      </c>
+      <c r="Q92">
+        <v>118.99281236</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3977549950263624</v>
+      </c>
+      <c r="T92">
+        <v>6.069333949167952</v>
+      </c>
+      <c r="U92">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V92">
+        <v>0.22</v>
+      </c>
+      <c r="W92">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>2.278780850397733</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1041647530451477</v>
+      </c>
+      <c r="C93">
+        <v>-167.5359728381907</v>
+      </c>
+      <c r="D93">
+        <v>482.3470271618094</v>
+      </c>
+      <c r="E93">
+        <v>560.5830000000001</v>
+      </c>
+      <c r="F93">
+        <v>838.383</v>
+      </c>
+      <c r="G93">
+        <v>188.5</v>
+      </c>
+      <c r="H93">
+        <v>643.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>216.1</v>
+      </c>
+      <c r="K93">
+        <v>43.4</v>
+      </c>
+      <c r="L93">
+        <v>172.7</v>
+      </c>
+      <c r="M93">
+        <v>76.62820620000001</v>
+      </c>
+      <c r="N93">
+        <v>96.07179379999998</v>
+      </c>
+      <c r="O93">
+        <v>21.13579463599999</v>
+      </c>
+      <c r="P93">
+        <v>74.93599916399998</v>
+      </c>
+      <c r="Q93">
+        <v>118.335999164</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4365448116127525</v>
+      </c>
+      <c r="T93">
+        <v>6.725205448246784</v>
+      </c>
+      <c r="U93">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V93">
+        <v>0.22</v>
+      </c>
+      <c r="W93">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>2.253739302591165</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1043912065876592</v>
+      </c>
+      <c r="C94">
+        <v>-178.4142752270815</v>
+      </c>
+      <c r="D94">
+        <v>480.6817247729185</v>
+      </c>
+      <c r="E94">
+        <v>569.796</v>
+      </c>
+      <c r="F94">
+        <v>847.596</v>
+      </c>
+      <c r="G94">
+        <v>188.5</v>
+      </c>
+      <c r="H94">
+        <v>643.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>216.1</v>
+      </c>
+      <c r="K94">
+        <v>43.4</v>
+      </c>
+      <c r="L94">
+        <v>172.7</v>
+      </c>
+      <c r="M94">
+        <v>77.47027440000001</v>
+      </c>
+      <c r="N94">
+        <v>95.22972559999998</v>
+      </c>
+      <c r="O94">
+        <v>20.95053963199999</v>
+      </c>
+      <c r="P94">
+        <v>74.27918596799998</v>
+      </c>
+      <c r="Q94">
+        <v>117.679185968</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.48503208234574</v>
+      </c>
+      <c r="T94">
+        <v>7.545044822095325</v>
+      </c>
+      <c r="U94">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V94">
+        <v>0.22</v>
+      </c>
+      <c r="W94">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>2.229242136258652</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1046176601301707</v>
+      </c>
+      <c r="C95">
+        <v>-189.2811182713353</v>
+      </c>
+      <c r="D95">
+        <v>479.0278817286646</v>
+      </c>
+      <c r="E95">
+        <v>579.009</v>
+      </c>
+      <c r="F95">
+        <v>856.809</v>
+      </c>
+      <c r="G95">
+        <v>188.5</v>
+      </c>
+      <c r="H95">
+        <v>643.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>216.1</v>
+      </c>
+      <c r="K95">
+        <v>43.4</v>
+      </c>
+      <c r="L95">
+        <v>172.7</v>
+      </c>
+      <c r="M95">
+        <v>78.31234260000001</v>
+      </c>
+      <c r="N95">
+        <v>94.38765739999998</v>
+      </c>
+      <c r="O95">
+        <v>20.76528462799999</v>
+      </c>
+      <c r="P95">
+        <v>73.62237277199999</v>
+      </c>
+      <c r="Q95">
+        <v>117.022372772</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5473728590024383</v>
+      </c>
+      <c r="T95">
+        <v>8.599124017043447</v>
+      </c>
+      <c r="U95">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V95">
+        <v>0.22</v>
+      </c>
+      <c r="W95">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>2.205271790707484</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1048441136726821</v>
+      </c>
+      <c r="C96">
+        <v>-200.1366198471284</v>
+      </c>
+      <c r="D96">
+        <v>477.3853801528716</v>
+      </c>
+      <c r="E96">
+        <v>588.222</v>
+      </c>
+      <c r="F96">
+        <v>866.022</v>
+      </c>
+      <c r="G96">
+        <v>188.5</v>
+      </c>
+      <c r="H96">
+        <v>643.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>216.1</v>
+      </c>
+      <c r="K96">
+        <v>43.4</v>
+      </c>
+      <c r="L96">
+        <v>172.7</v>
+      </c>
+      <c r="M96">
+        <v>79.15441080000001</v>
+      </c>
+      <c r="N96">
+        <v>93.54558919999998</v>
+      </c>
+      <c r="O96">
+        <v>20.58002962399999</v>
+      </c>
+      <c r="P96">
+        <v>72.96555957599999</v>
+      </c>
+      <c r="Q96">
+        <v>116.365559576</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6304938945447027</v>
+      </c>
+      <c r="T96">
+        <v>10.00456294364095</v>
+      </c>
+      <c r="U96">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V96">
+        <v>0.22</v>
+      </c>
+      <c r="W96">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>2.181811452508468</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1050705672151936</v>
+      </c>
+      <c r="C97">
+        <v>-210.9808962194546</v>
+      </c>
+      <c r="D97">
+        <v>475.7541037805454</v>
+      </c>
+      <c r="E97">
+        <v>597.4349999999999</v>
+      </c>
+      <c r="F97">
+        <v>875.235</v>
+      </c>
+      <c r="G97">
+        <v>188.5</v>
+      </c>
+      <c r="H97">
+        <v>643.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>216.1</v>
+      </c>
+      <c r="K97">
+        <v>43.4</v>
+      </c>
+      <c r="L97">
+        <v>172.7</v>
+      </c>
+      <c r="M97">
+        <v>79.99647900000001</v>
+      </c>
+      <c r="N97">
+        <v>92.70352099999998</v>
+      </c>
+      <c r="O97">
+        <v>20.39477461999999</v>
+      </c>
+      <c r="P97">
+        <v>72.30874637999999</v>
+      </c>
+      <c r="Q97">
+        <v>115.70874638</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.746863344303873</v>
+      </c>
+      <c r="T97">
+        <v>11.97217744087745</v>
+      </c>
+      <c r="U97">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V97">
+        <v>0.22</v>
+      </c>
+      <c r="W97">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>2.158845016166274</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1052970207577051</v>
+      </c>
+      <c r="C98">
+        <v>-221.8140620695611</v>
+      </c>
+      <c r="D98">
+        <v>474.1339379304388</v>
+      </c>
+      <c r="E98">
+        <v>606.6479999999999</v>
+      </c>
+      <c r="F98">
+        <v>884.448</v>
+      </c>
+      <c r="G98">
+        <v>188.5</v>
+      </c>
+      <c r="H98">
+        <v>643.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>216.1</v>
+      </c>
+      <c r="K98">
+        <v>43.4</v>
+      </c>
+      <c r="L98">
+        <v>172.7</v>
+      </c>
+      <c r="M98">
+        <v>80.83854720000001</v>
+      </c>
+      <c r="N98">
+        <v>91.86145279999998</v>
+      </c>
+      <c r="O98">
+        <v>20.20951961599999</v>
+      </c>
+      <c r="P98">
+        <v>71.65193318399999</v>
+      </c>
+      <c r="Q98">
+        <v>115.051933184</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9214175189426259</v>
+      </c>
+      <c r="T98">
+        <v>14.92359918673216</v>
+      </c>
+      <c r="U98">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V98">
+        <v>0.22</v>
+      </c>
+      <c r="W98">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>2.136357047247875</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1055234743002166</v>
+      </c>
+      <c r="C99">
+        <v>-232.6362305218239</v>
+      </c>
+      <c r="D99">
+        <v>472.5247694781761</v>
+      </c>
+      <c r="E99">
+        <v>615.8609999999999</v>
+      </c>
+      <c r="F99">
+        <v>893.6609999999999</v>
+      </c>
+      <c r="G99">
+        <v>188.5</v>
+      </c>
+      <c r="H99">
+        <v>643.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>216.1</v>
+      </c>
+      <c r="K99">
+        <v>43.4</v>
+      </c>
+      <c r="L99">
+        <v>172.7</v>
+      </c>
+      <c r="M99">
+        <v>81.68061540000001</v>
+      </c>
+      <c r="N99">
+        <v>91.01938459999998</v>
+      </c>
+      <c r="O99">
+        <v>20.02426461199999</v>
+      </c>
+      <c r="P99">
+        <v>70.99511998799998</v>
+      </c>
+      <c r="Q99">
+        <v>114.395119988</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.21234114334055</v>
+      </c>
+      <c r="T99">
+        <v>19.84263542982339</v>
+      </c>
+      <c r="U99">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V99">
+        <v>0.22</v>
+      </c>
+      <c r="W99">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>2.114332747791711</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.105749927842728</v>
+      </c>
+      <c r="C100">
+        <v>-243.4475131700757</v>
+      </c>
+      <c r="D100">
+        <v>470.9264868299242</v>
+      </c>
+      <c r="E100">
+        <v>625.0739999999998</v>
+      </c>
+      <c r="F100">
+        <v>902.8739999999999</v>
+      </c>
+      <c r="G100">
+        <v>188.5</v>
+      </c>
+      <c r="H100">
+        <v>643.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>216.1</v>
+      </c>
+      <c r="K100">
+        <v>43.4</v>
+      </c>
+      <c r="L100">
+        <v>172.7</v>
+      </c>
+      <c r="M100">
+        <v>82.52268359999999</v>
+      </c>
+      <c r="N100">
+        <v>90.1773164</v>
+      </c>
+      <c r="O100">
+        <v>19.839009608</v>
+      </c>
+      <c r="P100">
+        <v>70.338306792</v>
+      </c>
+      <c r="Q100">
+        <v>113.738306792</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.794188392136399</v>
+      </c>
+      <c r="T100">
+        <v>29.68070791600584</v>
+      </c>
+      <c r="U100">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V100">
+        <v>0.22</v>
+      </c>
+      <c r="W100">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>2.092757923834653</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1059763813852395</v>
+      </c>
+      <c r="C101">
+        <v>-254.2480201034062</v>
+      </c>
+      <c r="D101">
+        <v>469.3389798965937</v>
+      </c>
+      <c r="E101">
+        <v>634.287</v>
+      </c>
+      <c r="F101">
+        <v>912.087</v>
+      </c>
+      <c r="G101">
+        <v>188.5</v>
+      </c>
+      <c r="H101">
+        <v>643.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>216.1</v>
+      </c>
+      <c r="K101">
+        <v>43.4</v>
+      </c>
+      <c r="L101">
+        <v>172.7</v>
+      </c>
+      <c r="M101">
+        <v>83.36475180000001</v>
+      </c>
+      <c r="N101">
+        <v>89.33524819999998</v>
+      </c>
+      <c r="O101">
+        <v>19.65375460399999</v>
+      </c>
+      <c r="P101">
+        <v>69.681493596</v>
+      </c>
+      <c r="Q101">
+        <v>113.081493596</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.539730138523946</v>
+      </c>
+      <c r="T101">
+        <v>59.19492537455321</v>
+      </c>
+      <c r="U101">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V101">
+        <v>0.22</v>
+      </c>
+      <c r="W101">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>2.07161895490703</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_paper_forest_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07460628441596914</v>
+        <v>0.07447725059025401</v>
       </c>
       <c r="C2">
-        <v>565.4077841660771</v>
+        <v>560.3821204202225</v>
       </c>
       <c r="D2">
-        <v>413.0077841660771</v>
+        <v>414.8661204202225</v>
       </c>
       <c r="E2">
-        <v>-505.4</v>
+        <v>-498.516</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.884</v>
       </c>
       <c r="G2">
         <v>152.4</v>
@@ -1451,28 +1451,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3462652</v>
       </c>
       <c r="N2">
-        <v>53.33333333333333</v>
+        <v>52.98706813333333</v>
       </c>
       <c r="O2">
-        <v>11.73333333333333</v>
+        <v>11.65715498933333</v>
       </c>
       <c r="P2">
-        <v>41.59999999999999</v>
+        <v>41.329913144</v>
       </c>
       <c r="Q2">
-        <v>90.59999999999999</v>
+        <v>90.32991314399999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07460628441596914</v>
+        <v>0.07483324302045859</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6705136956226002</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>154.0245260954128</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07447725059025401</v>
+        <v>0.07434821676453887</v>
       </c>
       <c r="C3">
-        <v>560.3821204202225</v>
+        <v>555.3732554984986</v>
       </c>
       <c r="D3">
-        <v>414.8661204202225</v>
+        <v>416.7412554984986</v>
       </c>
       <c r="E3">
-        <v>-498.516</v>
+        <v>-491.6319999999999</v>
       </c>
       <c r="F3">
-        <v>6.884</v>
+        <v>13.768</v>
       </c>
       <c r="G3">
         <v>152.4</v>
@@ -1533,28 +1533,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M3">
-        <v>0.3462652</v>
+        <v>0.6925304</v>
       </c>
       <c r="N3">
-        <v>52.98706813333333</v>
+        <v>52.64080293333333</v>
       </c>
       <c r="O3">
-        <v>11.65715498933333</v>
+        <v>11.58097664533333</v>
       </c>
       <c r="P3">
-        <v>41.329913144</v>
+        <v>41.059826288</v>
       </c>
       <c r="Q3">
-        <v>90.32991314399999</v>
+        <v>90.059826288</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07483324302045859</v>
+        <v>0.07506483343320293</v>
       </c>
       <c r="T3">
-        <v>0.6705136956226002</v>
+        <v>0.6758622040000677</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.0245260954128</v>
+        <v>77.0122630477064</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07434821676453887</v>
+        <v>0.07421918293882374</v>
       </c>
       <c r="C4">
-        <v>555.3732554984986</v>
+        <v>550.3814182199271</v>
       </c>
       <c r="D4">
-        <v>416.7412554984986</v>
+        <v>418.6334182199271</v>
       </c>
       <c r="E4">
-        <v>-491.6319999999999</v>
+        <v>-484.748</v>
       </c>
       <c r="F4">
-        <v>13.768</v>
+        <v>20.652</v>
       </c>
       <c r="G4">
         <v>152.4</v>
@@ -1615,28 +1615,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M4">
-        <v>0.6925304</v>
+        <v>1.0387956</v>
       </c>
       <c r="N4">
-        <v>52.64080293333333</v>
+        <v>52.29453773333333</v>
       </c>
       <c r="O4">
-        <v>11.58097664533333</v>
+        <v>11.50479830133333</v>
       </c>
       <c r="P4">
-        <v>41.059826288</v>
+        <v>40.789739432</v>
       </c>
       <c r="Q4">
-        <v>90.059826288</v>
+        <v>89.789739432</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07506483343320293</v>
+        <v>0.07530119890600386</v>
       </c>
       <c r="T4">
-        <v>0.6758622040000677</v>
+        <v>0.6813209909007819</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.0122630477064</v>
+        <v>51.34150869847094</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07421918293882374</v>
+        <v>0.07409014911310861</v>
       </c>
       <c r="C5">
-        <v>550.3814182199271</v>
+        <v>545.406841578183</v>
       </c>
       <c r="D5">
-        <v>418.6334182199271</v>
+        <v>420.5428415781831</v>
       </c>
       <c r="E5">
-        <v>-484.748</v>
+        <v>-477.864</v>
       </c>
       <c r="F5">
-        <v>20.652</v>
+        <v>27.536</v>
       </c>
       <c r="G5">
         <v>152.4</v>
@@ -1697,28 +1697,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M5">
-        <v>1.0387956</v>
+        <v>1.3850608</v>
       </c>
       <c r="N5">
-        <v>52.29453773333333</v>
+        <v>51.94827253333333</v>
       </c>
       <c r="O5">
-        <v>11.50479830133333</v>
+        <v>11.42861995733333</v>
       </c>
       <c r="P5">
-        <v>40.789739432</v>
+        <v>40.519652576</v>
       </c>
       <c r="Q5">
-        <v>89.789739432</v>
+        <v>89.519652576</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07530119890600386</v>
+        <v>0.07554248865948814</v>
       </c>
       <c r="T5">
-        <v>0.6813209909007819</v>
+        <v>0.6868935025285944</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.34150869847094</v>
+        <v>38.5061315238532</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07409014911310861</v>
+        <v>0.07396111528739348</v>
       </c>
       <c r="C6">
-        <v>545.406841578183</v>
+        <v>540.4497628372371</v>
       </c>
       <c r="D6">
-        <v>420.5428415781831</v>
+        <v>422.4697628372371</v>
       </c>
       <c r="E6">
-        <v>-477.864</v>
+        <v>-470.98</v>
       </c>
       <c r="F6">
-        <v>27.536</v>
+        <v>34.42</v>
       </c>
       <c r="G6">
         <v>152.4</v>
@@ -1779,28 +1779,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M6">
-        <v>1.3850608</v>
+        <v>1.731326</v>
       </c>
       <c r="N6">
-        <v>51.94827253333333</v>
+        <v>51.60200733333333</v>
       </c>
       <c r="O6">
-        <v>11.42861995733333</v>
+        <v>11.35244161333333</v>
       </c>
       <c r="P6">
-        <v>40.519652576</v>
+        <v>40.24956571999999</v>
       </c>
       <c r="Q6">
-        <v>89.519652576</v>
+        <v>89.24956571999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07554248865948814</v>
+        <v>0.0757888581972563</v>
       </c>
       <c r="T6">
-        <v>0.6868935025285944</v>
+        <v>0.6925833301906765</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.5061315238532</v>
+        <v>30.80490521908256</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07396111528739348</v>
+        <v>0.07383208146167834</v>
       </c>
       <c r="C7">
-        <v>540.4497628372371</v>
+        <v>535.5104236296359</v>
       </c>
       <c r="D7">
-        <v>422.4697628372371</v>
+        <v>424.4144236296358</v>
       </c>
       <c r="E7">
-        <v>-470.98</v>
+        <v>-464.096</v>
       </c>
       <c r="F7">
-        <v>34.42</v>
+        <v>41.304</v>
       </c>
       <c r="G7">
         <v>152.4</v>
@@ -1861,28 +1861,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M7">
-        <v>1.731326</v>
+        <v>2.0775912</v>
       </c>
       <c r="N7">
-        <v>51.60200733333333</v>
+        <v>51.25574213333333</v>
       </c>
       <c r="O7">
-        <v>11.35244161333333</v>
+        <v>11.27626326933333</v>
       </c>
       <c r="P7">
-        <v>40.24956571999999</v>
+        <v>39.97947886399999</v>
       </c>
       <c r="Q7">
-        <v>89.24956571999999</v>
+        <v>88.97947886399999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0757888581972563</v>
+        <v>0.07604046964008335</v>
       </c>
       <c r="T7">
-        <v>0.6925833301906765</v>
+        <v>0.6983942180157816</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.80490521908256</v>
+        <v>25.67075434923546</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07383208146167834</v>
+        <v>0.07370304763596322</v>
       </c>
       <c r="C8">
-        <v>535.5104236296359</v>
+        <v>530.5890700575131</v>
       </c>
       <c r="D8">
-        <v>424.4144236296358</v>
+        <v>426.3770700575131</v>
       </c>
       <c r="E8">
-        <v>-464.096</v>
+        <v>-457.212</v>
       </c>
       <c r="F8">
-        <v>41.30399999999999</v>
+        <v>48.188</v>
       </c>
       <c r="G8">
         <v>152.4</v>
@@ -1943,28 +1943,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M8">
-        <v>2.0775912</v>
+        <v>2.4238564</v>
       </c>
       <c r="N8">
-        <v>51.25574213333333</v>
+        <v>50.90947693333333</v>
       </c>
       <c r="O8">
-        <v>11.27626326933333</v>
+        <v>11.20008492533333</v>
       </c>
       <c r="P8">
-        <v>39.97947886399999</v>
+        <v>39.70939200799999</v>
       </c>
       <c r="Q8">
-        <v>88.97947886399999</v>
+        <v>88.70939200799999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07604046964008335</v>
+        <v>0.07629749208168088</v>
       </c>
       <c r="T8">
-        <v>0.6983942180157816</v>
+        <v>0.704330071170459</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.67075434923547</v>
+        <v>22.00350372791612</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07370304763596322</v>
+        <v>0.07357401381024808</v>
       </c>
       <c r="C9">
-        <v>530.5890700575131</v>
+        <v>525.6859527964145</v>
       </c>
       <c r="D9">
-        <v>426.3770700575131</v>
+        <v>428.3579527964145</v>
       </c>
       <c r="E9">
-        <v>-457.212</v>
+        <v>-450.328</v>
       </c>
       <c r="F9">
-        <v>48.188</v>
+        <v>55.072</v>
       </c>
       <c r="G9">
         <v>152.4</v>
@@ -2025,28 +2025,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M9">
-        <v>2.4238564</v>
+        <v>2.7701216</v>
       </c>
       <c r="N9">
-        <v>50.90947693333333</v>
+        <v>50.56321173333333</v>
       </c>
       <c r="O9">
-        <v>11.20008492533333</v>
+        <v>11.12390658133333</v>
       </c>
       <c r="P9">
-        <v>39.70939200799999</v>
+        <v>39.439305152</v>
       </c>
       <c r="Q9">
-        <v>88.70939200799999</v>
+        <v>88.439305152</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07629749208168088</v>
+        <v>0.07656010196766096</v>
       </c>
       <c r="T9">
-        <v>0.7043300711704591</v>
+        <v>0.7103949646111076</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.00350372791611</v>
+        <v>19.2530657619266</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07357401381024808</v>
+        <v>0.07344497998453296</v>
       </c>
       <c r="C10">
-        <v>525.6859527964145</v>
+        <v>520.8013272020297</v>
       </c>
       <c r="D10">
-        <v>428.3579527964145</v>
+        <v>430.3573272020297</v>
       </c>
       <c r="E10">
-        <v>-450.328</v>
+        <v>-443.444</v>
       </c>
       <c r="F10">
-        <v>55.072</v>
+        <v>61.956</v>
       </c>
       <c r="G10">
         <v>152.4</v>
@@ -2107,28 +2107,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M10">
-        <v>2.7701216</v>
+        <v>3.116386799999999</v>
       </c>
       <c r="N10">
-        <v>50.56321173333333</v>
+        <v>50.21694653333333</v>
       </c>
       <c r="O10">
-        <v>11.12390658133333</v>
+        <v>11.04772823733333</v>
       </c>
       <c r="P10">
-        <v>39.439305152</v>
+        <v>39.169218296</v>
       </c>
       <c r="Q10">
-        <v>88.439305152</v>
+        <v>88.169218296</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07656010196766096</v>
+        <v>0.07682848349948676</v>
       </c>
       <c r="T10">
-        <v>0.7103949646111076</v>
+        <v>0.7165931524130892</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.2530657619266</v>
+        <v>17.11383623282365</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07344497998453296</v>
+        <v>0.07331594615881781</v>
       </c>
       <c r="C11">
-        <v>520.8013272020297</v>
+        <v>515.9354534199293</v>
       </c>
       <c r="D11">
-        <v>430.3573272020297</v>
+        <v>432.3754534199293</v>
       </c>
       <c r="E11">
-        <v>-443.444</v>
+        <v>-436.56</v>
       </c>
       <c r="F11">
-        <v>61.956</v>
+        <v>68.83999999999999</v>
       </c>
       <c r="G11">
         <v>152.4</v>
@@ -2189,28 +2189,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M11">
-        <v>3.116386799999999</v>
+        <v>3.462651999999999</v>
       </c>
       <c r="N11">
-        <v>50.21694653333333</v>
+        <v>49.87068133333333</v>
       </c>
       <c r="O11">
-        <v>11.04772823733333</v>
+        <v>10.97154989333333</v>
       </c>
       <c r="P11">
-        <v>39.169218296</v>
+        <v>38.89913144</v>
       </c>
       <c r="Q11">
-        <v>88.169218296</v>
+        <v>87.89913143999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07682848349948676</v>
+        <v>0.07710282906535312</v>
       </c>
       <c r="T11">
-        <v>0.7165931524130892</v>
+        <v>0.7229290777217813</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.11383623282365</v>
+        <v>15.40245260954128</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07331594615881781</v>
+        <v>0.07318691233310269</v>
       </c>
       <c r="C12">
-        <v>515.9354534199293</v>
+        <v>511.0885964984007</v>
       </c>
       <c r="D12">
-        <v>432.3754534199293</v>
+        <v>434.4125964984007</v>
       </c>
       <c r="E12">
-        <v>-436.5599999999999</v>
+        <v>-429.676</v>
       </c>
       <c r="F12">
-        <v>68.84</v>
+        <v>75.724</v>
       </c>
       <c r="G12">
         <v>152.4</v>
@@ -2271,28 +2271,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M12">
-        <v>3.462652</v>
+        <v>3.8089172</v>
       </c>
       <c r="N12">
-        <v>49.87068133333333</v>
+        <v>49.52441613333333</v>
       </c>
       <c r="O12">
-        <v>10.97154989333333</v>
+        <v>10.89537154933333</v>
       </c>
       <c r="P12">
-        <v>38.89913144</v>
+        <v>38.629044584</v>
       </c>
       <c r="Q12">
-        <v>87.89913143999999</v>
+        <v>87.629044584</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07710282906535312</v>
+        <v>0.07738333970011538</v>
       </c>
       <c r="T12">
-        <v>0.7229290777217813</v>
+        <v>0.7294073833744892</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.40245260954128</v>
+        <v>14.00222964503753</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07318691233310269</v>
+        <v>0.07319827850738755</v>
       </c>
       <c r="C13">
-        <v>511.0885964984007</v>
+        <v>504.0243804573816</v>
       </c>
       <c r="D13">
-        <v>434.4125964984007</v>
+        <v>434.2323804573816</v>
       </c>
       <c r="E13">
-        <v>-429.676</v>
+        <v>-422.792</v>
       </c>
       <c r="F13">
-        <v>75.724</v>
+        <v>82.60799999999999</v>
       </c>
       <c r="G13">
         <v>152.4</v>
@@ -2353,45 +2353,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M13">
-        <v>3.8089172</v>
+        <v>4.279094399999999</v>
       </c>
       <c r="N13">
-        <v>49.52441613333333</v>
+        <v>49.05423893333333</v>
       </c>
       <c r="O13">
-        <v>10.89537154933333</v>
+        <v>10.79193256533333</v>
       </c>
       <c r="P13">
-        <v>38.629044584</v>
+        <v>38.262306368</v>
       </c>
       <c r="Q13">
-        <v>87.629044584</v>
+        <v>87.262306368</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07738333970011538</v>
+        <v>0.07767022557657677</v>
       </c>
       <c r="T13">
-        <v>0.7294073833744892</v>
+        <v>0.7360329232465767</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>14.00222964503753</v>
+        <v>12.46369636840294</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07319827850738755</v>
+        <v>0.07308094468167242</v>
       </c>
       <c r="C14">
-        <v>504.0243804573816</v>
+        <v>499.0079897738098</v>
       </c>
       <c r="D14">
-        <v>434.2323804573816</v>
+        <v>436.0999897738098</v>
       </c>
       <c r="E14">
-        <v>-422.792</v>
+        <v>-415.908</v>
       </c>
       <c r="F14">
-        <v>82.60799999999999</v>
+        <v>89.492</v>
       </c>
       <c r="G14">
         <v>152.4</v>
@@ -2435,28 +2435,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M14">
-        <v>4.279094399999999</v>
+        <v>4.6356856</v>
       </c>
       <c r="N14">
-        <v>49.05423893333333</v>
+        <v>48.69764773333333</v>
       </c>
       <c r="O14">
-        <v>10.79193256533333</v>
+        <v>10.71348250133333</v>
       </c>
       <c r="P14">
-        <v>38.262306368</v>
+        <v>37.984165232</v>
       </c>
       <c r="Q14">
-        <v>87.262306368</v>
+        <v>86.984165232</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07767022557657677</v>
+        <v>0.07796370653065796</v>
       </c>
       <c r="T14">
-        <v>0.7360329232465767</v>
+        <v>0.7428107743800914</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.46369636840294</v>
+        <v>11.5049504939104</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07308094468167242</v>
+        <v>0.07296361085595729</v>
       </c>
       <c r="C15">
-        <v>499.0079897738098</v>
+        <v>494.0077334508132</v>
       </c>
       <c r="D15">
-        <v>436.0999897738098</v>
+        <v>437.9837334508132</v>
       </c>
       <c r="E15">
-        <v>-415.908</v>
+        <v>-409.024</v>
       </c>
       <c r="F15">
-        <v>89.492</v>
+        <v>96.376</v>
       </c>
       <c r="G15">
         <v>152.4</v>
@@ -2517,28 +2517,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M15">
-        <v>4.6356856</v>
+        <v>4.9922768</v>
       </c>
       <c r="N15">
-        <v>48.69764773333333</v>
+        <v>48.34105653333333</v>
       </c>
       <c r="O15">
-        <v>10.71348250133333</v>
+        <v>10.63503243733333</v>
       </c>
       <c r="P15">
-        <v>37.984165232</v>
+        <v>37.70602409599999</v>
       </c>
       <c r="Q15">
-        <v>86.984165232</v>
+        <v>86.70602409599999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07796370653065796</v>
+        <v>0.07826401262320615</v>
       </c>
       <c r="T15">
-        <v>0.7428107743800914</v>
+        <v>0.7497462499585716</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.5049504939104</v>
+        <v>10.68316831577394</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07296361085595729</v>
+        <v>0.07284627703024216</v>
       </c>
       <c r="C16">
-        <v>494.0077334508132</v>
+        <v>489.0238214736239</v>
       </c>
       <c r="D16">
-        <v>437.9837334508132</v>
+        <v>439.8838214736239</v>
       </c>
       <c r="E16">
-        <v>-409.024</v>
+        <v>-402.14</v>
       </c>
       <c r="F16">
-        <v>96.376</v>
+        <v>103.26</v>
       </c>
       <c r="G16">
         <v>152.4</v>
@@ -2599,28 +2599,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M16">
-        <v>4.9922768</v>
+        <v>5.348868</v>
       </c>
       <c r="N16">
-        <v>48.34105653333333</v>
+        <v>47.98446533333333</v>
       </c>
       <c r="O16">
-        <v>10.63503243733333</v>
+        <v>10.55658237333333</v>
       </c>
       <c r="P16">
-        <v>37.70602409599999</v>
+        <v>37.42788295999999</v>
       </c>
       <c r="Q16">
-        <v>86.70602409599999</v>
+        <v>86.42788295999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07826401262320615</v>
+        <v>0.07857138474146136</v>
       </c>
       <c r="T16">
-        <v>0.7497462499585716</v>
+        <v>0.756844913197722</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.68316831577394</v>
+        <v>9.970957094722346</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07284627703024216</v>
+        <v>0.07294110320452701</v>
       </c>
       <c r="C17">
-        <v>489.0238214736239</v>
+        <v>480.6029458497476</v>
       </c>
       <c r="D17">
-        <v>439.8838214736239</v>
+        <v>438.3469458497476</v>
       </c>
       <c r="E17">
-        <v>-402.14</v>
+        <v>-395.256</v>
       </c>
       <c r="F17">
-        <v>103.26</v>
+        <v>110.144</v>
       </c>
       <c r="G17">
         <v>152.4</v>
@@ -2681,45 +2681,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M17">
-        <v>5.348868</v>
+        <v>5.892704</v>
       </c>
       <c r="N17">
-        <v>47.98446533333333</v>
+        <v>47.44062933333333</v>
       </c>
       <c r="O17">
-        <v>10.55658237333333</v>
+        <v>10.43693845333333</v>
       </c>
       <c r="P17">
-        <v>37.42788296</v>
+        <v>37.00369087999999</v>
       </c>
       <c r="Q17">
-        <v>86.42788296000001</v>
+        <v>86.00369087999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07857138474146136</v>
+        <v>0.07888607524348455</v>
       </c>
       <c r="T17">
-        <v>0.756844913197722</v>
+        <v>0.7641125922282807</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.970957094722348</v>
+        <v>9.050740260045869</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07294110320452701</v>
+        <v>0.0728370293788119</v>
       </c>
       <c r="C18">
-        <v>480.6029458497476</v>
+        <v>475.4062778049687</v>
       </c>
       <c r="D18">
-        <v>438.3469458497476</v>
+        <v>440.0342778049687</v>
       </c>
       <c r="E18">
-        <v>-395.256</v>
+        <v>-388.372</v>
       </c>
       <c r="F18">
-        <v>110.144</v>
+        <v>117.028</v>
       </c>
       <c r="G18">
         <v>152.4</v>
@@ -2763,28 +2763,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M18">
-        <v>5.892704</v>
+        <v>6.260998</v>
       </c>
       <c r="N18">
-        <v>47.44062933333333</v>
+        <v>47.07233533333333</v>
       </c>
       <c r="O18">
-        <v>10.43693845333333</v>
+        <v>10.35591377333333</v>
       </c>
       <c r="P18">
-        <v>37.00369087999999</v>
+        <v>36.71642155999999</v>
       </c>
       <c r="Q18">
-        <v>86.00369087999999</v>
+        <v>85.71642155999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07888607524348455</v>
+        <v>0.07920834864917095</v>
       </c>
       <c r="T18">
-        <v>0.7641125922282807</v>
+        <v>0.7715553960547565</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.050740260045869</v>
+        <v>8.518343774160817</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0728370293788119</v>
+        <v>0.07273295555309675</v>
       </c>
       <c r="C19">
-        <v>475.4062778049687</v>
+        <v>470.2226500736816</v>
       </c>
       <c r="D19">
-        <v>440.0342778049687</v>
+        <v>441.7346500736816</v>
       </c>
       <c r="E19">
-        <v>-388.372</v>
+        <v>-381.4879999999999</v>
       </c>
       <c r="F19">
-        <v>117.028</v>
+        <v>123.912</v>
       </c>
       <c r="G19">
         <v>152.4</v>
@@ -2845,28 +2845,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M19">
-        <v>6.260998</v>
+        <v>6.629292</v>
       </c>
       <c r="N19">
-        <v>47.07233533333333</v>
+        <v>46.70404133333333</v>
       </c>
       <c r="O19">
-        <v>10.35591377333333</v>
+        <v>10.27488909333333</v>
       </c>
       <c r="P19">
-        <v>36.71642155999999</v>
+        <v>36.42915223999999</v>
       </c>
       <c r="Q19">
-        <v>85.71642155999999</v>
+        <v>85.42915223999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07920834864917095</v>
+        <v>0.07953848238182532</v>
       </c>
       <c r="T19">
-        <v>0.7715553960547565</v>
+        <v>0.7791797316818782</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.518343774160817</v>
+        <v>8.045102453374104</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07273295555309676</v>
+        <v>0.07262888172738163</v>
       </c>
       <c r="C20">
-        <v>470.2226500736815</v>
+        <v>465.0522144127117</v>
       </c>
       <c r="D20">
-        <v>441.7346500736814</v>
+        <v>443.4482144127118</v>
       </c>
       <c r="E20">
-        <v>-381.488</v>
+        <v>-374.604</v>
       </c>
       <c r="F20">
-        <v>123.912</v>
+        <v>130.796</v>
       </c>
       <c r="G20">
         <v>152.4</v>
@@ -2927,28 +2927,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M20">
-        <v>6.629292</v>
+        <v>6.997585999999999</v>
       </c>
       <c r="N20">
-        <v>46.70404133333333</v>
+        <v>46.33574733333333</v>
       </c>
       <c r="O20">
-        <v>10.27488909333333</v>
+        <v>10.19386441333333</v>
       </c>
       <c r="P20">
-        <v>36.42915223999999</v>
+        <v>36.14188292</v>
       </c>
       <c r="Q20">
-        <v>85.42915223999999</v>
+        <v>85.14188292</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07953848238182532</v>
+        <v>0.07987676756466867</v>
       </c>
       <c r="T20">
-        <v>0.7791797316818779</v>
+        <v>0.7869923225096692</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.045102453374106</v>
+        <v>7.62167600845968</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07262888172738163</v>
+        <v>0.07264960790166651</v>
       </c>
       <c r="C21">
-        <v>465.0522144127117</v>
+        <v>457.8259008485101</v>
       </c>
       <c r="D21">
-        <v>443.4482144127118</v>
+        <v>443.1059008485101</v>
       </c>
       <c r="E21">
-        <v>-374.604</v>
+        <v>-367.72</v>
       </c>
       <c r="F21">
-        <v>130.796</v>
+        <v>137.68</v>
       </c>
       <c r="G21">
         <v>152.4</v>
@@ -3009,45 +3009,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M21">
-        <v>6.997585999999999</v>
+        <v>7.476024000000001</v>
       </c>
       <c r="N21">
-        <v>46.33574733333333</v>
+        <v>45.85730933333333</v>
       </c>
       <c r="O21">
-        <v>10.19386441333333</v>
+        <v>10.08860805333333</v>
       </c>
       <c r="P21">
-        <v>36.14188292</v>
+        <v>35.76870127999999</v>
       </c>
       <c r="Q21">
-        <v>85.14188292</v>
+        <v>84.76870127999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07987676756466867</v>
+        <v>0.08022350987708313</v>
       </c>
       <c r="T21">
-        <v>0.7869923225096692</v>
+        <v>0.7950002281081553</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.62167600845968</v>
+        <v>7.133916816389744</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07264960790166651</v>
+        <v>0.07255177407595137</v>
       </c>
       <c r="C22">
-        <v>457.8259008485101</v>
+        <v>452.5623819931955</v>
       </c>
       <c r="D22">
-        <v>443.1059008485101</v>
+        <v>444.7263819931956</v>
       </c>
       <c r="E22">
-        <v>-367.72</v>
+        <v>-360.836</v>
       </c>
       <c r="F22">
-        <v>137.68</v>
+        <v>144.564</v>
       </c>
       <c r="G22">
         <v>152.4</v>
@@ -3091,28 +3091,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M22">
-        <v>7.476024000000001</v>
+        <v>7.849825200000002</v>
       </c>
       <c r="N22">
-        <v>45.85730933333333</v>
+        <v>45.48350813333333</v>
       </c>
       <c r="O22">
-        <v>10.08860805333333</v>
+        <v>10.00637178933333</v>
       </c>
       <c r="P22">
-        <v>35.76870127999999</v>
+        <v>35.477136344</v>
       </c>
       <c r="Q22">
-        <v>84.76870127999999</v>
+        <v>84.477136344</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08022350987708313</v>
+        <v>0.0805790304758878</v>
       </c>
       <c r="T22">
-        <v>0.7950002281081553</v>
+        <v>0.8032108654939447</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.133916816389744</v>
+        <v>6.794206491799756</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07255177407595137</v>
+        <v>0.07245394025023623</v>
       </c>
       <c r="C23">
-        <v>452.5623819931956</v>
+        <v>447.310759155385</v>
       </c>
       <c r="D23">
-        <v>444.7263819931956</v>
+        <v>446.358759155385</v>
       </c>
       <c r="E23">
-        <v>-360.836</v>
+        <v>-353.952</v>
       </c>
       <c r="F23">
-        <v>144.564</v>
+        <v>151.448</v>
       </c>
       <c r="G23">
         <v>152.4</v>
@@ -3173,28 +3173,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M23">
-        <v>7.8498252</v>
+        <v>8.223626400000001</v>
       </c>
       <c r="N23">
-        <v>45.48350813333333</v>
+        <v>45.10970693333333</v>
       </c>
       <c r="O23">
-        <v>10.00637178933333</v>
+        <v>9.924135525333332</v>
       </c>
       <c r="P23">
-        <v>35.477136344</v>
+        <v>35.18557140799999</v>
       </c>
       <c r="Q23">
-        <v>84.477136344</v>
+        <v>84.18557140799999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0805790304758878</v>
+        <v>0.08094366698748234</v>
       </c>
       <c r="T23">
-        <v>0.8032108654939446</v>
+        <v>0.8116320320434722</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.794206491799758</v>
+        <v>6.485378923990677</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07245394025023623</v>
+        <v>0.0723561064245211</v>
       </c>
       <c r="C24">
-        <v>447.310759155385</v>
+        <v>442.0711638113818</v>
       </c>
       <c r="D24">
-        <v>446.358759155385</v>
+        <v>448.0031638113817</v>
       </c>
       <c r="E24">
-        <v>-353.952</v>
+        <v>-347.068</v>
       </c>
       <c r="F24">
-        <v>151.448</v>
+        <v>158.332</v>
       </c>
       <c r="G24">
         <v>152.4</v>
@@ -3255,28 +3255,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M24">
-        <v>8.223626400000001</v>
+        <v>8.5974276</v>
       </c>
       <c r="N24">
-        <v>45.10970693333333</v>
+        <v>44.73590573333333</v>
       </c>
       <c r="O24">
-        <v>9.924135525333332</v>
+        <v>9.841899261333332</v>
       </c>
       <c r="P24">
-        <v>35.18557140799999</v>
+        <v>34.89400647199999</v>
       </c>
       <c r="Q24">
-        <v>84.18557140799999</v>
+        <v>83.894006472</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08094366698748234</v>
+        <v>0.08131777457730013</v>
       </c>
       <c r="T24">
-        <v>0.8116320320434722</v>
+        <v>0.820271930191689</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.485378923990677</v>
+        <v>6.203405927295431</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0723561064245211</v>
+        <v>0.07244547259880596</v>
       </c>
       <c r="C25">
-        <v>442.0711638113818</v>
+        <v>433.6846072825427</v>
       </c>
       <c r="D25">
-        <v>448.0031638113817</v>
+        <v>446.5006072825427</v>
       </c>
       <c r="E25">
-        <v>-347.068</v>
+        <v>-340.184</v>
       </c>
       <c r="F25">
-        <v>158.332</v>
+        <v>165.216</v>
       </c>
       <c r="G25">
         <v>152.4</v>
@@ -3337,45 +3337,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M25">
-        <v>8.5974276</v>
+        <v>9.136444800000001</v>
       </c>
       <c r="N25">
-        <v>44.73590573333333</v>
+        <v>44.19688853333333</v>
       </c>
       <c r="O25">
-        <v>9.841899261333332</v>
+        <v>9.723315477333333</v>
       </c>
       <c r="P25">
-        <v>34.89400647199999</v>
+        <v>34.47357305599999</v>
       </c>
       <c r="Q25">
-        <v>83.894006472</v>
+        <v>83.47357305599999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08131777457730013</v>
+        <v>0.08170172710369206</v>
       </c>
       <c r="T25">
-        <v>0.820271930191689</v>
+        <v>0.8291391940806482</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.203405927295431</v>
+        <v>5.837427413049475</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07244547259880596</v>
+        <v>0.07235543877309084</v>
       </c>
       <c r="C26">
-        <v>433.6846072825427</v>
+        <v>428.3144274156339</v>
       </c>
       <c r="D26">
-        <v>446.5006072825427</v>
+        <v>448.0144274156339</v>
       </c>
       <c r="E26">
-        <v>-340.184</v>
+        <v>-333.3</v>
       </c>
       <c r="F26">
-        <v>165.216</v>
+        <v>172.1</v>
       </c>
       <c r="G26">
         <v>152.4</v>
@@ -3419,28 +3419,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M26">
-        <v>9.1364448</v>
+        <v>9.51713</v>
       </c>
       <c r="N26">
-        <v>44.19688853333333</v>
+        <v>43.81620333333333</v>
       </c>
       <c r="O26">
-        <v>9.723315477333333</v>
+        <v>9.639564733333332</v>
       </c>
       <c r="P26">
-        <v>34.47357305599999</v>
+        <v>34.1766386</v>
       </c>
       <c r="Q26">
-        <v>83.47357305599999</v>
+        <v>83.17663859999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08170172710369206</v>
+        <v>0.08209591836412111</v>
       </c>
       <c r="T26">
-        <v>0.8291391940806482</v>
+        <v>0.8382429183399795</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.837427413049475</v>
+        <v>5.603930316527496</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07235543877309084</v>
+        <v>0.0722654049473757</v>
       </c>
       <c r="C27">
-        <v>428.3144274156339</v>
+        <v>422.9545474113797</v>
       </c>
       <c r="D27">
-        <v>448.0144274156339</v>
+        <v>449.5385474113798</v>
       </c>
       <c r="E27">
-        <v>-333.3</v>
+        <v>-326.4159999999999</v>
       </c>
       <c r="F27">
-        <v>172.1</v>
+        <v>178.984</v>
       </c>
       <c r="G27">
         <v>152.4</v>
@@ -3501,28 +3501,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M27">
-        <v>9.51713</v>
+        <v>9.8978152</v>
       </c>
       <c r="N27">
-        <v>43.81620333333333</v>
+        <v>43.43551813333333</v>
       </c>
       <c r="O27">
-        <v>9.639564733333332</v>
+        <v>9.555813989333332</v>
       </c>
       <c r="P27">
-        <v>34.1766386</v>
+        <v>33.879704144</v>
       </c>
       <c r="Q27">
-        <v>83.17663859999999</v>
+        <v>82.879704144</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08209591836412111</v>
+        <v>0.08250076344239959</v>
       </c>
       <c r="T27">
-        <v>0.8382429183399795</v>
+        <v>0.8475926892009146</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.603930316527496</v>
+        <v>5.388394535122592</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0722654049473757</v>
+        <v>0.07217537112166057</v>
       </c>
       <c r="C28">
-        <v>422.9545474113797</v>
+        <v>417.6050727472764</v>
       </c>
       <c r="D28">
-        <v>449.5385474113798</v>
+        <v>451.0730727472765</v>
       </c>
       <c r="E28">
-        <v>-326.4159999999999</v>
+        <v>-319.532</v>
       </c>
       <c r="F28">
-        <v>178.984</v>
+        <v>185.868</v>
       </c>
       <c r="G28">
         <v>152.4</v>
@@ -3583,28 +3583,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M28">
-        <v>9.8978152</v>
+        <v>10.2785004</v>
       </c>
       <c r="N28">
-        <v>43.43551813333333</v>
+        <v>43.05483293333333</v>
       </c>
       <c r="O28">
-        <v>9.555813989333332</v>
+        <v>9.472063245333333</v>
       </c>
       <c r="P28">
-        <v>33.879704144</v>
+        <v>33.582769688</v>
       </c>
       <c r="Q28">
-        <v>82.879704144</v>
+        <v>82.582769688</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08250076344239959</v>
+        <v>0.08291670016665832</v>
       </c>
       <c r="T28">
-        <v>0.8475926892009146</v>
+        <v>0.8571986181676287</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.388394535122592</v>
+        <v>5.188824367155089</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07217537112166057</v>
+        <v>0.07208533729594545</v>
       </c>
       <c r="C29">
-        <v>417.6050727472764</v>
+        <v>412.2661103459675</v>
       </c>
       <c r="D29">
-        <v>451.0730727472765</v>
+        <v>452.6181103459676</v>
       </c>
       <c r="E29">
-        <v>-319.532</v>
+        <v>-312.648</v>
       </c>
       <c r="F29">
-        <v>185.868</v>
+        <v>192.752</v>
       </c>
       <c r="G29">
         <v>152.4</v>
@@ -3665,28 +3665,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M29">
-        <v>10.2785004</v>
+        <v>10.6591856</v>
       </c>
       <c r="N29">
-        <v>43.05483293333333</v>
+        <v>42.67414773333333</v>
       </c>
       <c r="O29">
-        <v>9.472063245333333</v>
+        <v>9.388312501333333</v>
       </c>
       <c r="P29">
-        <v>33.582769688</v>
+        <v>33.285835232</v>
       </c>
       <c r="Q29">
-        <v>82.582769688</v>
+        <v>82.285835232</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08291670016665832</v>
+        <v>0.08334419068881312</v>
       </c>
       <c r="T29">
-        <v>0.8571986181676287</v>
+        <v>0.8670713784945292</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.188824367155089</v>
+        <v>5.003509211185264</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07208533729594545</v>
+        <v>0.07199530347023031</v>
       </c>
       <c r="C30">
-        <v>412.2661103459675</v>
+        <v>406.9377686000785</v>
       </c>
       <c r="D30">
-        <v>452.6181103459676</v>
+        <v>454.1737686000785</v>
       </c>
       <c r="E30">
-        <v>-312.648</v>
+        <v>-305.764</v>
       </c>
       <c r="F30">
-        <v>192.752</v>
+        <v>199.636</v>
       </c>
       <c r="G30">
         <v>152.4</v>
@@ -3747,28 +3747,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M30">
-        <v>10.6591856</v>
+        <v>11.0398708</v>
       </c>
       <c r="N30">
-        <v>42.67414773333333</v>
+        <v>42.29346253333333</v>
       </c>
       <c r="O30">
-        <v>9.388312501333333</v>
+        <v>9.304561757333332</v>
       </c>
       <c r="P30">
-        <v>33.285835232</v>
+        <v>32.98890077599999</v>
       </c>
       <c r="Q30">
-        <v>82.285835232</v>
+        <v>81.98890077599999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08334419068881312</v>
+        <v>0.08378372319750747</v>
       </c>
       <c r="T30">
-        <v>0.8670713784945292</v>
+        <v>0.8772222447461311</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.003509211185264</v>
+        <v>4.830974410799564</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07199530347023031</v>
+        <v>0.07190526964451517</v>
       </c>
       <c r="C31">
-        <v>406.9377686000786</v>
+        <v>401.6201573975648</v>
       </c>
       <c r="D31">
-        <v>454.1737686000785</v>
+        <v>455.7401573975648</v>
       </c>
       <c r="E31">
-        <v>-305.764</v>
+        <v>-298.88</v>
       </c>
       <c r="F31">
-        <v>199.636</v>
+        <v>206.52</v>
       </c>
       <c r="G31">
         <v>152.4</v>
@@ -3829,28 +3829,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M31">
-        <v>11.0398708</v>
+        <v>11.420556</v>
       </c>
       <c r="N31">
-        <v>42.29346253333333</v>
+        <v>41.91277733333333</v>
       </c>
       <c r="O31">
-        <v>9.304561757333332</v>
+        <v>9.220811013333332</v>
       </c>
       <c r="P31">
-        <v>32.98890077599999</v>
+        <v>32.69196632</v>
       </c>
       <c r="Q31">
-        <v>81.98890077599999</v>
+        <v>81.69196632000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08378372319750747</v>
+        <v>0.08423581377787881</v>
       </c>
       <c r="T31">
-        <v>0.8772222447461311</v>
+        <v>0.8876631357477788</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.830974410799566</v>
+        <v>4.669941930439581</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07190526964451517</v>
+        <v>0.07181523581880003</v>
       </c>
       <c r="C32">
-        <v>401.6201573975648</v>
+        <v>396.3133881475883</v>
       </c>
       <c r="D32">
-        <v>455.7401573975648</v>
+        <v>457.3173881475882</v>
       </c>
       <c r="E32">
-        <v>-298.88</v>
+        <v>-291.996</v>
       </c>
       <c r="F32">
-        <v>206.52</v>
+        <v>213.404</v>
       </c>
       <c r="G32">
         <v>152.4</v>
@@ -3911,28 +3911,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M32">
-        <v>11.420556</v>
+        <v>11.8012412</v>
       </c>
       <c r="N32">
-        <v>41.91277733333333</v>
+        <v>41.53209213333333</v>
       </c>
       <c r="O32">
-        <v>9.220811013333332</v>
+        <v>9.137060269333332</v>
       </c>
       <c r="P32">
-        <v>32.69196632</v>
+        <v>32.395031864</v>
       </c>
       <c r="Q32">
-        <v>81.69196632000001</v>
+        <v>81.395031864</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08423581377787881</v>
+        <v>0.08470100843304354</v>
       </c>
       <c r="T32">
-        <v>0.8876631357477788</v>
+        <v>0.8984066612712135</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.669941930439581</v>
+        <v>4.519298642360884</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07181523581880003</v>
+        <v>0.07234920199308492</v>
       </c>
       <c r="C33">
-        <v>396.3133881475883</v>
+        <v>380.2316722898111</v>
       </c>
       <c r="D33">
-        <v>457.3173881475882</v>
+        <v>448.1196722898111</v>
       </c>
       <c r="E33">
-        <v>-291.996</v>
+        <v>-285.112</v>
       </c>
       <c r="F33">
-        <v>213.404</v>
+        <v>220.288</v>
       </c>
       <c r="G33">
         <v>152.4</v>
@@ -3993,45 +3993,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M33">
-        <v>11.8012412</v>
+        <v>12.7326464</v>
       </c>
       <c r="N33">
-        <v>41.53209213333333</v>
+        <v>40.60068693333333</v>
       </c>
       <c r="O33">
-        <v>9.137060269333332</v>
+        <v>8.932151125333332</v>
       </c>
       <c r="P33">
-        <v>32.395031864</v>
+        <v>31.66853580799999</v>
       </c>
       <c r="Q33">
-        <v>81.395031864</v>
+        <v>80.668535808</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08470100843304354</v>
+        <v>0.0851798852839484</v>
       </c>
       <c r="T33">
-        <v>0.8984066612712135</v>
+        <v>0.9094661728394551</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.519298642360884</v>
+        <v>4.188707646301504</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07234920199308492</v>
+        <v>0.07227866816736978</v>
       </c>
       <c r="C34">
-        <v>380.2316722898111</v>
+        <v>374.5413726173739</v>
       </c>
       <c r="D34">
-        <v>448.1196722898111</v>
+        <v>449.3133726173739</v>
       </c>
       <c r="E34">
-        <v>-285.112</v>
+        <v>-278.228</v>
       </c>
       <c r="F34">
-        <v>220.288</v>
+        <v>227.172</v>
       </c>
       <c r="G34">
         <v>152.4</v>
@@ -4075,28 +4075,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M34">
-        <v>12.7326464</v>
+        <v>13.1305416</v>
       </c>
       <c r="N34">
-        <v>40.60068693333333</v>
+        <v>40.20279173333333</v>
       </c>
       <c r="O34">
-        <v>8.932151125333332</v>
+        <v>8.844614181333332</v>
       </c>
       <c r="P34">
-        <v>31.66853580799999</v>
+        <v>31.35817755199999</v>
       </c>
       <c r="Q34">
-        <v>80.668535808</v>
+        <v>80.358177552</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0851798852839484</v>
+        <v>0.08567305696622354</v>
       </c>
       <c r="T34">
-        <v>0.9094661728394551</v>
+        <v>0.9208558190813754</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.188707646301504</v>
+        <v>4.061777111565095</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07227866816736978</v>
+        <v>0.07313633434165465</v>
       </c>
       <c r="C35">
-        <v>374.5413726173739</v>
+        <v>353.5603515416341</v>
       </c>
       <c r="D35">
-        <v>449.3133726173739</v>
+        <v>435.2163515416341</v>
       </c>
       <c r="E35">
-        <v>-278.228</v>
+        <v>-271.3439999999999</v>
       </c>
       <c r="F35">
-        <v>227.172</v>
+        <v>234.056</v>
       </c>
       <c r="G35">
         <v>152.4</v>
@@ -4157,45 +4157,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M35">
-        <v>13.1305416</v>
+        <v>14.3476328</v>
       </c>
       <c r="N35">
-        <v>40.20279173333333</v>
+        <v>38.98570053333333</v>
       </c>
       <c r="O35">
-        <v>8.844614181333332</v>
+        <v>8.576854117333333</v>
       </c>
       <c r="P35">
-        <v>31.35817755199999</v>
+        <v>30.408846416</v>
       </c>
       <c r="Q35">
-        <v>80.358177552</v>
+        <v>79.40884641599999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08567305696622354</v>
+        <v>0.08618117324493128</v>
       </c>
       <c r="T35">
-        <v>0.9208558190813754</v>
+        <v>0.9325906061185054</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.061777111565095</v>
+        <v>3.717221793781433</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07313633434165465</v>
+        <v>0.07309310051593951</v>
       </c>
       <c r="C36">
-        <v>353.5603515416341</v>
+        <v>347.3657590305319</v>
       </c>
       <c r="D36">
-        <v>435.2163515416341</v>
+        <v>435.905759030532</v>
       </c>
       <c r="E36">
-        <v>-271.3439999999999</v>
+        <v>-264.4599999999999</v>
       </c>
       <c r="F36">
-        <v>234.056</v>
+        <v>240.94</v>
       </c>
       <c r="G36">
         <v>152.4</v>
@@ -4239,28 +4239,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M36">
-        <v>14.3476328</v>
+        <v>14.769622</v>
       </c>
       <c r="N36">
-        <v>38.98570053333333</v>
+        <v>38.56371133333333</v>
       </c>
       <c r="O36">
-        <v>8.576854117333333</v>
+        <v>8.484016493333332</v>
       </c>
       <c r="P36">
-        <v>30.408846416</v>
+        <v>30.07969484</v>
       </c>
       <c r="Q36">
-        <v>79.40884641599999</v>
+        <v>79.07969484</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08618117324493128</v>
+        <v>0.08670492387067619</v>
       </c>
       <c r="T36">
-        <v>0.9325906061185054</v>
+        <v>0.9446864635260088</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.717221793781433</v>
+        <v>3.611015456816249</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07309310051593951</v>
+        <v>0.07304986669022438</v>
       </c>
       <c r="C37">
-        <v>347.3657590305319</v>
+        <v>341.1733541061478</v>
       </c>
       <c r="D37">
-        <v>435.905759030532</v>
+        <v>436.5973541061477</v>
       </c>
       <c r="E37">
-        <v>-264.4599999999999</v>
+        <v>-257.576</v>
       </c>
       <c r="F37">
-        <v>240.94</v>
+        <v>247.824</v>
       </c>
       <c r="G37">
         <v>152.4</v>
@@ -4321,28 +4321,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M37">
-        <v>14.769622</v>
+        <v>15.1916112</v>
       </c>
       <c r="N37">
-        <v>38.56371133333333</v>
+        <v>38.14172213333333</v>
       </c>
       <c r="O37">
-        <v>8.484016493333332</v>
+        <v>8.391178869333332</v>
       </c>
       <c r="P37">
-        <v>30.07969484</v>
+        <v>29.750543264</v>
       </c>
       <c r="Q37">
-        <v>79.07969484</v>
+        <v>78.750543264</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08670492387067619</v>
+        <v>0.08724504170347561</v>
       </c>
       <c r="T37">
-        <v>0.9446864635260088</v>
+        <v>0.9571603164774967</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.611015456816249</v>
+        <v>3.510709471904687</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07304986669022438</v>
+        <v>0.07381471286450925</v>
       </c>
       <c r="C38">
-        <v>341.1733541061478</v>
+        <v>322.3695526216205</v>
       </c>
       <c r="D38">
-        <v>436.5973541061477</v>
+        <v>424.6775526216205</v>
       </c>
       <c r="E38">
-        <v>-257.576</v>
+        <v>-250.692</v>
       </c>
       <c r="F38">
-        <v>247.824</v>
+        <v>254.708</v>
       </c>
       <c r="G38">
         <v>152.4</v>
@@ -4403,45 +4403,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M38">
-        <v>15.1916112</v>
+        <v>16.3267828</v>
       </c>
       <c r="N38">
-        <v>38.14172213333333</v>
+        <v>37.00655053333332</v>
       </c>
       <c r="O38">
-        <v>8.391178869333332</v>
+        <v>8.141441117333331</v>
       </c>
       <c r="P38">
-        <v>29.750543264</v>
+        <v>28.865109416</v>
       </c>
       <c r="Q38">
-        <v>78.750543264</v>
+        <v>77.865109416</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08724504170347559</v>
+        <v>0.08780230613414167</v>
       </c>
       <c r="T38">
-        <v>0.9571603164774964</v>
+        <v>0.9700301647607775</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.510709471904688</v>
+        <v>3.266616208879396</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07381471286450925</v>
+        <v>0.07379331903879413</v>
       </c>
       <c r="C39">
-        <v>322.3695526216205</v>
+        <v>315.8101114041399</v>
       </c>
       <c r="D39">
-        <v>424.6775526216205</v>
+        <v>425.0021114041399</v>
       </c>
       <c r="E39">
-        <v>-250.692</v>
+        <v>-243.808</v>
       </c>
       <c r="F39">
-        <v>254.708</v>
+        <v>261.592</v>
       </c>
       <c r="G39">
         <v>152.4</v>
@@ -4485,28 +4485,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M39">
-        <v>16.3267828</v>
+        <v>16.7680472</v>
       </c>
       <c r="N39">
-        <v>37.00655053333332</v>
+        <v>36.56528613333333</v>
       </c>
       <c r="O39">
-        <v>8.141441117333331</v>
+        <v>8.044362949333333</v>
       </c>
       <c r="P39">
-        <v>28.865109416</v>
+        <v>28.520923184</v>
       </c>
       <c r="Q39">
-        <v>77.865109416</v>
+        <v>77.520923184</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08780230613414167</v>
+        <v>0.08837754683676471</v>
       </c>
       <c r="T39">
-        <v>0.9700301647607775</v>
+        <v>0.9833151694402935</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.266616208879396</v>
+        <v>3.180652624435201</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07379331903879413</v>
+        <v>0.07377192521307899</v>
       </c>
       <c r="C40">
-        <v>315.8101114041399</v>
+        <v>309.2511666525966</v>
       </c>
       <c r="D40">
-        <v>425.0021114041399</v>
+        <v>425.3271666525965</v>
       </c>
       <c r="E40">
-        <v>-243.808</v>
+        <v>-236.924</v>
       </c>
       <c r="F40">
-        <v>261.592</v>
+        <v>268.476</v>
       </c>
       <c r="G40">
         <v>152.4</v>
@@ -4567,28 +4567,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M40">
-        <v>16.7680472</v>
+        <v>17.2093116</v>
       </c>
       <c r="N40">
-        <v>36.56528613333333</v>
+        <v>36.12402173333333</v>
       </c>
       <c r="O40">
-        <v>8.044362949333333</v>
+        <v>7.947284781333332</v>
       </c>
       <c r="P40">
-        <v>28.520923184</v>
+        <v>28.176736952</v>
       </c>
       <c r="Q40">
-        <v>77.520923184</v>
+        <v>77.176736952</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08837754683676471</v>
+        <v>0.08897164789029341</v>
       </c>
       <c r="T40">
-        <v>0.9833151694402935</v>
+        <v>0.997035748043728</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.180652624435201</v>
+        <v>3.099097428936863</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07377192521307899</v>
+        <v>0.07375053138736386</v>
       </c>
       <c r="C41">
-        <v>309.2511666525966</v>
+        <v>302.692719507001</v>
       </c>
       <c r="D41">
-        <v>425.3271666525965</v>
+        <v>425.652719507001</v>
       </c>
       <c r="E41">
-        <v>-236.924</v>
+        <v>-230.04</v>
       </c>
       <c r="F41">
-        <v>268.476</v>
+        <v>275.36</v>
       </c>
       <c r="G41">
         <v>152.4</v>
@@ -4649,28 +4649,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M41">
-        <v>17.2093116</v>
+        <v>17.650576</v>
       </c>
       <c r="N41">
-        <v>36.12402173333333</v>
+        <v>35.68275733333333</v>
       </c>
       <c r="O41">
-        <v>7.947284781333332</v>
+        <v>7.850206613333332</v>
       </c>
       <c r="P41">
-        <v>28.176736952</v>
+        <v>27.83255072</v>
       </c>
       <c r="Q41">
-        <v>77.176736952</v>
+        <v>76.83255072</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08897164789029341</v>
+        <v>0.0895855523122731</v>
       </c>
       <c r="T41">
-        <v>0.997035748043728</v>
+        <v>1.011213679267277</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.099097428936863</v>
+        <v>3.021619993213441</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07375053138736386</v>
+        <v>0.07622357756164873</v>
       </c>
       <c r="C42">
-        <v>302.692719507001</v>
+        <v>261.2086193899885</v>
       </c>
       <c r="D42">
-        <v>425.652719507001</v>
+        <v>391.0526193899885</v>
       </c>
       <c r="E42">
-        <v>-230.04</v>
+        <v>-223.1559999999999</v>
       </c>
       <c r="F42">
-        <v>275.36</v>
+        <v>282.244</v>
       </c>
       <c r="G42">
         <v>152.4</v>
@@ -4731,45 +4731,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M42">
-        <v>17.650576</v>
+        <v>20.2933436</v>
       </c>
       <c r="N42">
-        <v>35.68275733333333</v>
+        <v>33.03998973333333</v>
       </c>
       <c r="O42">
-        <v>7.850206613333332</v>
+        <v>7.268797741333333</v>
       </c>
       <c r="P42">
-        <v>27.83255072</v>
+        <v>25.77119199199999</v>
       </c>
       <c r="Q42">
-        <v>76.83255072</v>
+        <v>74.771191992</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0895855523122731</v>
+        <v>0.0902202670536419</v>
       </c>
       <c r="T42">
-        <v>1.011213679267277</v>
+        <v>1.025872218328912</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.021619993213441</v>
+        <v>2.628119563960535</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07622357756164873</v>
+        <v>0.07626302373593359</v>
       </c>
       <c r="C43">
-        <v>261.2086193899885</v>
+        <v>253.8182504256754</v>
       </c>
       <c r="D43">
-        <v>391.0526193899885</v>
+        <v>390.5462504256755</v>
       </c>
       <c r="E43">
-        <v>-223.1559999999999</v>
+        <v>-216.2719999999999</v>
       </c>
       <c r="F43">
-        <v>282.244</v>
+        <v>289.128</v>
       </c>
       <c r="G43">
         <v>152.4</v>
@@ -4813,28 +4813,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M43">
-        <v>20.2933436</v>
+        <v>20.7883032</v>
       </c>
       <c r="N43">
-        <v>33.03998973333333</v>
+        <v>32.54503013333333</v>
       </c>
       <c r="O43">
-        <v>7.268797741333333</v>
+        <v>7.159906629333332</v>
       </c>
       <c r="P43">
-        <v>25.77119199199999</v>
+        <v>25.385123504</v>
       </c>
       <c r="Q43">
-        <v>74.771191992</v>
+        <v>74.38512350399999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0902202670536419</v>
+        <v>0.09087686851023033</v>
       </c>
       <c r="T43">
-        <v>1.025872218328912</v>
+        <v>1.041036224254742</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.628119563960535</v>
+        <v>2.565545288628142</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0762630237359336</v>
+        <v>0.07630246991021847</v>
       </c>
       <c r="C44">
-        <v>253.8182504256752</v>
+        <v>246.4291911466747</v>
       </c>
       <c r="D44">
-        <v>390.5462504256752</v>
+        <v>390.0411911466747</v>
       </c>
       <c r="E44">
-        <v>-216.272</v>
+        <v>-209.388</v>
       </c>
       <c r="F44">
-        <v>289.128</v>
+        <v>296.012</v>
       </c>
       <c r="G44">
         <v>152.4</v>
@@ -4895,28 +4895,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M44">
-        <v>20.7883032</v>
+        <v>21.2832628</v>
       </c>
       <c r="N44">
-        <v>32.54503013333333</v>
+        <v>32.05007053333333</v>
       </c>
       <c r="O44">
-        <v>7.159906629333332</v>
+        <v>7.051015517333331</v>
       </c>
       <c r="P44">
-        <v>25.385123504</v>
+        <v>24.99905501599999</v>
       </c>
       <c r="Q44">
-        <v>74.38512350399999</v>
+        <v>73.999055016</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09087686851023033</v>
+        <v>0.09155650861441836</v>
       </c>
       <c r="T44">
-        <v>1.041036224254742</v>
+        <v>1.056732300563934</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.565545288628142</v>
+        <v>2.505881444706557</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07630246991021847</v>
+        <v>0.07768039608450333</v>
       </c>
       <c r="C45">
-        <v>246.4291911466747</v>
+        <v>222.686932394002</v>
       </c>
       <c r="D45">
-        <v>390.0411911466747</v>
+        <v>373.182932394002</v>
       </c>
       <c r="E45">
-        <v>-209.388</v>
+        <v>-202.504</v>
       </c>
       <c r="F45">
-        <v>296.012</v>
+        <v>302.896</v>
       </c>
       <c r="G45">
         <v>152.4</v>
@@ -4977,45 +4977,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M45">
-        <v>21.2832628</v>
+        <v>22.9595168</v>
       </c>
       <c r="N45">
-        <v>32.05007053333333</v>
+        <v>30.37381653333333</v>
       </c>
       <c r="O45">
-        <v>7.051015517333331</v>
+        <v>6.682239637333332</v>
       </c>
       <c r="P45">
-        <v>24.99905501599999</v>
+        <v>23.69157689599999</v>
       </c>
       <c r="Q45">
-        <v>73.999055016</v>
+        <v>72.69157689599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09155650861441836</v>
+        <v>0.09226042157947023</v>
       </c>
       <c r="T45">
-        <v>1.056732300563934</v>
+        <v>1.072988951027026</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.505881444706557</v>
+        <v>2.322929258395077</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07768039608450333</v>
+        <v>0.0777502622587882</v>
       </c>
       <c r="C46">
-        <v>222.686932394002</v>
+        <v>214.9868870174855</v>
       </c>
       <c r="D46">
-        <v>373.182932394002</v>
+        <v>372.3668870174855</v>
       </c>
       <c r="E46">
-        <v>-202.504</v>
+        <v>-195.62</v>
       </c>
       <c r="F46">
-        <v>302.896</v>
+        <v>309.78</v>
       </c>
       <c r="G46">
         <v>152.4</v>
@@ -5059,28 +5059,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M46">
-        <v>22.9595168</v>
+        <v>23.481324</v>
       </c>
       <c r="N46">
-        <v>30.37381653333333</v>
+        <v>29.85200933333333</v>
       </c>
       <c r="O46">
-        <v>6.682239637333332</v>
+        <v>6.567442053333332</v>
       </c>
       <c r="P46">
-        <v>23.69157689599999</v>
+        <v>23.28456728</v>
       </c>
       <c r="Q46">
-        <v>72.69157689599999</v>
+        <v>72.28456728</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09226042157947023</v>
+        <v>0.09298993137961489</v>
       </c>
       <c r="T46">
-        <v>1.072988951027026</v>
+        <v>1.089836752416048</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.322929258395077</v>
+        <v>2.27130860820852</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0777502622587882</v>
+        <v>0.07782012843307307</v>
       </c>
       <c r="C47">
-        <v>214.9868870174855</v>
+        <v>207.2904027739992</v>
       </c>
       <c r="D47">
-        <v>372.3668870174855</v>
+        <v>371.5544027739992</v>
       </c>
       <c r="E47">
-        <v>-195.62</v>
+        <v>-188.736</v>
       </c>
       <c r="F47">
-        <v>309.78</v>
+        <v>316.664</v>
       </c>
       <c r="G47">
         <v>152.4</v>
@@ -5141,28 +5141,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M47">
-        <v>23.481324</v>
+        <v>24.0031312</v>
       </c>
       <c r="N47">
-        <v>29.85200933333333</v>
+        <v>29.33020213333333</v>
       </c>
       <c r="O47">
-        <v>6.567442053333332</v>
+        <v>6.452644469333332</v>
       </c>
       <c r="P47">
-        <v>23.28456728</v>
+        <v>22.87755766399999</v>
       </c>
       <c r="Q47">
-        <v>72.28456728</v>
+        <v>71.87755766399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09298993137961489</v>
+        <v>0.0937464600612464</v>
       </c>
       <c r="T47">
-        <v>1.089836752416048</v>
+        <v>1.107308546449109</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.27130860820852</v>
+        <v>2.221932334117031</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07782012843307307</v>
+        <v>0.07788999460735793</v>
       </c>
       <c r="C48">
-        <v>207.2904027739992</v>
+        <v>199.5974564037008</v>
       </c>
       <c r="D48">
-        <v>371.5544027739992</v>
+        <v>370.7454564037008</v>
       </c>
       <c r="E48">
-        <v>-188.736</v>
+        <v>-181.852</v>
       </c>
       <c r="F48">
-        <v>316.664</v>
+        <v>323.548</v>
       </c>
       <c r="G48">
         <v>152.4</v>
@@ -5223,28 +5223,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M48">
-        <v>24.0031312</v>
+        <v>24.5249384</v>
       </c>
       <c r="N48">
-        <v>29.33020213333333</v>
+        <v>28.80839493333333</v>
       </c>
       <c r="O48">
-        <v>6.452644469333332</v>
+        <v>6.337846885333332</v>
       </c>
       <c r="P48">
-        <v>22.87755766399999</v>
+        <v>22.47054804799999</v>
       </c>
       <c r="Q48">
-        <v>71.87755766399999</v>
+        <v>71.470548048</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0937464600612464</v>
+        <v>0.09453153699501496</v>
       </c>
       <c r="T48">
-        <v>1.107308546449109</v>
+        <v>1.125439653464549</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.221932334117031</v>
+        <v>2.174657178071987</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07788999460735793</v>
+        <v>0.0779598607816428</v>
       </c>
       <c r="C49">
-        <v>199.5974564037008</v>
+        <v>191.9080248488724</v>
       </c>
       <c r="D49">
-        <v>370.7454564037008</v>
+        <v>369.9400248488724</v>
       </c>
       <c r="E49">
-        <v>-181.852</v>
+        <v>-174.968</v>
       </c>
       <c r="F49">
-        <v>323.548</v>
+        <v>330.432</v>
       </c>
       <c r="G49">
         <v>152.4</v>
@@ -5305,28 +5305,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M49">
-        <v>24.5249384</v>
+        <v>25.0467456</v>
       </c>
       <c r="N49">
-        <v>28.80839493333333</v>
+        <v>28.28658773333332</v>
       </c>
       <c r="O49">
-        <v>6.337846885333332</v>
+        <v>6.223049301333331</v>
       </c>
       <c r="P49">
-        <v>22.47054804799999</v>
+        <v>22.06353843199999</v>
       </c>
       <c r="Q49">
-        <v>71.470548048</v>
+        <v>71.063538432</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09453153699501496</v>
+        <v>0.09534680919546693</v>
       </c>
       <c r="T49">
-        <v>1.125439653464549</v>
+        <v>1.144268110749814</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.174657178071987</v>
+        <v>2.129351820195487</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0779598607816428</v>
+        <v>0.07802972695592766</v>
       </c>
       <c r="C50">
-        <v>191.9080248488725</v>
+        <v>184.2220852517303</v>
       </c>
       <c r="D50">
-        <v>369.9400248488724</v>
+        <v>369.1380852517303</v>
       </c>
       <c r="E50">
-        <v>-174.968</v>
+        <v>-168.084</v>
       </c>
       <c r="F50">
-        <v>330.432</v>
+        <v>337.316</v>
       </c>
       <c r="G50">
         <v>152.4</v>
@@ -5387,28 +5387,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M50">
-        <v>25.0467456</v>
+        <v>25.5685528</v>
       </c>
       <c r="N50">
-        <v>28.28658773333333</v>
+        <v>27.76478053333333</v>
       </c>
       <c r="O50">
-        <v>6.223049301333333</v>
+        <v>6.108251717333332</v>
       </c>
       <c r="P50">
-        <v>22.063538432</v>
+        <v>21.656528816</v>
       </c>
       <c r="Q50">
-        <v>71.063538432</v>
+        <v>70.65652881599999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09534680919546693</v>
+        <v>0.09619405285476013</v>
       </c>
       <c r="T50">
-        <v>1.144268110749813</v>
+        <v>1.16383493890901</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.129351820195488</v>
+        <v>2.085895660599662</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07802972695592766</v>
+        <v>0.07809959313021253</v>
       </c>
       <c r="C51">
-        <v>184.2220852517303</v>
+        <v>176.5396149522622</v>
       </c>
       <c r="D51">
-        <v>369.1380852517303</v>
+        <v>368.3396149522621</v>
       </c>
       <c r="E51">
-        <v>-168.084</v>
+        <v>-161.2</v>
       </c>
       <c r="F51">
-        <v>337.316</v>
+        <v>344.2</v>
       </c>
       <c r="G51">
         <v>152.4</v>
@@ -5469,28 +5469,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M51">
-        <v>25.5685528</v>
+        <v>26.09036</v>
       </c>
       <c r="N51">
-        <v>27.76478053333333</v>
+        <v>27.24297333333333</v>
       </c>
       <c r="O51">
-        <v>6.108251717333332</v>
+        <v>5.993454133333333</v>
       </c>
       <c r="P51">
-        <v>21.656528816</v>
+        <v>21.24951919999999</v>
       </c>
       <c r="Q51">
-        <v>70.65652881599999</v>
+        <v>70.24951919999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09619405285476013</v>
+        <v>0.09707518626042506</v>
       </c>
       <c r="T51">
-        <v>1.16383493890901</v>
+        <v>1.184184440194574</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.085895660599662</v>
+        <v>2.044177747387669</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07809959313021253</v>
+        <v>0.0781694593044974</v>
       </c>
       <c r="C52">
-        <v>176.5396149522622</v>
+        <v>168.8605914860931</v>
       </c>
       <c r="D52">
-        <v>368.3396149522621</v>
+        <v>367.5445914860932</v>
       </c>
       <c r="E52">
-        <v>-161.2</v>
+        <v>-154.316</v>
       </c>
       <c r="F52">
-        <v>344.2</v>
+        <v>351.084</v>
       </c>
       <c r="G52">
         <v>152.4</v>
@@ -5551,28 +5551,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M52">
-        <v>26.09036</v>
+        <v>26.6121672</v>
       </c>
       <c r="N52">
-        <v>27.24297333333333</v>
+        <v>26.72116613333333</v>
       </c>
       <c r="O52">
-        <v>5.993454133333333</v>
+        <v>5.878656549333332</v>
       </c>
       <c r="P52">
-        <v>21.24951919999999</v>
+        <v>20.84250958399999</v>
       </c>
       <c r="Q52">
-        <v>70.24951919999999</v>
+        <v>69.842509584</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09707518626042506</v>
+        <v>0.09799228429489265</v>
       </c>
       <c r="T52">
-        <v>1.184184440194574</v>
+        <v>1.205364533369345</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.044177747387669</v>
+        <v>2.004095830772224</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0781694593044974</v>
+        <v>0.08399884547878228</v>
       </c>
       <c r="C53">
-        <v>168.8605914860931</v>
+        <v>105.886954922802</v>
       </c>
       <c r="D53">
-        <v>367.5445914860932</v>
+        <v>311.454954922802</v>
       </c>
       <c r="E53">
-        <v>-154.316</v>
+        <v>-147.432</v>
       </c>
       <c r="F53">
-        <v>351.084</v>
+        <v>357.968</v>
       </c>
       <c r="G53">
         <v>152.4</v>
@@ -5633,45 +5633,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M53">
-        <v>26.6121672</v>
+        <v>32.21712</v>
       </c>
       <c r="N53">
-        <v>26.72116613333333</v>
+        <v>21.11621333333333</v>
       </c>
       <c r="O53">
-        <v>5.878656549333332</v>
+        <v>4.645566933333332</v>
       </c>
       <c r="P53">
-        <v>20.84250958399999</v>
+        <v>16.4706464</v>
       </c>
       <c r="Q53">
-        <v>69.842509584</v>
+        <v>65.47064639999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09799228429489265</v>
+        <v>0.09894759474746306</v>
       </c>
       <c r="T53">
-        <v>1.205364533369345</v>
+        <v>1.227427130426399</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.004095830772224</v>
+        <v>1.655434543290441</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08399884547878228</v>
+        <v>0.08417947165306713</v>
       </c>
       <c r="C54">
-        <v>105.886954922802</v>
+        <v>97.5371474338844</v>
       </c>
       <c r="D54">
-        <v>311.454954922802</v>
+        <v>309.9891474338844</v>
       </c>
       <c r="E54">
-        <v>-147.432</v>
+        <v>-140.5479999999999</v>
       </c>
       <c r="F54">
-        <v>357.968</v>
+        <v>364.852</v>
       </c>
       <c r="G54">
         <v>152.4</v>
@@ -5715,28 +5715,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M54">
-        <v>32.21712</v>
+        <v>32.83668</v>
       </c>
       <c r="N54">
-        <v>21.11621333333333</v>
+        <v>20.49665333333333</v>
       </c>
       <c r="O54">
-        <v>4.645566933333332</v>
+        <v>4.509263733333332</v>
       </c>
       <c r="P54">
-        <v>16.4706464</v>
+        <v>15.9873896</v>
       </c>
       <c r="Q54">
-        <v>65.47064639999999</v>
+        <v>64.9873896</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09894759474746306</v>
+        <v>0.09994355670865349</v>
       </c>
       <c r="T54">
-        <v>1.227427130426399</v>
+        <v>1.250428561400773</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.655434543290441</v>
+        <v>1.624199929266093</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08417947165306713</v>
+        <v>0.08436009782735202</v>
       </c>
       <c r="C55">
-        <v>97.5371474338844</v>
+        <v>89.20107244119345</v>
       </c>
       <c r="D55">
-        <v>309.9891474338844</v>
+        <v>308.5370724411934</v>
       </c>
       <c r="E55">
-        <v>-140.5479999999999</v>
+        <v>-133.664</v>
       </c>
       <c r="F55">
-        <v>364.852</v>
+        <v>371.736</v>
       </c>
       <c r="G55">
         <v>152.4</v>
@@ -5797,28 +5797,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M55">
-        <v>32.83668</v>
+        <v>33.45624</v>
       </c>
       <c r="N55">
-        <v>20.49665333333333</v>
+        <v>19.87709333333333</v>
       </c>
       <c r="O55">
-        <v>4.509263733333332</v>
+        <v>4.372960533333332</v>
       </c>
       <c r="P55">
-        <v>15.9873896</v>
+        <v>15.5041328</v>
       </c>
       <c r="Q55">
-        <v>64.9873896</v>
+        <v>64.50413279999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09994355670865349</v>
+        <v>0.1009828213638087</v>
       </c>
       <c r="T55">
-        <v>1.250428561400773</v>
+        <v>1.274430054591425</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.624199929266093</v>
+        <v>1.594122152798202</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08436009782735202</v>
+        <v>0.08454072400163687</v>
       </c>
       <c r="C56">
-        <v>89.20107244119345</v>
+        <v>80.87853786404537</v>
       </c>
       <c r="D56">
-        <v>308.5370724411934</v>
+        <v>307.0985378640454</v>
       </c>
       <c r="E56">
-        <v>-133.664</v>
+        <v>-126.78</v>
       </c>
       <c r="F56">
-        <v>371.736</v>
+        <v>378.62</v>
       </c>
       <c r="G56">
         <v>152.4</v>
@@ -5879,28 +5879,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M56">
-        <v>33.45624</v>
+        <v>34.0758</v>
       </c>
       <c r="N56">
-        <v>19.87709333333333</v>
+        <v>19.25753333333333</v>
       </c>
       <c r="O56">
-        <v>4.372960533333332</v>
+        <v>4.236657333333332</v>
       </c>
       <c r="P56">
-        <v>15.5041328</v>
+        <v>15.020876</v>
       </c>
       <c r="Q56">
-        <v>64.50413279999999</v>
+        <v>64.020876</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1009828213638087</v>
+        <v>0.1020682755591931</v>
       </c>
       <c r="T56">
-        <v>1.274430054591425</v>
+        <v>1.299498280812773</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.594122152798202</v>
+        <v>1.565138113656417</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08454072400163687</v>
+        <v>0.08472135017592174</v>
       </c>
       <c r="C57">
-        <v>80.87853786404537</v>
+        <v>72.56935518738749</v>
       </c>
       <c r="D57">
-        <v>307.0985378640454</v>
+        <v>305.6733551873875</v>
       </c>
       <c r="E57">
-        <v>-126.78</v>
+        <v>-119.896</v>
       </c>
       <c r="F57">
-        <v>378.62</v>
+        <v>385.504</v>
       </c>
       <c r="G57">
         <v>152.4</v>
@@ -5961,28 +5961,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M57">
-        <v>34.0758</v>
+        <v>34.69536</v>
       </c>
       <c r="N57">
-        <v>19.25753333333333</v>
+        <v>18.63797333333333</v>
       </c>
       <c r="O57">
-        <v>4.236657333333332</v>
+        <v>4.100354133333332</v>
       </c>
       <c r="P57">
-        <v>15.020876</v>
+        <v>14.53761919999999</v>
       </c>
       <c r="Q57">
-        <v>64.020876</v>
+        <v>63.53761919999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1020682755591931</v>
+        <v>0.1032030685816403</v>
       </c>
       <c r="T57">
-        <v>1.299498280812773</v>
+        <v>1.325705971862363</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.565138113656417</v>
+        <v>1.537189218769695</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08472135017592174</v>
+        <v>0.0849019763502066</v>
       </c>
       <c r="C58">
-        <v>72.56935518738749</v>
+        <v>64.27333937944422</v>
       </c>
       <c r="D58">
-        <v>305.6733551873875</v>
+        <v>304.2613393794442</v>
       </c>
       <c r="E58">
-        <v>-119.896</v>
+        <v>-113.0119999999999</v>
       </c>
       <c r="F58">
-        <v>385.504</v>
+        <v>392.388</v>
       </c>
       <c r="G58">
         <v>152.4</v>
@@ -6043,28 +6043,28 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M58">
-        <v>34.69536</v>
+        <v>35.31492</v>
       </c>
       <c r="N58">
-        <v>18.63797333333333</v>
+        <v>18.01841333333333</v>
       </c>
       <c r="O58">
-        <v>4.100354133333332</v>
+        <v>3.964050933333332</v>
       </c>
       <c r="P58">
-        <v>14.53761919999999</v>
+        <v>14.0543624</v>
       </c>
       <c r="Q58">
-        <v>63.53761919999999</v>
+        <v>63.0543624</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1032030685816403</v>
+        <v>0.1043906426748991</v>
       </c>
       <c r="T58">
-        <v>1.325705971862363</v>
+        <v>1.353132625286353</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.537189218769695</v>
+        <v>1.510220986861455</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0849019763502066</v>
+        <v>0.1127973492228753</v>
       </c>
       <c r="C59">
-        <v>64.27333937944422</v>
+        <v>-69.29453111955866</v>
       </c>
       <c r="D59">
-        <v>304.2613393794442</v>
+        <v>177.5774688804414</v>
       </c>
       <c r="E59">
-        <v>-113.0119999999999</v>
+        <v>-106.1279999999999</v>
       </c>
       <c r="F59">
-        <v>392.388</v>
+        <v>399.272</v>
       </c>
       <c r="G59">
         <v>152.4</v>
@@ -6125,45 +6125,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M59">
-        <v>35.31492</v>
+        <v>58.61312960000001</v>
       </c>
       <c r="N59">
-        <v>18.01841333333333</v>
+        <v>-5.279796266666686</v>
       </c>
       <c r="O59">
-        <v>3.964050933333332</v>
+        <v>-1.161555178666671</v>
       </c>
       <c r="P59">
-        <v>14.0543624</v>
+        <v>-4.118241088000016</v>
       </c>
       <c r="Q59">
-        <v>63.0543624</v>
+        <v>44.88175891199998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1043906426748991</v>
+        <v>0.1064231030490326</v>
       </c>
       <c r="T59">
-        <v>1.353132625286353</v>
+        <v>1.400071663949946</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.22</v>
+        <v>0.2001826794338811</v>
       </c>
       <c r="W59">
-        <v>0.0702</v>
+        <v>0.1174131826591063</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.510220986861455</v>
+        <v>0.9099212701540051</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1127973492228753</v>
+        <v>0.1138073492228753</v>
       </c>
       <c r="C60">
-        <v>-69.29453111955848</v>
+        <v>-78.81579379217737</v>
       </c>
       <c r="D60">
-        <v>177.5774688804414</v>
+        <v>174.9402062078226</v>
       </c>
       <c r="E60">
-        <v>-106.128</v>
+        <v>-99.24400000000003</v>
       </c>
       <c r="F60">
-        <v>399.2719999999999</v>
+        <v>406.1559999999999</v>
       </c>
       <c r="G60">
         <v>152.4</v>
@@ -6207,37 +6207,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M60">
-        <v>58.61312959999999</v>
+        <v>59.62370079999999</v>
       </c>
       <c r="N60">
-        <v>-5.279796266666665</v>
+        <v>-6.290367466666666</v>
       </c>
       <c r="O60">
-        <v>-1.161555178666666</v>
+        <v>-1.383880842666666</v>
       </c>
       <c r="P60">
-        <v>-4.118241087999999</v>
+        <v>-4.906486623999999</v>
       </c>
       <c r="Q60">
-        <v>44.881758912</v>
+        <v>44.093513376</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1064231030490326</v>
+        <v>0.1079017153185212</v>
       </c>
       <c r="T60">
-        <v>1.400071663949945</v>
+        <v>1.434219753314578</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2001826794338812</v>
+        <v>0.1967897526638154</v>
       </c>
       <c r="W60">
-        <v>0.1174131826591062</v>
+        <v>0.1179112643089519</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9099212701540055</v>
+        <v>0.8944988757446155</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1138073492228753</v>
+        <v>0.1148173492228753</v>
       </c>
       <c r="C61">
-        <v>-78.81579379217737</v>
+        <v>-88.25986905237505</v>
       </c>
       <c r="D61">
-        <v>174.9402062078226</v>
+        <v>172.3801309476249</v>
       </c>
       <c r="E61">
-        <v>-99.24400000000003</v>
+        <v>-92.36000000000001</v>
       </c>
       <c r="F61">
-        <v>406.1559999999999</v>
+        <v>413.04</v>
       </c>
       <c r="G61">
         <v>152.4</v>
@@ -6289,37 +6289,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M61">
-        <v>59.62370079999999</v>
+        <v>60.634272</v>
       </c>
       <c r="N61">
-        <v>-6.290367466666666</v>
+        <v>-7.300938666666674</v>
       </c>
       <c r="O61">
-        <v>-1.383880842666666</v>
+        <v>-1.606206506666668</v>
       </c>
       <c r="P61">
-        <v>-4.906486623999999</v>
+        <v>-5.694732160000006</v>
       </c>
       <c r="Q61">
-        <v>44.093513376</v>
+        <v>43.30526783999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1079017153185212</v>
+        <v>0.1094542582014843</v>
       </c>
       <c r="T61">
-        <v>1.434219753314578</v>
+        <v>1.470075247147443</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1967897526638154</v>
+        <v>0.1935099234527518</v>
       </c>
       <c r="W61">
-        <v>0.1179112643089519</v>
+        <v>0.1183927432371361</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8944988757446155</v>
+        <v>0.8795905611488718</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1148173492228753</v>
+        <v>0.1158273492228754</v>
       </c>
       <c r="C62">
-        <v>-88.25986905237505</v>
+        <v>-97.63009670755855</v>
       </c>
       <c r="D62">
-        <v>172.3801309476249</v>
+        <v>169.8939032924415</v>
       </c>
       <c r="E62">
-        <v>-92.36000000000001</v>
+        <v>-85.476</v>
       </c>
       <c r="F62">
-        <v>413.04</v>
+        <v>419.924</v>
       </c>
       <c r="G62">
         <v>152.4</v>
@@ -6371,37 +6371,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M62">
-        <v>60.634272</v>
+        <v>61.6448432</v>
       </c>
       <c r="N62">
-        <v>-7.300938666666674</v>
+        <v>-8.311509866666675</v>
       </c>
       <c r="O62">
-        <v>-1.606206506666668</v>
+        <v>-1.828532170666669</v>
       </c>
       <c r="P62">
-        <v>-5.694732160000006</v>
+        <v>-6.482977696000007</v>
       </c>
       <c r="Q62">
-        <v>43.30526783999999</v>
+        <v>42.51702230399999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1094542582014843</v>
+        <v>0.111086418668189</v>
       </c>
       <c r="T62">
-        <v>1.470075247147443</v>
+        <v>1.507769484253787</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1935099234527518</v>
+        <v>0.1903376296256575</v>
       </c>
       <c r="W62">
-        <v>0.1183927432371361</v>
+        <v>0.1188584359709535</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8795905611488718</v>
+        <v>0.8651710437529887</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1158273492228754</v>
+        <v>0.1168373492228753</v>
       </c>
       <c r="C63">
-        <v>-97.63009670755855</v>
+        <v>-106.9296266253064</v>
       </c>
       <c r="D63">
-        <v>169.8939032924415</v>
+        <v>167.4783733746936</v>
       </c>
       <c r="E63">
-        <v>-85.476</v>
+        <v>-78.59199999999998</v>
       </c>
       <c r="F63">
-        <v>419.924</v>
+        <v>426.808</v>
       </c>
       <c r="G63">
         <v>152.4</v>
@@ -6453,37 +6453,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M63">
-        <v>61.6448432</v>
+        <v>62.65541440000001</v>
       </c>
       <c r="N63">
-        <v>-8.311509866666675</v>
+        <v>-9.322081066666676</v>
       </c>
       <c r="O63">
-        <v>-1.828532170666669</v>
+        <v>-2.050857834666669</v>
       </c>
       <c r="P63">
-        <v>-6.482977696000007</v>
+        <v>-7.271223232000008</v>
       </c>
       <c r="Q63">
-        <v>42.51702230399999</v>
+        <v>41.72877676799999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.111086418668189</v>
+        <v>0.1128044823173519</v>
       </c>
       <c r="T63">
-        <v>1.507769484253787</v>
+        <v>1.547447628576256</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1903376296256575</v>
+        <v>0.1872676678575017</v>
       </c>
       <c r="W63">
-        <v>0.1188584359709535</v>
+        <v>0.1193091063585188</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8651710437529887</v>
+        <v>0.8512166720795533</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1168373492228753</v>
+        <v>0.1178473492228753</v>
       </c>
       <c r="C64">
-        <v>-106.9296266253064</v>
+        <v>-116.1614320467824</v>
       </c>
       <c r="D64">
-        <v>167.4783733746936</v>
+        <v>165.1305679532176</v>
       </c>
       <c r="E64">
-        <v>-78.59199999999998</v>
+        <v>-71.70799999999997</v>
       </c>
       <c r="F64">
-        <v>426.808</v>
+        <v>433.692</v>
       </c>
       <c r="G64">
         <v>152.4</v>
@@ -6535,37 +6535,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M64">
-        <v>62.65541440000001</v>
+        <v>63.66598560000001</v>
       </c>
       <c r="N64">
-        <v>-9.322081066666676</v>
+        <v>-10.33265226666668</v>
       </c>
       <c r="O64">
-        <v>-2.050857834666669</v>
+        <v>-2.273183498666669</v>
       </c>
       <c r="P64">
-        <v>-7.271223232000008</v>
+        <v>-8.059468768000009</v>
       </c>
       <c r="Q64">
-        <v>41.72877676799999</v>
+        <v>40.94053123199999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1128044823173519</v>
+        <v>0.1146154142718749</v>
       </c>
       <c r="T64">
-        <v>1.547447628576256</v>
+        <v>1.589270537456695</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1872676678575017</v>
+        <v>0.184295165193097</v>
       </c>
       <c r="W64">
-        <v>0.1193091063585188</v>
+        <v>0.1197454697496534</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8512166720795533</v>
+        <v>0.8377052963322589</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1178473492228753</v>
+        <v>0.1188573492228753</v>
       </c>
       <c r="C65">
-        <v>-116.1614320467824</v>
+        <v>-125.3283217958199</v>
       </c>
       <c r="D65">
-        <v>165.1305679532176</v>
+        <v>162.8476782041802</v>
       </c>
       <c r="E65">
-        <v>-71.70799999999997</v>
+        <v>-64.82399999999996</v>
       </c>
       <c r="F65">
-        <v>433.692</v>
+        <v>440.576</v>
       </c>
       <c r="G65">
         <v>152.4</v>
@@ -6617,37 +6617,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M65">
-        <v>63.66598560000001</v>
+        <v>64.67655680000001</v>
       </c>
       <c r="N65">
-        <v>-10.33265226666668</v>
+        <v>-11.34322346666669</v>
       </c>
       <c r="O65">
-        <v>-2.273183498666669</v>
+        <v>-2.495509162666671</v>
       </c>
       <c r="P65">
-        <v>-8.059468768000009</v>
+        <v>-8.847714304000014</v>
       </c>
       <c r="Q65">
-        <v>40.94053123199999</v>
+        <v>40.15228569599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1146154142718749</v>
+        <v>0.1165269535572047</v>
       </c>
       <c r="T65">
-        <v>1.589270537456695</v>
+        <v>1.633416941274936</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.184295165193097</v>
+        <v>0.1814155532369548</v>
       </c>
       <c r="W65">
-        <v>0.1197454697496534</v>
+        <v>0.1201681967848151</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8377052963322589</v>
+        <v>0.8246161510770672</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1188573492228753</v>
+        <v>0.1198673492228753</v>
       </c>
       <c r="C66">
-        <v>-125.3283217958199</v>
+        <v>-134.4329514890913</v>
       </c>
       <c r="D66">
-        <v>162.8476782041802</v>
+        <v>160.6270485109087</v>
       </c>
       <c r="E66">
-        <v>-64.82399999999996</v>
+        <v>-57.94</v>
       </c>
       <c r="F66">
-        <v>440.576</v>
+        <v>447.46</v>
       </c>
       <c r="G66">
         <v>152.4</v>
@@ -6699,37 +6699,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M66">
-        <v>64.67655680000001</v>
+        <v>65.687128</v>
       </c>
       <c r="N66">
-        <v>-11.34322346666669</v>
+        <v>-12.35379466666667</v>
       </c>
       <c r="O66">
-        <v>-2.495509162666671</v>
+        <v>-2.717834826666668</v>
       </c>
       <c r="P66">
-        <v>-8.847714304000014</v>
+        <v>-9.635959840000005</v>
       </c>
       <c r="Q66">
-        <v>40.15228569599999</v>
+        <v>39.36404015999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1165269535572047</v>
+        <v>0.1185477236588392</v>
       </c>
       <c r="T66">
-        <v>1.633416941274936</v>
+        <v>1.680085996739935</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1814155532369548</v>
+        <v>0.1786245447256171</v>
       </c>
       <c r="W66">
-        <v>0.1201681967848151</v>
+        <v>0.1205779168342794</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8246161510770672</v>
+        <v>0.8119297487528048</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1198673492228753</v>
+        <v>0.1574167883728269</v>
       </c>
       <c r="C67">
-        <v>-134.4329514890913</v>
+        <v>-195.3541234219566</v>
       </c>
       <c r="D67">
-        <v>160.6270485109087</v>
+        <v>106.5898765780434</v>
       </c>
       <c r="E67">
-        <v>-57.94</v>
+        <v>-51.05599999999998</v>
       </c>
       <c r="F67">
-        <v>447.46</v>
+        <v>454.344</v>
       </c>
       <c r="G67">
         <v>152.4</v>
@@ -6781,45 +6781,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M67">
-        <v>65.687128</v>
+        <v>91.2322752</v>
       </c>
       <c r="N67">
-        <v>-12.35379466666667</v>
+        <v>-37.89894186666668</v>
       </c>
       <c r="O67">
-        <v>-2.717834826666668</v>
+        <v>-8.337767210666669</v>
       </c>
       <c r="P67">
-        <v>-9.635959840000005</v>
+        <v>-29.56117465600001</v>
       </c>
       <c r="Q67">
-        <v>39.36404015999999</v>
+        <v>19.43882534399999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1185477236588392</v>
+        <v>0.1233327718545449</v>
       </c>
       <c r="T67">
-        <v>1.680085996739935</v>
+        <v>1.79059519294561</v>
       </c>
       <c r="U67">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1786245447256171</v>
+        <v>0.1286094565504526</v>
       </c>
       <c r="W67">
-        <v>0.1205779168342794</v>
+        <v>0.1749752211246692</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8119297487528048</v>
+        <v>0.5845884388656934</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1574167883728269</v>
+        <v>0.1589667883728269</v>
       </c>
       <c r="C68">
-        <v>-195.3541234219566</v>
+        <v>-203.6980421054458</v>
       </c>
       <c r="D68">
-        <v>106.5898765780434</v>
+        <v>105.1299578945541</v>
       </c>
       <c r="E68">
-        <v>-51.05599999999998</v>
+        <v>-44.17199999999997</v>
       </c>
       <c r="F68">
-        <v>454.344</v>
+        <v>461.228</v>
       </c>
       <c r="G68">
         <v>152.4</v>
@@ -6863,37 +6863,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M68">
-        <v>91.2322752</v>
+        <v>92.6145824</v>
       </c>
       <c r="N68">
-        <v>-37.89894186666668</v>
+        <v>-39.28124906666667</v>
       </c>
       <c r="O68">
-        <v>-8.337767210666669</v>
+        <v>-8.641874794666668</v>
       </c>
       <c r="P68">
-        <v>-29.56117465600001</v>
+        <v>-30.639374272</v>
       </c>
       <c r="Q68">
-        <v>19.43882534399999</v>
+        <v>18.360625728</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1233327718545449</v>
+        <v>0.1256822497895311</v>
       </c>
       <c r="T68">
-        <v>1.79059519294561</v>
+        <v>1.844855653337901</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1286094565504526</v>
+        <v>0.1266899124228339</v>
       </c>
       <c r="W68">
-        <v>0.1749752211246692</v>
+        <v>0.175360665585495</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5845884388656934</v>
+        <v>0.5758632382856086</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1589667883728269</v>
+        <v>0.1605167883728269</v>
       </c>
       <c r="C69">
-        <v>-203.6980421054458</v>
+        <v>-212.0025093016419</v>
       </c>
       <c r="D69">
-        <v>105.1299578945541</v>
+        <v>103.7094906983582</v>
       </c>
       <c r="E69">
-        <v>-44.17199999999997</v>
+        <v>-37.28799999999995</v>
       </c>
       <c r="F69">
-        <v>461.228</v>
+        <v>468.112</v>
       </c>
       <c r="G69">
         <v>152.4</v>
@@ -6945,37 +6945,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M69">
-        <v>92.6145824</v>
+        <v>93.9968896</v>
       </c>
       <c r="N69">
-        <v>-39.28124906666667</v>
+        <v>-40.66355626666667</v>
       </c>
       <c r="O69">
-        <v>-8.641874794666668</v>
+        <v>-8.945982378666669</v>
       </c>
       <c r="P69">
-        <v>-30.639374272</v>
+        <v>-31.717573888</v>
       </c>
       <c r="Q69">
-        <v>18.360625728</v>
+        <v>17.282426112</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1256822497895311</v>
+        <v>0.128178570095454</v>
       </c>
       <c r="T69">
-        <v>1.844855653337901</v>
+        <v>1.902507392504711</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1266899124228339</v>
+        <v>0.1248268254754393</v>
       </c>
       <c r="W69">
-        <v>0.175360665585495</v>
+        <v>0.1757347734445318</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5758632382856086</v>
+        <v>0.5673946612519967</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1605167883728269</v>
+        <v>0.1620667883728269</v>
       </c>
       <c r="C70">
-        <v>-212.0025093016419</v>
+        <v>-220.269102842172</v>
       </c>
       <c r="D70">
-        <v>103.7094906983582</v>
+        <v>102.326897157828</v>
       </c>
       <c r="E70">
-        <v>-37.28799999999995</v>
+        <v>-30.40399999999994</v>
       </c>
       <c r="F70">
-        <v>468.112</v>
+        <v>474.996</v>
       </c>
       <c r="G70">
         <v>152.4</v>
@@ -7027,37 +7027,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M70">
-        <v>93.9968896</v>
+        <v>95.37919680000002</v>
       </c>
       <c r="N70">
-        <v>-40.66355626666667</v>
+        <v>-42.04586346666669</v>
       </c>
       <c r="O70">
-        <v>-8.945982378666669</v>
+        <v>-9.250089962666671</v>
       </c>
       <c r="P70">
-        <v>-31.717573888</v>
+        <v>-32.79577350400002</v>
       </c>
       <c r="Q70">
-        <v>17.282426112</v>
+        <v>16.20422649599998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.128178570095454</v>
+        <v>0.1308359433243396</v>
       </c>
       <c r="T70">
-        <v>1.902507392504711</v>
+        <v>1.96387859871454</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1248268254754393</v>
+        <v>0.123017741048259</v>
       </c>
       <c r="W70">
-        <v>0.1757347734445318</v>
+        <v>0.1760980375975096</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5673946612519967</v>
+        <v>0.5591715502193589</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1620667883728269</v>
+        <v>0.1636167883728269</v>
       </c>
       <c r="C71">
-        <v>-220.269102842172</v>
+        <v>-228.4993175267272</v>
       </c>
       <c r="D71">
-        <v>102.326897157828</v>
+        <v>100.9806824732728</v>
       </c>
       <c r="E71">
-        <v>-30.40399999999994</v>
+        <v>-23.51999999999992</v>
       </c>
       <c r="F71">
-        <v>474.996</v>
+        <v>481.8800000000001</v>
       </c>
       <c r="G71">
         <v>152.4</v>
@@ -7109,37 +7109,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M71">
-        <v>95.37919680000002</v>
+        <v>96.76150400000002</v>
       </c>
       <c r="N71">
-        <v>-42.04586346666669</v>
+        <v>-43.42817066666669</v>
       </c>
       <c r="O71">
-        <v>-9.250089962666671</v>
+        <v>-9.554197546666671</v>
       </c>
       <c r="P71">
-        <v>-32.79577350400002</v>
+        <v>-33.87397312000002</v>
       </c>
       <c r="Q71">
-        <v>16.20422649599998</v>
+        <v>15.12602687999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1308359433243396</v>
+        <v>0.1336704747684842</v>
       </c>
       <c r="T71">
-        <v>1.96387859871454</v>
+        <v>2.029341218671691</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.123017741048259</v>
+        <v>0.1212603447475696</v>
       </c>
       <c r="W71">
-        <v>0.1760980375975096</v>
+        <v>0.176450922774688</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5591715502193589</v>
+        <v>0.5511833852162252</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1636167883728269</v>
+        <v>0.1651667883728269</v>
       </c>
       <c r="C72">
-        <v>-228.4993175267272</v>
+        <v>-236.6945705139878</v>
       </c>
       <c r="D72">
-        <v>100.9806824732728</v>
+        <v>99.66942948601222</v>
       </c>
       <c r="E72">
-        <v>-23.51999999999992</v>
+        <v>-16.63599999999997</v>
       </c>
       <c r="F72">
-        <v>481.8800000000001</v>
+        <v>488.764</v>
       </c>
       <c r="G72">
         <v>152.4</v>
@@ -7191,37 +7191,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M72">
-        <v>96.76150400000002</v>
+        <v>98.1438112</v>
       </c>
       <c r="N72">
-        <v>-43.42817066666669</v>
+        <v>-44.81047786666667</v>
       </c>
       <c r="O72">
-        <v>-9.554197546666671</v>
+        <v>-9.858305130666668</v>
       </c>
       <c r="P72">
-        <v>-33.87397312000002</v>
+        <v>-34.95217273600001</v>
       </c>
       <c r="Q72">
-        <v>15.12602687999998</v>
+        <v>14.04782726399999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1336704747684842</v>
+        <v>0.1367004911398113</v>
       </c>
       <c r="T72">
-        <v>2.029341218671691</v>
+        <v>2.099318502074164</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1212603447475696</v>
+        <v>0.1195524525680263</v>
       </c>
       <c r="W72">
-        <v>0.176450922774688</v>
+        <v>0.1767938675243403</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5511833852162252</v>
+        <v>0.5434202389455742</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1651667883728269</v>
+        <v>0.1667167883728269</v>
       </c>
       <c r="C73">
-        <v>-236.6945705139878</v>
+        <v>-244.8562062979203</v>
       </c>
       <c r="D73">
-        <v>99.66942948601216</v>
+        <v>98.39179370207964</v>
       </c>
       <c r="E73">
-        <v>-16.63600000000002</v>
+        <v>-9.75200000000001</v>
       </c>
       <c r="F73">
-        <v>488.764</v>
+        <v>495.648</v>
       </c>
       <c r="G73">
         <v>152.4</v>
@@ -7273,37 +7273,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M73">
-        <v>98.14381119999999</v>
+        <v>99.5261184</v>
       </c>
       <c r="N73">
-        <v>-44.81047786666666</v>
+        <v>-46.19278506666667</v>
       </c>
       <c r="O73">
-        <v>-9.858305130666665</v>
+        <v>-10.16241271466667</v>
       </c>
       <c r="P73">
-        <v>-34.95217273599999</v>
+        <v>-36.030372352</v>
       </c>
       <c r="Q73">
-        <v>14.04782726400001</v>
+        <v>12.969627648</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1367004911398113</v>
+        <v>0.1399469372519474</v>
       </c>
       <c r="T73">
-        <v>2.099318502074163</v>
+        <v>2.174294162862526</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1195524525680264</v>
+        <v>0.1178920018379149</v>
       </c>
       <c r="W73">
-        <v>0.1767938675243403</v>
+        <v>0.1771272860309467</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5434202389455743</v>
+        <v>0.5358727356268858</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1667167883728269</v>
+        <v>0.1682667883728269</v>
       </c>
       <c r="C74">
-        <v>-244.8562062979203</v>
+        <v>-252.9855013061795</v>
       </c>
       <c r="D74">
-        <v>98.39179370207964</v>
+        <v>97.14649869382043</v>
       </c>
       <c r="E74">
-        <v>-9.75200000000001</v>
+        <v>-2.867999999999995</v>
       </c>
       <c r="F74">
-        <v>495.648</v>
+        <v>502.532</v>
       </c>
       <c r="G74">
         <v>152.4</v>
@@ -7355,37 +7355,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M74">
-        <v>99.5261184</v>
+        <v>100.9084256</v>
       </c>
       <c r="N74">
-        <v>-46.19278506666667</v>
+        <v>-47.57509226666667</v>
       </c>
       <c r="O74">
-        <v>-10.16241271466667</v>
+        <v>-10.46652029866667</v>
       </c>
       <c r="P74">
-        <v>-36.030372352</v>
+        <v>-37.10857196800001</v>
       </c>
       <c r="Q74">
-        <v>12.969627648</v>
+        <v>11.89142803199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1399469372519474</v>
+        <v>0.1434338608538713</v>
       </c>
       <c r="T74">
-        <v>2.174294162862526</v>
+        <v>2.254823576301879</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1178920018379149</v>
+        <v>0.1162770429086284</v>
       </c>
       <c r="W74">
-        <v>0.1771272860309467</v>
+        <v>0.1774515697839474</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5358727356268858</v>
+        <v>0.528532013221038</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1682667883728269</v>
+        <v>0.1698167883728269</v>
       </c>
       <c r="C75">
-        <v>-252.9855013061795</v>
+        <v>-261.0836681536773</v>
       </c>
       <c r="D75">
-        <v>97.14649869382043</v>
+        <v>95.93233184632275</v>
       </c>
       <c r="E75">
-        <v>-2.867999999999995</v>
+        <v>4.01600000000002</v>
       </c>
       <c r="F75">
-        <v>502.532</v>
+        <v>509.416</v>
       </c>
       <c r="G75">
         <v>152.4</v>
@@ -7437,37 +7437,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M75">
-        <v>100.9084256</v>
+        <v>102.2907328</v>
       </c>
       <c r="N75">
-        <v>-47.57509226666667</v>
+        <v>-48.95739946666667</v>
       </c>
       <c r="O75">
-        <v>-10.46652029866667</v>
+        <v>-10.77062788266667</v>
       </c>
       <c r="P75">
-        <v>-37.10857196800001</v>
+        <v>-38.18677158400001</v>
       </c>
       <c r="Q75">
-        <v>11.89142803199999</v>
+        <v>10.81322841599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1434338608538713</v>
+        <v>0.147189009348251</v>
       </c>
       <c r="T75">
-        <v>2.254823576301879</v>
+        <v>2.341547560005797</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1162770429086284</v>
+        <v>0.1147057315179712</v>
       </c>
       <c r="W75">
-        <v>0.1774515697839474</v>
+        <v>0.1777670891111914</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.528532013221038</v>
+        <v>0.5213896887180509</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1698167883728269</v>
+        <v>0.1713667883728269</v>
       </c>
       <c r="C76">
-        <v>-261.0836681536773</v>
+        <v>-269.1518595811134</v>
       </c>
       <c r="D76">
-        <v>95.93233184632275</v>
+        <v>94.74814041888656</v>
       </c>
       <c r="E76">
-        <v>4.01600000000002</v>
+        <v>10.89999999999998</v>
       </c>
       <c r="F76">
-        <v>509.416</v>
+        <v>516.3</v>
       </c>
       <c r="G76">
         <v>152.4</v>
@@ -7519,37 +7519,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M76">
-        <v>102.2907328</v>
+        <v>103.67304</v>
       </c>
       <c r="N76">
-        <v>-48.95739946666667</v>
+        <v>-50.33970666666667</v>
       </c>
       <c r="O76">
-        <v>-10.77062788266667</v>
+        <v>-11.07473546666667</v>
       </c>
       <c r="P76">
-        <v>-38.18677158400001</v>
+        <v>-39.26497120000001</v>
       </c>
       <c r="Q76">
-        <v>10.81322841599999</v>
+        <v>9.735028799999995</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.147189009348251</v>
+        <v>0.1512445697221811</v>
       </c>
       <c r="T76">
-        <v>2.341547560005797</v>
+        <v>2.435209462406029</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1147057315179712</v>
+        <v>0.1131763217643983</v>
       </c>
       <c r="W76">
-        <v>0.1777670891111914</v>
+        <v>0.1780741945897088</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5213896887180509</v>
+        <v>0.5144378262018103</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1713667883728269</v>
+        <v>0.1729167883728269</v>
       </c>
       <c r="C77">
-        <v>-269.1518595811134</v>
+        <v>-277.1911721053611</v>
       </c>
       <c r="D77">
-        <v>94.74814041888656</v>
+        <v>93.59282789463882</v>
       </c>
       <c r="E77">
-        <v>10.89999999999998</v>
+        <v>17.78399999999999</v>
       </c>
       <c r="F77">
-        <v>516.3</v>
+        <v>523.184</v>
       </c>
       <c r="G77">
         <v>152.4</v>
@@ -7601,37 +7601,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M77">
-        <v>103.67304</v>
+        <v>105.0553472</v>
       </c>
       <c r="N77">
-        <v>-50.33970666666667</v>
+        <v>-51.72201386666667</v>
       </c>
       <c r="O77">
-        <v>-11.07473546666667</v>
+        <v>-11.37884305066667</v>
       </c>
       <c r="P77">
-        <v>-39.26497120000001</v>
+        <v>-40.343170816</v>
       </c>
       <c r="Q77">
-        <v>9.735028799999995</v>
+        <v>8.656829183999996</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1512445697221811</v>
+        <v>0.1556380934606053</v>
       </c>
       <c r="T77">
-        <v>2.435209462406029</v>
+        <v>2.536676523339614</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1131763217643983</v>
+        <v>0.1116871596359193</v>
       </c>
       <c r="W77">
-        <v>0.1780741945897088</v>
+        <v>0.1783732183451074</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5144378262018103</v>
+        <v>0.507668907435997</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1729167883728269</v>
+        <v>0.1744667883728269</v>
       </c>
       <c r="C78">
-        <v>-277.1911721053611</v>
+        <v>-285.2026494060018</v>
       </c>
       <c r="D78">
-        <v>93.59282789463882</v>
+        <v>92.46535059399821</v>
       </c>
       <c r="E78">
-        <v>17.78399999999999</v>
+        <v>24.66800000000001</v>
       </c>
       <c r="F78">
-        <v>523.184</v>
+        <v>530.068</v>
       </c>
       <c r="G78">
         <v>152.4</v>
@@ -7683,37 +7683,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M78">
-        <v>105.0553472</v>
+        <v>106.4376544</v>
       </c>
       <c r="N78">
-        <v>-51.72201386666667</v>
+        <v>-53.10432106666667</v>
       </c>
       <c r="O78">
-        <v>-11.37884305066667</v>
+        <v>-11.68295063466667</v>
       </c>
       <c r="P78">
-        <v>-40.343170816</v>
+        <v>-41.421370432</v>
       </c>
       <c r="Q78">
-        <v>8.656829183999996</v>
+        <v>7.578629567999997</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1556380934606053</v>
+        <v>0.1604136627415012</v>
       </c>
       <c r="T78">
-        <v>2.536676523339614</v>
+        <v>2.646966806963075</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1116871596359193</v>
+        <v>0.1102366770432451</v>
       </c>
       <c r="W78">
-        <v>0.1783732183451074</v>
+        <v>0.1786644752497164</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.507668907435997</v>
+        <v>0.501075804742023</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1744667883728269</v>
+        <v>0.2036797229338525</v>
       </c>
       <c r="C79">
-        <v>-285.2026494060018</v>
+        <v>-309.1957764418813</v>
       </c>
       <c r="D79">
-        <v>92.46535059399821</v>
+        <v>75.35622355811866</v>
       </c>
       <c r="E79">
-        <v>24.66800000000001</v>
+        <v>31.55200000000002</v>
       </c>
       <c r="F79">
-        <v>530.068</v>
+        <v>536.952</v>
       </c>
       <c r="G79">
         <v>152.4</v>
@@ -7765,45 +7765,45 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M79">
-        <v>106.4376544</v>
+        <v>126.6132816</v>
       </c>
       <c r="N79">
-        <v>-53.10432106666667</v>
+        <v>-73.27994826666668</v>
       </c>
       <c r="O79">
-        <v>-11.68295063466667</v>
+        <v>-16.12158861866667</v>
       </c>
       <c r="P79">
-        <v>-41.421370432</v>
+        <v>-57.15835964800001</v>
       </c>
       <c r="Q79">
-        <v>7.578629567999997</v>
+        <v>-8.158359648000008</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1604136627415012</v>
+        <v>0.167273077234413</v>
       </c>
       <c r="T79">
-        <v>2.646966806963075</v>
+        <v>2.805382846060347</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1102366770432451</v>
+        <v>0.09267063601116972</v>
       </c>
       <c r="W79">
-        <v>0.1786644752497164</v>
+        <v>0.2139482640285662</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.501075804742023</v>
+        <v>0.4212301636871351</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2036797229338525</v>
+        <v>0.2055797229338525</v>
       </c>
       <c r="C80">
-        <v>-309.1957764418813</v>
+        <v>-316.9758652704976</v>
       </c>
       <c r="D80">
-        <v>75.35622355811866</v>
+        <v>74.46013472950234</v>
       </c>
       <c r="E80">
-        <v>31.55200000000002</v>
+        <v>38.43600000000004</v>
       </c>
       <c r="F80">
-        <v>536.952</v>
+        <v>543.836</v>
       </c>
       <c r="G80">
         <v>152.4</v>
@@ -7847,37 +7847,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M80">
-        <v>126.6132816</v>
+        <v>128.2365288</v>
       </c>
       <c r="N80">
-        <v>-73.27994826666668</v>
+        <v>-74.90319546666667</v>
       </c>
       <c r="O80">
-        <v>-16.12158861866667</v>
+        <v>-16.47870300266667</v>
       </c>
       <c r="P80">
-        <v>-57.15835964800001</v>
+        <v>-58.424492464</v>
       </c>
       <c r="Q80">
-        <v>-8.158359648000008</v>
+        <v>-9.424492464000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.167273077234413</v>
+        <v>0.1730575094836708</v>
       </c>
       <c r="T80">
-        <v>2.805382846060347</v>
+        <v>2.938972505396555</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09267063601116972</v>
+        <v>0.09149758998571188</v>
       </c>
       <c r="W80">
-        <v>0.2139482640285662</v>
+        <v>0.2142248682813691</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4212301636871351</v>
+        <v>0.4158981362986903</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2055797229338525</v>
+        <v>0.2074797229338525</v>
       </c>
       <c r="C81">
-        <v>-316.9758652704976</v>
+        <v>-324.7348930935225</v>
       </c>
       <c r="D81">
-        <v>74.46013472950234</v>
+        <v>73.58510690647753</v>
       </c>
       <c r="E81">
-        <v>38.43600000000004</v>
+        <v>45.32000000000005</v>
       </c>
       <c r="F81">
-        <v>543.836</v>
+        <v>550.72</v>
       </c>
       <c r="G81">
         <v>152.4</v>
@@ -7929,37 +7929,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M81">
-        <v>128.2365288</v>
+        <v>129.859776</v>
       </c>
       <c r="N81">
-        <v>-74.90319546666667</v>
+        <v>-76.52644266666668</v>
       </c>
       <c r="O81">
-        <v>-16.47870300266667</v>
+        <v>-16.83581738666667</v>
       </c>
       <c r="P81">
-        <v>-58.424492464</v>
+        <v>-59.69062528000001</v>
       </c>
       <c r="Q81">
-        <v>-9.424492464000004</v>
+        <v>-10.69062528000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1730575094836708</v>
+        <v>0.1794203849578543</v>
       </c>
       <c r="T81">
-        <v>2.938972505396555</v>
+        <v>3.085921130666382</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09149758998571188</v>
+        <v>0.09035387011089047</v>
       </c>
       <c r="W81">
-        <v>0.2142248682813691</v>
+        <v>0.214494557427852</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4158981362986903</v>
+        <v>0.4106994095949567</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2074797229338525</v>
+        <v>0.2093797229338525</v>
       </c>
       <c r="C82">
-        <v>-324.7348930935225</v>
+        <v>-332.473593790007</v>
       </c>
       <c r="D82">
-        <v>73.58510690647753</v>
+        <v>72.73040620999301</v>
       </c>
       <c r="E82">
-        <v>45.32000000000005</v>
+        <v>52.20400000000006</v>
       </c>
       <c r="F82">
-        <v>550.72</v>
+        <v>557.604</v>
       </c>
       <c r="G82">
         <v>152.4</v>
@@ -8011,37 +8011,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M82">
-        <v>129.859776</v>
+        <v>131.4830232</v>
       </c>
       <c r="N82">
-        <v>-76.52644266666668</v>
+        <v>-78.14968986666669</v>
       </c>
       <c r="O82">
-        <v>-16.83581738666667</v>
+        <v>-17.19293177066667</v>
       </c>
       <c r="P82">
-        <v>-59.69062528000001</v>
+        <v>-60.95675809600002</v>
       </c>
       <c r="Q82">
-        <v>-10.69062528000001</v>
+        <v>-11.95675809600002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1794203849578543</v>
+        <v>0.1864530367977414</v>
       </c>
       <c r="T82">
-        <v>3.085921130666382</v>
+        <v>3.248338032280402</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09035387011089047</v>
+        <v>0.08923839023297823</v>
       </c>
       <c r="W82">
-        <v>0.214494557427852</v>
+        <v>0.2147575875830638</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4106994095949567</v>
+        <v>0.4056290465135374</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2093797229338525</v>
+        <v>0.2112797229338525</v>
       </c>
       <c r="C83">
-        <v>-332.473593790007</v>
+        <v>-340.1926675340827</v>
       </c>
       <c r="D83">
-        <v>72.73040620999301</v>
+        <v>71.89533246591739</v>
       </c>
       <c r="E83">
-        <v>52.20400000000006</v>
+        <v>59.08800000000008</v>
       </c>
       <c r="F83">
-        <v>557.604</v>
+        <v>564.4880000000001</v>
       </c>
       <c r="G83">
         <v>152.4</v>
@@ -8093,37 +8093,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M83">
-        <v>131.4830232</v>
+        <v>133.1062704</v>
       </c>
       <c r="N83">
-        <v>-78.14968986666669</v>
+        <v>-79.7729370666667</v>
       </c>
       <c r="O83">
-        <v>-17.19293177066667</v>
+        <v>-17.55004615466667</v>
       </c>
       <c r="P83">
-        <v>-60.95675809600002</v>
+        <v>-62.22289091200003</v>
       </c>
       <c r="Q83">
-        <v>-11.95675809600002</v>
+        <v>-13.22289091200003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1864530367977414</v>
+        <v>0.1942670943976159</v>
       </c>
       <c r="T83">
-        <v>3.248338032280402</v>
+        <v>3.42880125629598</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08923839023297823</v>
+        <v>0.08815011718135655</v>
       </c>
       <c r="W83">
-        <v>0.2147575875830638</v>
+        <v>0.2150142023686361</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4056290465135374</v>
+        <v>0.4006823508243479</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2112797229338525</v>
+        <v>0.2131797229338525</v>
       </c>
       <c r="C84">
-        <v>-340.1926675340827</v>
+        <v>-347.8927827079574</v>
       </c>
       <c r="D84">
-        <v>71.89533246591739</v>
+        <v>71.07921729204267</v>
       </c>
       <c r="E84">
-        <v>59.08800000000008</v>
+        <v>65.97200000000009</v>
       </c>
       <c r="F84">
-        <v>564.4880000000001</v>
+        <v>571.3720000000001</v>
       </c>
       <c r="G84">
         <v>152.4</v>
@@ -8175,37 +8175,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M84">
-        <v>133.1062704</v>
+        <v>134.7295176</v>
       </c>
       <c r="N84">
-        <v>-79.7729370666667</v>
+        <v>-81.39618426666668</v>
       </c>
       <c r="O84">
-        <v>-17.55004615466667</v>
+        <v>-17.90716053866667</v>
       </c>
       <c r="P84">
-        <v>-62.22289091200003</v>
+        <v>-63.48902372800001</v>
       </c>
       <c r="Q84">
-        <v>-13.22289091200003</v>
+        <v>-14.48902372800001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1942670943976159</v>
+        <v>0.2030004528915934</v>
       </c>
       <c r="T84">
-        <v>3.42880125629598</v>
+        <v>3.630495447842803</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08815011718135655</v>
+        <v>0.08708806757676189</v>
       </c>
       <c r="W84">
-        <v>0.2150142023686361</v>
+        <v>0.2152646336653996</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4006823508243479</v>
+        <v>0.395854852621645</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2131797229338525</v>
+        <v>0.2150797229338525</v>
       </c>
       <c r="C85">
-        <v>-347.8927827079574</v>
+        <v>-355.5745776860815</v>
       </c>
       <c r="D85">
-        <v>71.07921729204267</v>
+        <v>70.28142231391857</v>
       </c>
       <c r="E85">
-        <v>65.97200000000009</v>
+        <v>72.85600000000011</v>
       </c>
       <c r="F85">
-        <v>571.3720000000001</v>
+        <v>578.2560000000001</v>
       </c>
       <c r="G85">
         <v>152.4</v>
@@ -8257,37 +8257,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M85">
-        <v>134.7295176</v>
+        <v>136.3527648</v>
       </c>
       <c r="N85">
-        <v>-81.39618426666668</v>
+        <v>-83.01943146666669</v>
       </c>
       <c r="O85">
-        <v>-17.90716053866667</v>
+        <v>-18.26427492266667</v>
       </c>
       <c r="P85">
-        <v>-63.48902372800001</v>
+        <v>-64.75515654400002</v>
       </c>
       <c r="Q85">
-        <v>-14.48902372800001</v>
+        <v>-15.75515654400002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2030004528915934</v>
+        <v>0.212825481197318</v>
       </c>
       <c r="T85">
-        <v>3.630495447842803</v>
+        <v>3.857401413332979</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08708806757676189</v>
+        <v>0.08605130486751472</v>
       </c>
       <c r="W85">
-        <v>0.2152646336653996</v>
+        <v>0.21550910231224</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.395854852621645</v>
+        <v>0.3911422948523396</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2150797229338525</v>
+        <v>0.2169797229338525</v>
       </c>
       <c r="C86">
-        <v>-355.5745776860813</v>
+        <v>-363.2386625004963</v>
       </c>
       <c r="D86">
-        <v>70.28142231391863</v>
+        <v>69.50133749950373</v>
       </c>
       <c r="E86">
-        <v>72.85599999999999</v>
+        <v>79.74000000000001</v>
       </c>
       <c r="F86">
-        <v>578.256</v>
+        <v>585.14</v>
       </c>
       <c r="G86">
         <v>152.4</v>
@@ -8339,37 +8339,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M86">
-        <v>136.3527648</v>
+        <v>137.976012</v>
       </c>
       <c r="N86">
-        <v>-83.01943146666666</v>
+        <v>-84.64267866666667</v>
       </c>
       <c r="O86">
-        <v>-18.26427492266667</v>
+        <v>-18.62138930666667</v>
       </c>
       <c r="P86">
-        <v>-64.75515654399999</v>
+        <v>-66.02128936</v>
       </c>
       <c r="Q86">
-        <v>-15.75515654399999</v>
+        <v>-17.02128936</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2128254811973179</v>
+        <v>0.2239605132771391</v>
       </c>
       <c r="T86">
-        <v>3.857401413332976</v>
+        <v>4.114561507555175</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08605130486751475</v>
+        <v>0.08503893657495575</v>
       </c>
       <c r="W86">
-        <v>0.21550910231224</v>
+        <v>0.2157478187556254</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3911422948523398</v>
+        <v>0.3865406207952534</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2169797229338525</v>
+        <v>0.2188797229338525</v>
       </c>
       <c r="C87">
-        <v>-363.2386625004963</v>
+        <v>-370.8856203964916</v>
       </c>
       <c r="D87">
-        <v>69.50133749950373</v>
+        <v>68.73837960350842</v>
       </c>
       <c r="E87">
-        <v>79.74000000000001</v>
+        <v>86.62400000000002</v>
       </c>
       <c r="F87">
-        <v>585.14</v>
+        <v>592.024</v>
       </c>
       <c r="G87">
         <v>152.4</v>
@@ -8421,37 +8421,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M87">
-        <v>137.976012</v>
+        <v>139.5992592</v>
       </c>
       <c r="N87">
-        <v>-84.64267866666667</v>
+        <v>-86.26592586666668</v>
       </c>
       <c r="O87">
-        <v>-18.62138930666667</v>
+        <v>-18.97850369066667</v>
       </c>
       <c r="P87">
-        <v>-66.02128936</v>
+        <v>-67.28742217600001</v>
       </c>
       <c r="Q87">
-        <v>-17.02128936</v>
+        <v>-18.28742217600001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2239605132771391</v>
+        <v>0.2366862642255061</v>
       </c>
       <c r="T87">
-        <v>4.114561507555175</v>
+        <v>4.40845875809483</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08503893657495575</v>
+        <v>0.0840501117310609</v>
       </c>
       <c r="W87">
-        <v>0.2157478187556254</v>
+        <v>0.2159809836538159</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3865406207952534</v>
+        <v>0.3820459624139132</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2188797229338525</v>
+        <v>0.2207797229338525</v>
       </c>
       <c r="C88">
-        <v>-370.8856203964916</v>
+        <v>-378.516009286912</v>
       </c>
       <c r="D88">
-        <v>68.73837960350842</v>
+        <v>67.99199071308803</v>
       </c>
       <c r="E88">
-        <v>86.62400000000002</v>
+        <v>93.50800000000004</v>
       </c>
       <c r="F88">
-        <v>592.024</v>
+        <v>598.908</v>
       </c>
       <c r="G88">
         <v>152.4</v>
@@ -8503,37 +8503,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M88">
-        <v>139.5992592</v>
+        <v>141.2225064</v>
       </c>
       <c r="N88">
-        <v>-86.26592586666668</v>
+        <v>-87.88917306666669</v>
       </c>
       <c r="O88">
-        <v>-18.97850369066667</v>
+        <v>-19.33561807466667</v>
       </c>
       <c r="P88">
-        <v>-67.28742217600001</v>
+        <v>-68.55355499200002</v>
       </c>
       <c r="Q88">
-        <v>-18.28742217600001</v>
+        <v>-19.55355499200002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2366862642255061</v>
+        <v>0.2513698230120835</v>
       </c>
       <c r="T88">
-        <v>4.40845875809483</v>
+        <v>4.747570970255971</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0840501117310609</v>
+        <v>0.08308401849277285</v>
       </c>
       <c r="W88">
-        <v>0.2159809836538159</v>
+        <v>0.2162087884394042</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3820459624139132</v>
+        <v>0.3776546295126039</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2207797229338525</v>
+        <v>0.2226797229338525</v>
       </c>
       <c r="C89">
-        <v>-378.516009286912</v>
+        <v>-386.1303631127329</v>
       </c>
       <c r="D89">
-        <v>67.99199071308803</v>
+        <v>67.26163688726713</v>
       </c>
       <c r="E89">
-        <v>93.50800000000004</v>
+        <v>100.3920000000001</v>
       </c>
       <c r="F89">
-        <v>598.908</v>
+        <v>605.792</v>
       </c>
       <c r="G89">
         <v>152.4</v>
@@ -8585,37 +8585,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M89">
-        <v>141.2225064</v>
+        <v>142.8457536</v>
       </c>
       <c r="N89">
-        <v>-87.88917306666669</v>
+        <v>-89.51242026666669</v>
       </c>
       <c r="O89">
-        <v>-19.33561807466667</v>
+        <v>-19.69273245866667</v>
       </c>
       <c r="P89">
-        <v>-68.55355499200002</v>
+        <v>-69.81968780800003</v>
       </c>
       <c r="Q89">
-        <v>-19.55355499200002</v>
+        <v>-20.81968780800003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2513698230120835</v>
+        <v>0.2685006415964238</v>
       </c>
       <c r="T89">
-        <v>4.747570970255971</v>
+        <v>5.143201884443969</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08308401849277285</v>
+        <v>0.08213988191899133</v>
       </c>
       <c r="W89">
-        <v>0.2162087884394042</v>
+        <v>0.2164314158435018</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3776546295126039</v>
+        <v>0.3733630996317787</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2226797229338525</v>
+        <v>0.2245797229338525</v>
       </c>
       <c r="C90">
-        <v>-386.1303631127329</v>
+        <v>-393.7291931168776</v>
       </c>
       <c r="D90">
-        <v>67.26163688726713</v>
+        <v>66.54680688312243</v>
       </c>
       <c r="E90">
-        <v>100.3920000000001</v>
+        <v>107.2760000000001</v>
       </c>
       <c r="F90">
-        <v>605.792</v>
+        <v>612.676</v>
       </c>
       <c r="G90">
         <v>152.4</v>
@@ -8667,37 +8667,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M90">
-        <v>142.8457536</v>
+        <v>144.4690008</v>
       </c>
       <c r="N90">
-        <v>-89.51242026666669</v>
+        <v>-91.13566746666667</v>
       </c>
       <c r="O90">
-        <v>-19.69273245866667</v>
+        <v>-20.04984684266667</v>
       </c>
       <c r="P90">
-        <v>-69.81968780800003</v>
+        <v>-71.08582062400001</v>
       </c>
       <c r="Q90">
-        <v>-20.81968780800003</v>
+        <v>-22.08582062400001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2685006415964238</v>
+        <v>0.288746154468826</v>
       </c>
       <c r="T90">
-        <v>5.143201884443969</v>
+        <v>5.610765692120694</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08213988191899133</v>
+        <v>0.08121696189742965</v>
       </c>
       <c r="W90">
-        <v>0.2164314158435018</v>
+        <v>0.2166490403845861</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3733630996317787</v>
+        <v>0.3691680086246801</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2245797229338525</v>
+        <v>0.2264797229338525</v>
       </c>
       <c r="C91">
-        <v>-393.7291931168776</v>
+        <v>-401.3129890376639</v>
       </c>
       <c r="D91">
-        <v>66.54680688312243</v>
+        <v>65.84701096233603</v>
       </c>
       <c r="E91">
-        <v>107.2760000000001</v>
+        <v>114.16</v>
       </c>
       <c r="F91">
-        <v>612.676</v>
+        <v>619.5599999999999</v>
       </c>
       <c r="G91">
         <v>152.4</v>
@@ -8749,37 +8749,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M91">
-        <v>144.4690008</v>
+        <v>146.092248</v>
       </c>
       <c r="N91">
-        <v>-91.13566746666667</v>
+        <v>-92.75891466666666</v>
       </c>
       <c r="O91">
-        <v>-20.04984684266667</v>
+        <v>-20.40696122666666</v>
       </c>
       <c r="P91">
-        <v>-71.08582062400001</v>
+        <v>-72.35195343999999</v>
       </c>
       <c r="Q91">
-        <v>-22.08582062400001</v>
+        <v>-23.35195343999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.288746154468826</v>
+        <v>0.3130407699157087</v>
       </c>
       <c r="T91">
-        <v>5.610765692120694</v>
+        <v>6.171842261332763</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08121696189742965</v>
+        <v>0.08031455120968044</v>
       </c>
       <c r="W91">
-        <v>0.2166490403845861</v>
+        <v>0.2168618288247574</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3691680086246801</v>
+        <v>0.3650661418621838</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2264797229338525</v>
+        <v>0.2283797229338525</v>
       </c>
       <c r="C92">
-        <v>-401.3129890376639</v>
+        <v>-408.882220227733</v>
       </c>
       <c r="D92">
-        <v>65.84701096233603</v>
+        <v>65.16177977226693</v>
       </c>
       <c r="E92">
-        <v>114.16</v>
+        <v>121.044</v>
       </c>
       <c r="F92">
-        <v>619.5599999999999</v>
+        <v>626.444</v>
       </c>
       <c r="G92">
         <v>152.4</v>
@@ -8831,37 +8831,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M92">
-        <v>146.092248</v>
+        <v>147.7154952</v>
       </c>
       <c r="N92">
-        <v>-92.75891466666666</v>
+        <v>-94.38216186666666</v>
       </c>
       <c r="O92">
-        <v>-20.40696122666666</v>
+        <v>-20.76407561066667</v>
       </c>
       <c r="P92">
-        <v>-72.35195343999999</v>
+        <v>-73.618086256</v>
       </c>
       <c r="Q92">
-        <v>-23.35195343999999</v>
+        <v>-24.618086256</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3130407699157087</v>
+        <v>0.3427341887952319</v>
       </c>
       <c r="T92">
-        <v>6.171842261332763</v>
+        <v>6.857602512591961</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08031455120968044</v>
+        <v>0.07943197372385977</v>
       </c>
       <c r="W92">
-        <v>0.2168618288247574</v>
+        <v>0.2170699405959139</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3650661418621838</v>
+        <v>0.3610544260175443</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2283797229338525</v>
+        <v>0.2302797229338525</v>
       </c>
       <c r="C93">
-        <v>-408.882220227733</v>
+        <v>-416.4373367038332</v>
       </c>
       <c r="D93">
-        <v>65.16177977226693</v>
+        <v>64.49066329616673</v>
       </c>
       <c r="E93">
-        <v>121.044</v>
+        <v>127.928</v>
       </c>
       <c r="F93">
-        <v>626.444</v>
+        <v>633.328</v>
       </c>
       <c r="G93">
         <v>152.4</v>
@@ -8913,37 +8913,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M93">
-        <v>147.7154952</v>
+        <v>149.3387424</v>
       </c>
       <c r="N93">
-        <v>-94.38216186666666</v>
+        <v>-96.00540906666667</v>
       </c>
       <c r="O93">
-        <v>-20.76407561066667</v>
+        <v>-21.12118999466667</v>
       </c>
       <c r="P93">
-        <v>-73.618086256</v>
+        <v>-74.88421907200001</v>
       </c>
       <c r="Q93">
-        <v>-24.618086256</v>
+        <v>-25.88421907200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3427341887952319</v>
+        <v>0.379850962394636</v>
       </c>
       <c r="T93">
-        <v>6.857602512591961</v>
+        <v>7.714802826665959</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07943197372385977</v>
+        <v>0.07856858270512215</v>
       </c>
       <c r="W93">
-        <v>0.2170699405959139</v>
+        <v>0.2172735281981322</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3610544260175443</v>
+        <v>0.3571299213869189</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2302797229338525</v>
+        <v>0.2321797229338525</v>
       </c>
       <c r="C94">
-        <v>-416.4373367038332</v>
+        <v>-423.9787701323946</v>
       </c>
       <c r="D94">
-        <v>64.49066329616673</v>
+        <v>63.83322986760533</v>
       </c>
       <c r="E94">
-        <v>127.928</v>
+        <v>134.812</v>
       </c>
       <c r="F94">
-        <v>633.328</v>
+        <v>640.212</v>
       </c>
       <c r="G94">
         <v>152.4</v>
@@ -8995,37 +8995,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M94">
-        <v>149.3387424</v>
+        <v>150.9619896</v>
       </c>
       <c r="N94">
-        <v>-96.00540906666667</v>
+        <v>-97.62865626666668</v>
       </c>
       <c r="O94">
-        <v>-21.12118999466667</v>
+        <v>-21.47830437866667</v>
       </c>
       <c r="P94">
-        <v>-74.88421907200001</v>
+        <v>-76.15035188800002</v>
       </c>
       <c r="Q94">
-        <v>-25.88421907200001</v>
+        <v>-27.15035188800002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.379850962394636</v>
+        <v>0.4275725284510126</v>
       </c>
       <c r="T94">
-        <v>7.714802826665959</v>
+        <v>8.816917516189667</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07856858270512215</v>
+        <v>0.07772375923517461</v>
       </c>
       <c r="W94">
-        <v>0.2172735281981322</v>
+        <v>0.2174727375723458</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3571299213869189</v>
+        <v>0.353289814705339</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2321797229338525</v>
+        <v>0.2340797229338525</v>
       </c>
       <c r="C95">
-        <v>-423.9787701323946</v>
+        <v>-431.5069347554276</v>
       </c>
       <c r="D95">
-        <v>63.83322986760533</v>
+        <v>63.18906524457239</v>
       </c>
       <c r="E95">
-        <v>134.812</v>
+        <v>141.696</v>
       </c>
       <c r="F95">
-        <v>640.212</v>
+        <v>647.096</v>
       </c>
       <c r="G95">
         <v>152.4</v>
@@ -9077,37 +9077,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M95">
-        <v>150.9619896</v>
+        <v>152.5852368</v>
       </c>
       <c r="N95">
-        <v>-97.62865626666668</v>
+        <v>-99.25190346666669</v>
       </c>
       <c r="O95">
-        <v>-21.47830437866667</v>
+        <v>-21.83541876266667</v>
       </c>
       <c r="P95">
-        <v>-76.15035188800002</v>
+        <v>-77.41648470400001</v>
       </c>
       <c r="Q95">
-        <v>-27.15035188800002</v>
+        <v>-28.41648470400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4275725284510126</v>
+        <v>0.4912012831928482</v>
       </c>
       <c r="T95">
-        <v>8.816917516189667</v>
+        <v>10.28640376888795</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07772375923517461</v>
+        <v>0.07689691073267273</v>
       </c>
       <c r="W95">
-        <v>0.2174727375723458</v>
+        <v>0.2176677084492358</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.353289814705339</v>
+        <v>0.3495314124212398</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2340797229338525</v>
+        <v>0.2359797229338525</v>
       </c>
       <c r="C96">
-        <v>-431.5069347554276</v>
+        <v>-439.0222282609211</v>
       </c>
       <c r="D96">
-        <v>63.18906524457239</v>
+        <v>62.55777173907889</v>
       </c>
       <c r="E96">
-        <v>141.696</v>
+        <v>148.58</v>
       </c>
       <c r="F96">
-        <v>647.096</v>
+        <v>653.98</v>
       </c>
       <c r="G96">
         <v>152.4</v>
@@ -9159,37 +9159,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M96">
-        <v>152.5852368</v>
+        <v>154.208484</v>
       </c>
       <c r="N96">
-        <v>-99.25190346666669</v>
+        <v>-100.8751506666667</v>
       </c>
       <c r="O96">
-        <v>-21.83541876266667</v>
+        <v>-22.19253314666667</v>
       </c>
       <c r="P96">
-        <v>-77.41648470400001</v>
+        <v>-78.68261752000001</v>
       </c>
       <c r="Q96">
-        <v>-28.41648470400001</v>
+        <v>-29.68261752000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4912012831928482</v>
+        <v>0.5802815398314179</v>
       </c>
       <c r="T96">
-        <v>10.28640376888795</v>
+        <v>12.34368452266554</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07689691073267273</v>
+        <v>0.07608746956706566</v>
       </c>
       <c r="W96">
-        <v>0.2176677084492358</v>
+        <v>0.2178585746760859</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3495314124212398</v>
+        <v>0.345852134395753</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2359797229338525</v>
+        <v>0.2378797229338525</v>
       </c>
       <c r="C97">
-        <v>-439.0222282609211</v>
+        <v>-446.5250326015812</v>
       </c>
       <c r="D97">
-        <v>62.55777173907889</v>
+        <v>61.93896739841886</v>
       </c>
       <c r="E97">
-        <v>148.58</v>
+        <v>155.4640000000001</v>
       </c>
       <c r="F97">
-        <v>653.98</v>
+        <v>660.864</v>
       </c>
       <c r="G97">
         <v>152.4</v>
@@ -9241,37 +9241,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M97">
-        <v>154.208484</v>
+        <v>155.8317312</v>
       </c>
       <c r="N97">
-        <v>-100.8751506666667</v>
+        <v>-102.4983978666667</v>
       </c>
       <c r="O97">
-        <v>-22.19253314666667</v>
+        <v>-22.54964753066667</v>
       </c>
       <c r="P97">
-        <v>-78.68261752000001</v>
+        <v>-79.94875033600002</v>
       </c>
       <c r="Q97">
-        <v>-29.68261752000001</v>
+        <v>-30.94875033600002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5802815398314179</v>
+        <v>0.7139019247892727</v>
       </c>
       <c r="T97">
-        <v>12.34368452266554</v>
+        <v>15.42960565333193</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07608746956706566</v>
+        <v>0.07529489175907539</v>
       </c>
       <c r="W97">
-        <v>0.2178585746760859</v>
+        <v>0.21804546452321</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.345852134395753</v>
+        <v>0.3422495079957972</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2378797229338525</v>
+        <v>0.2397797229338525</v>
       </c>
       <c r="C98">
-        <v>-446.5250326015811</v>
+        <v>-454.015714765454</v>
       </c>
       <c r="D98">
-        <v>61.9389673984188</v>
+        <v>61.33228523454587</v>
       </c>
       <c r="E98">
-        <v>155.4639999999999</v>
+        <v>162.348</v>
       </c>
       <c r="F98">
-        <v>660.8639999999999</v>
+        <v>667.7479999999999</v>
       </c>
       <c r="G98">
         <v>152.4</v>
@@ -9323,37 +9323,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M98">
-        <v>155.8317312</v>
+        <v>157.4549784</v>
       </c>
       <c r="N98">
-        <v>-102.4983978666667</v>
+        <v>-104.1216450666667</v>
       </c>
       <c r="O98">
-        <v>-22.54964753066666</v>
+        <v>-22.90676191466666</v>
       </c>
       <c r="P98">
-        <v>-79.94875033599999</v>
+        <v>-81.214883152</v>
       </c>
       <c r="Q98">
-        <v>-30.94875033599999</v>
+        <v>-32.214883152</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7139019247892708</v>
+        <v>0.9366025663856947</v>
       </c>
       <c r="T98">
-        <v>15.42960565333189</v>
+        <v>20.57280753777586</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0752948917590754</v>
+        <v>0.07451865576155917</v>
       </c>
       <c r="W98">
-        <v>0.21804546452321</v>
+        <v>0.2182285009714244</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3422495079957973</v>
+        <v>0.3387211625525416</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2397797229338525</v>
+        <v>0.2416797229338525</v>
       </c>
       <c r="C99">
-        <v>-454.015714765454</v>
+        <v>-461.4946275016998</v>
       </c>
       <c r="D99">
-        <v>61.33228523454587</v>
+        <v>60.73737249830013</v>
       </c>
       <c r="E99">
-        <v>162.348</v>
+        <v>169.232</v>
       </c>
       <c r="F99">
-        <v>667.7479999999999</v>
+        <v>674.6319999999999</v>
       </c>
       <c r="G99">
         <v>152.4</v>
@@ -9405,37 +9405,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M99">
-        <v>157.4549784</v>
+        <v>159.0782256</v>
       </c>
       <c r="N99">
-        <v>-104.1216450666667</v>
+        <v>-105.7448922666667</v>
       </c>
       <c r="O99">
-        <v>-22.90676191466666</v>
+        <v>-23.26387629866667</v>
       </c>
       <c r="P99">
-        <v>-81.214883152</v>
+        <v>-82.48101596800001</v>
       </c>
       <c r="Q99">
-        <v>-32.214883152</v>
+        <v>-33.48101596800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9366025663856947</v>
+        <v>1.382003849578542</v>
       </c>
       <c r="T99">
-        <v>20.57280753777586</v>
+        <v>30.85921130666379</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07451865576155917</v>
+        <v>0.07375826131501263</v>
       </c>
       <c r="W99">
-        <v>0.2182285009714244</v>
+        <v>0.21840780198192</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3387211625525416</v>
+        <v>0.3352648241591484</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2416797229338525</v>
+        <v>0.2435797229338525</v>
       </c>
       <c r="C100">
-        <v>-461.4946275016998</v>
+        <v>-468.9621100045314</v>
       </c>
       <c r="D100">
-        <v>60.73737249830013</v>
+        <v>60.15388999546861</v>
       </c>
       <c r="E100">
-        <v>169.232</v>
+        <v>176.116</v>
       </c>
       <c r="F100">
-        <v>674.6319999999999</v>
+        <v>681.516</v>
       </c>
       <c r="G100">
         <v>152.4</v>
@@ -9487,37 +9487,37 @@
         <v>53.33333333333333</v>
       </c>
       <c r="M100">
-        <v>159.0782256</v>
+        <v>160.7014728</v>
       </c>
       <c r="N100">
-        <v>-105.7448922666667</v>
+        <v>-107.3681394666667</v>
       </c>
       <c r="O100">
-        <v>-23.26387629866667</v>
+        <v>-23.62099068266667</v>
       </c>
       <c r="P100">
-        <v>-82.48101596800001</v>
+        <v>-83.747148784</v>
       </c>
       <c r="Q100">
-        <v>-33.48101596800001</v>
+        <v>-34.747148784</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.382003849578542</v>
+        <v>2.718207699157084</v>
       </c>
       <c r="T100">
-        <v>30.85921130666379</v>
+        <v>61.71842261332758</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07375826131501263</v>
+        <v>0.07301322837243675</v>
       </c>
       <c r="W100">
-        <v>0.21840780198192</v>
+        <v>0.2185834807497794</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3352648241591484</v>
+        <v>0.3318783107838034</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2435797229338525</v>
-      </c>
-      <c r="C101">
-        <v>-468.9621100045314</v>
-      </c>
-      <c r="D101">
-        <v>60.15388999546861</v>
-      </c>
-      <c r="E101">
-        <v>176.116</v>
-      </c>
-      <c r="F101">
-        <v>681.516</v>
-      </c>
-      <c r="G101">
-        <v>152.4</v>
-      </c>
-      <c r="H101">
-        <v>183</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>102.3333333333333</v>
-      </c>
-      <c r="K101">
-        <v>49</v>
-      </c>
-      <c r="L101">
-        <v>53.33333333333333</v>
-      </c>
-      <c r="M101">
-        <v>160.7014728</v>
-      </c>
-      <c r="N101">
-        <v>-107.3681394666667</v>
-      </c>
-      <c r="O101">
-        <v>-23.62099068266667</v>
-      </c>
-      <c r="P101">
-        <v>-83.747148784</v>
-      </c>
-      <c r="Q101">
-        <v>-34.747148784</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.718207699157084</v>
-      </c>
-      <c r="T101">
-        <v>61.71842261332758</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07301322837243675</v>
-      </c>
-      <c r="W101">
-        <v>0.2185834807497794</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3318783107838034</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
